--- a/outputs/response_curves.xlsx
+++ b/outputs/response_curves.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="6">
   <si>
     <t>impressions</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>implied_roi</t>
+  </si>
+  <si>
+    <t>mroi</t>
   </si>
 </sst>
 </file>
@@ -363,10 +366,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -382,8 +385,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>6025214.466427003</v>
       </c>
@@ -391,16 +397,19 @@
         <v>69063.60521282686</v>
       </c>
       <c r="C2">
-        <v>20103.52114358863</v>
+        <v>10047.61751458828</v>
       </c>
       <c r="D2">
-        <v>191110.1255675075</v>
+        <v>95515.67763439489</v>
       </c>
       <c r="E2">
-        <v>2.767161154975639</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>1.383010303908305</v>
+      </c>
+      <c r="F2">
+        <v>2.629196656444142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>6377417.263279029</v>
       </c>
@@ -408,16 +417,19 @@
         <v>73100.70547741983</v>
       </c>
       <c r="C3">
-        <v>21055.55742989104</v>
+        <v>11164.17487829617</v>
       </c>
       <c r="D3">
-        <v>200160.4691824668</v>
+        <v>106130.0081517925</v>
       </c>
       <c r="E3">
-        <v>2.738146887574083</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>1.451832885314289</v>
+      </c>
+      <c r="F3">
+        <v>2.64765485992821</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>6729620.060131055</v>
       </c>
@@ -425,16 +437,19 @@
         <v>77137.8057420128</v>
       </c>
       <c r="C4">
-        <v>21950.918422483</v>
+        <v>12296.40976309815</v>
       </c>
       <c r="D4">
-        <v>208672.0403893381</v>
+        <v>116893.373905529</v>
       </c>
       <c r="E4">
-        <v>2.705185069526624</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>1.51538370557854</v>
+      </c>
+      <c r="F4">
+        <v>2.675637665401252</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>7081822.856983082</v>
       </c>
@@ -442,16 +457,19 @@
         <v>81174.90600660577</v>
       </c>
       <c r="C5">
-        <v>22792.28279841514</v>
+        <v>13436.73439231778</v>
       </c>
       <c r="D5">
-        <v>216670.3034987686</v>
+        <v>127733.6432056851</v>
       </c>
       <c r="E5">
-        <v>2.669178372453386</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>1.573560715860768</v>
+      </c>
+      <c r="F5">
+        <v>2.686415157098405</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>7434025.653835109</v>
       </c>
@@ -459,16 +477,19 @@
         <v>85212.00627119873</v>
       </c>
       <c r="C6">
-        <v>23582.5021072761</v>
+        <v>14578.123166531</v>
       </c>
       <c r="D6">
-        <v>224182.3661998068</v>
+        <v>138584.028588586</v>
       </c>
       <c r="E6">
-        <v>2.630877689774328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>1.626343923267381</v>
+      </c>
+      <c r="F6">
+        <v>2.681402476513121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>7786228.450687135</v>
       </c>
@@ -476,16 +497,19 @@
         <v>89249.1065357917</v>
       </c>
       <c r="C7">
-        <v>24324.49641275756</v>
+        <v>15714.19026301286</v>
       </c>
       <c r="D7">
-        <v>231235.9874971963</v>
+        <v>149383.8245005078</v>
       </c>
       <c r="E7">
-        <v>2.590905348777508</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>1.673785097676022</v>
+      </c>
+      <c r="F7">
+        <v>2.662161728778765</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>8138431.247539161</v>
       </c>
@@ -493,16 +517,19 @@
         <v>93286.20680038465</v>
       </c>
       <c r="C8">
-        <v>25021.17849606888</v>
+        <v>16839.23686022432</v>
       </c>
       <c r="D8">
-        <v>237858.8571662106</v>
+        <v>160078.85622787</v>
       </c>
       <c r="E8">
-        <v>2.549775206051467</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>1.715997055924992</v>
+      </c>
+      <c r="F8">
+        <v>2.630334509008536</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8490634.044391187</v>
       </c>
@@ -510,16 +537,19 @@
         <v>97323.30706497761</v>
       </c>
       <c r="C9">
-        <v>25675.40017175751</v>
+        <v>17948.27142833771</v>
       </c>
       <c r="D9">
-        <v>244078.0854146765</v>
+        <v>170621.6727850805</v>
       </c>
       <c r="E9">
-        <v>2.507909901291358</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>1.753142982196088</v>
+      </c>
+      <c r="F9">
+        <v>2.587583310384733</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8842836.841243213</v>
       </c>
@@ -527,16 +557,19 @@
         <v>101360.4073295706</v>
       </c>
       <c r="C10">
-        <v>26289.91552421684</v>
+        <v>19037.00718853836</v>
       </c>
       <c r="D10">
-        <v>249919.8533981483</v>
+        <v>180971.5227618911</v>
       </c>
       <c r="E10">
-        <v>2.46565557481967</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>1.785426159283942</v>
+      </c>
+      <c r="F10">
+        <v>2.535542904072138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9195039.638095239</v>
       </c>
@@ -544,16 +577,19 @@
         <v>105397.5075941635</v>
       </c>
       <c r="C11">
-        <v>26867.35694347337</v>
+        <v>20101.84110795835</v>
       </c>
       <c r="D11">
-        <v>255409.1854088836</v>
+        <v>191094.1546429133</v>
       </c>
       <c r="E11">
-        <v>2.423294357133613</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>1.813080394450384</v>
+      </c>
+      <c r="F11">
+        <v>2.475781934132283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>9547242.434947265</v>
       </c>
@@ -561,16 +597,19 @@
         <v>109434.6078587565</v>
       </c>
       <c r="C12">
-        <v>27410.22072610027</v>
+        <v>21139.81873952292</v>
       </c>
       <c r="D12">
-        <v>260569.8119937923</v>
+        <v>200961.4825646109</v>
       </c>
       <c r="E12">
-        <v>2.381054924874413</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>1.836361334834635</v>
+      </c>
+      <c r="F12">
+        <v>2.409774312935995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>9899445.231799291</v>
       </c>
@@ -578,16 +617,19 @@
         <v>113471.7081233495</v>
       </c>
       <c r="C13">
-        <v>27920.85972842839</v>
+        <v>22148.58892150667</v>
       </c>
       <c r="D13">
-        <v>265424.1001136483</v>
+        <v>210551.1556756398</v>
       </c>
       <c r="E13">
-        <v>2.339121394252027</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>1.8555387872258</v>
+      </c>
+      <c r="F13">
+        <v>2.338879541330148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>10251648.02865132</v>
       </c>
@@ -595,16 +637,19 @@
         <v>117508.8083879425</v>
       </c>
       <c r="C14">
-        <v>28401.48113694125</v>
+        <v>23126.35190226461</v>
       </c>
       <c r="D14">
-        <v>269993.031947792</v>
+        <v>219846.064994921</v>
       </c>
       <c r="E14">
-        <v>2.297640795202685</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>1.870890089099732</v>
+      </c>
+      <c r="F14">
+        <v>2.264330797719208</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>10603850.82550335</v>
       </c>
@@ -612,16 +657,19 @@
         <v>121545.9086525354</v>
       </c>
       <c r="C15">
-        <v>28854.14787799742</v>
+        <v>24071.80392322001</v>
       </c>
       <c r="D15">
-        <v>274296.2182953772</v>
+        <v>228833.8166008363</v>
       </c>
       <c r="E15">
-        <v>2.256729340676622</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>1.882694523721123</v>
+      </c>
+      <c r="F15">
+        <v>2.187229512560227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>10956053.62235537</v>
       </c>
@@ -629,16 +677,19 @@
         <v>125583.0089171284</v>
       </c>
       <c r="C16">
-        <v>29280.78254747618</v>
+        <v>24984.08073542937</v>
       </c>
       <c r="D16">
-        <v>278351.9359317645</v>
+        <v>237506.1946826858</v>
       </c>
       <c r="E16">
-        <v>2.216477677449563</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>1.891228731742007</v>
+      </c>
+      <c r="F16">
+        <v>2.108545135115937</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>11308256.4192074</v>
       </c>
@@ -646,16 +697,19 @@
         <v>129620.1091817213</v>
       </c>
       <c r="C17">
-        <v>29683.17301968268</v>
+        <v>25862.70198446146</v>
       </c>
       <c r="D17">
-        <v>282177.1809284639</v>
+        <v>245858.6328466018</v>
       </c>
       <c r="E17">
-        <v>2.17695527885156</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>1.896763043934174</v>
+      </c>
+      <c r="F17">
+        <v>2.029118873231217</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>11660459.21605942</v>
       </c>
@@ -663,16 +717,19 @@
         <v>133657.2094463143</v>
       </c>
       <c r="C18">
-        <v>30062.97911009679</v>
+        <v>26707.51790335056</v>
       </c>
       <c r="D18">
-        <v>285787.7319912309</v>
+        <v>253889.7073627105</v>
       </c>
       <c r="E18">
-        <v>2.138214116358777</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>1.899558642698504</v>
+      </c>
+      <c r="F18">
+        <v>1.949670313604066</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>12012662.01291145</v>
       </c>
@@ -680,16 +737,19 @@
         <v>137694.3097109073</v>
       </c>
       <c r="C19">
-        <v>30421.73983172107</v>
+        <v>27518.65932041933</v>
       </c>
       <c r="D19">
-        <v>289198.219441096</v>
+        <v>261600.6619244418</v>
       </c>
       <c r="E19">
-        <v>2.100291726275945</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>1.89986545176543</v>
+      </c>
+      <c r="F19">
+        <v>1.870805984251907</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>12364864.80976348</v>
       </c>
@@ -697,16 +757,19 @@
         <v>141731.4099755002</v>
       </c>
       <c r="C20">
-        <v>30760.88091077799</v>
+        <v>28296.49162478404</v>
       </c>
       <c r="D20">
-        <v>292422.1966608448</v>
+        <v>268994.9700307614</v>
       </c>
       <c r="E20">
-        <v>2.063213769702799</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>1.897920652008331</v>
+      </c>
+      <c r="F20">
+        <v>1.793029083438709</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>12717067.6066155</v>
       </c>
@@ -714,16 +777,19 @@
         <v>145768.5102400932</v>
       </c>
       <c r="C21">
-        <v>31081.72232304938</v>
+        <v>29041.57303746591</v>
       </c>
       <c r="D21">
-        <v>295472.2117377308</v>
+        <v>276077.9382987884</v>
       </c>
       <c r="E21">
-        <v>2.026996168452726</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>1.893947724677055</v>
+      </c>
+      <c r="F21">
+        <v>1.716749756786525</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>13069270.40346753</v>
       </c>
@@ -731,16 +797,19 @@
         <v>149805.6105046861</v>
       </c>
       <c r="C22">
-        <v>31385.48568415909</v>
+        <v>29754.61730578667</v>
       </c>
       <c r="D22">
-        <v>298359.8777177274</v>
+        <v>282856.351825487</v>
       </c>
       <c r="E22">
-        <v>1.991646886338708</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>1.888155930025323</v>
+      </c>
+      <c r="F22">
+        <v>1.642295448126845</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>13421473.20031955</v>
       </c>
@@ -748,16 +817,19 @@
         <v>153842.7107692791</v>
       </c>
       <c r="C23">
-        <v>31673.30138100414</v>
+        <v>30436.46076600121</v>
       </c>
       <c r="D23">
-        <v>301095.9403990603</v>
+        <v>289338.1610751338</v>
       </c>
       <c r="E23">
-        <v>1.957167414000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>1.880740137952066</v>
+      </c>
+      <c r="F23">
+        <v>1.569920975236504</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>13773675.99717158</v>
       </c>
@@ -765,16 +837,19 @@
         <v>157879.811033872</v>
       </c>
       <c r="C24">
-        <v>31946.21537158298</v>
+        <v>31088.03359554455</v>
       </c>
       <c r="D24">
-        <v>303690.3429734214</v>
+        <v>295532.2085945216</v>
       </c>
       <c r="E24">
-        <v>1.923554005953724</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>1.871880936892667</v>
+      </c>
+      <c r="F24">
+        <v>1.499818087221903</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>14125878.79402361</v>
       </c>
@@ -782,16 +857,19 @@
         <v>161916.911298465</v>
       </c>
       <c r="C25">
-        <v>32205.1956099429</v>
+        <v>31710.33499325263</v>
       </c>
       <c r="D25">
-        <v>306152.2871034552</v>
+        <v>301447.9930686635</v>
       </c>
       <c r="E25">
-        <v>1.890798710575191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>1.861744957035388</v>
+      </c>
+      <c r="F25">
+        <v>1.432124346216329</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>14478081.59087563</v>
       </c>
@@ -799,16 +877,19 @@
         <v>165954.011563058</v>
       </c>
       <c r="C26">
-        <v>32451.13807441752</v>
+        <v>32304.41197530093</v>
       </c>
       <c r="D26">
-        <v>308490.2902289981</v>
+        <v>307095.4677486016</v>
       </c>
       <c r="E26">
-        <v>1.858890227017984</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>1.850485353479471</v>
+      </c>
+      <c r="F26">
+        <v>1.366931243727859</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>14830284.38772766</v>
       </c>
@@ -816,16 +897,19 @@
         <v>169991.111827651</v>
       </c>
       <c r="C27">
-        <v>32684.87239270877</v>
+        <v>32871.34144906557</v>
       </c>
       <c r="D27">
-        <v>310712.2390408022</v>
+        <v>312484.8700401318</v>
       </c>
       <c r="E27">
-        <v>1.827814617483203</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>1.838242403855509</v>
+      </c>
+      <c r="F27">
+        <v>1.304291513586095</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>15182487.18457969</v>
       </c>
@@ -833,16 +917,19 @@
         <v>174028.2120922439</v>
       </c>
       <c r="C28">
-        <v>32907.16706818848</v>
+        <v>33412.21522033156</v>
       </c>
       <c r="D28">
-        <v>312825.4391633322</v>
+        <v>317626.5789778112</v>
       </c>
       <c r="E28">
-        <v>1.79755589856614</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>1.825144182998632</v>
+      </c>
+      <c r="F28">
+        <v>1.244225641415804</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>15534689.98143171</v>
       </c>
@@ -850,16 +937,19 @@
         <v>178065.3123568369</v>
       </c>
       <c r="C29">
-        <v>33118.73431920351</v>
+        <v>33928.12759599143</v>
       </c>
       <c r="D29">
-        <v>314836.6611586566</v>
+        <v>322530.997372478</v>
       </c>
       <c r="E29">
-        <v>1.768096531500389</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>1.811307284408862</v>
+      </c>
+      <c r="F29">
+        <v>1.186727597340933</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>15886892.77828374</v>
       </c>
@@ -867,16 +957,19 @@
         <v>182102.4126214298</v>
       </c>
       <c r="C30">
-        <v>33320.23454804122</v>
+        <v>34420.16526033995</v>
       </c>
       <c r="D30">
-        <v>316752.1830097795</v>
+        <v>327208.4555722608</v>
       </c>
       <c r="E30">
-        <v>1.739417827858609</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>1.796837564434085</v>
+      </c>
+      <c r="F30">
+        <v>1.131769836449804</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>16239095.57513576</v>
       </c>
@@ -884,16 +977,19 @@
         <v>186139.5128860228</v>
       </c>
       <c r="C31">
-        <v>33512.28045921621</v>
+        <v>34889.3991249303</v>
       </c>
       <c r="D31">
-        <v>318577.8292703145</v>
+        <v>331669.1339848576</v>
       </c>
       <c r="E31">
-        <v>1.711500284549399</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>1.781830890402865</v>
+      </c>
+      <c r="F31">
+        <v>1.079307622425665</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>16591298.37198779</v>
       </c>
@@ -901,16 +997,19 @@
         <v>190176.6131506157</v>
       </c>
       <c r="C32">
-        <v>33695.44084837972</v>
+        <v>35336.87787715522</v>
       </c>
       <c r="D32">
-        <v>320319.0070829982</v>
+        <v>335923.0017484045</v>
       </c>
       <c r="E32">
-        <v>1.684323859681487</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>1.76637387838199</v>
+      </c>
+      <c r="F32">
+        <v>1.02928273536715</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>16943501.16883982</v>
       </c>
@@ -918,16 +1017,19 @@
         <v>194213.7134152087</v>
       </c>
       <c r="C33">
-        <v>33870.2440838113</v>
+        <v>35763.6229793497</v>
       </c>
       <c r="D33">
-        <v>321980.7392757981</v>
+        <v>339979.769191441</v>
       </c>
       <c r="E33">
-        <v>1.657868198974378</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>1.750544609919484</v>
+      </c>
+      <c r="F33">
+        <v>0.9816266265934026</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>17295703.96569184</v>
       </c>
@@ -935,16 +1037,19 @@
         <v>198250.8136798017</v>
       </c>
       <c r="C34">
-        <v>34037.18130241511</v>
+        <v>36170.62489691367</v>
       </c>
       <c r="D34">
-        <v>323567.6947440166</v>
+        <v>343848.851976308</v>
       </c>
       <c r="E34">
-        <v>1.632112820816042</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>1.734413320147398</v>
+      </c>
+      <c r="F34">
+        <v>0.9362630822786575</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>17647906.76254387</v>
       </c>
@@ -952,16 +1057,19 @@
         <v>202287.9139443946</v>
       </c>
       <c r="C35">
-        <v>34196.7093416257</v>
+        <v>36558.84035977945</v>
       </c>
       <c r="D35">
-        <v>325084.2163218695</v>
+        <v>347539.3450658326</v>
       </c>
       <c r="E35">
-        <v>1.607037266750545</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>1.718043052049887</v>
+      </c>
+      <c r="F35">
+        <v>0.8931104549778219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>18000109.55939589</v>
       </c>
@@ -969,16 +1077,19 @@
         <v>206325.0142089876</v>
       </c>
       <c r="C36">
-        <v>34349.25342778855</v>
+        <v>36929.19048588614</v>
       </c>
       <c r="D36">
-        <v>326534.3463390412</v>
+        <v>351060.0048845114</v>
       </c>
       <c r="E36">
-        <v>1.582621223078133</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>1.701490273636531</v>
+      </c>
+      <c r="F36">
+        <v>0.8520835181668056</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>18352312.35624792</v>
       </c>
@@ -986,16 +1097,19 @@
         <v>210362.1144735806</v>
       </c>
       <c r="C37">
-        <v>34495.20964053965</v>
+        <v>37282.55961780558</v>
       </c>
       <c r="D37">
-        <v>327921.8500478189</v>
+        <v>354419.2382591256</v>
       </c>
       <c r="E37">
-        <v>1.558844618330753</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>1.684805456277334</v>
+      </c>
+      <c r="F37">
+        <v>0.8130949943386796</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>18704515.15309995</v>
       </c>
@@ -1003,16 +1117,19 @@
         <v>214399.2147381735</v>
       </c>
       <c r="C38">
-        <v>34634.94717154883</v>
+        <v>37619.79474410904</v>
       </c>
       <c r="D38">
-        <v>329250.2370953871</v>
+        <v>357625.0969180792</v>
       </c>
       <c r="E38">
-        <v>1.535687700617145</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>1.668033613625006</v>
+      </c>
+      <c r="F38">
+        <v>0.7760568023388366</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>19056717.94995197</v>
       </c>
@@ -1020,16 +1137,19 @@
         <v>218436.3150027665</v>
       </c>
       <c r="C39">
-        <v>34768.81039477899</v>
+        <v>37941.70539542036</v>
       </c>
       <c r="D39">
-        <v>330522.7812043353</v>
+        <v>360685.2765032482</v>
       </c>
       <c r="E39">
-        <v>1.513131098188272</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>1.651214801433911</v>
+      </c>
+      <c r="F39">
+        <v>0.7408810647507785</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>19408920.746804</v>
       </c>
@@ -1037,16 +1157,19 @@
         <v>222473.4152673595</v>
       </c>
       <c r="C40">
-        <v>34897.12076419063</v>
+        <v>38249.06392140826</v>
       </c>
       <c r="D40">
-        <v>331742.538212808</v>
+        <v>363607.1192031538</v>
       </c>
       <c r="E40">
-        <v>1.491155866035199</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>1.634384579236964</v>
+      </c>
+      <c r="F40">
+        <v>0.7074809114357545</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>19761123.54365603</v>
       </c>
@@ -1054,16 +1177,19 @@
         <v>226510.5155319524</v>
       </c>
       <c r="C41">
-        <v>35020.17855361856</v>
+        <v>38542.60606932789</v>
       </c>
       <c r="D41">
-        <v>332912.3626142976</v>
+        <v>366397.6192527517</v>
       </c>
       <c r="E41">
-        <v>1.469743520880097</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>1.617574435307249</v>
+      </c>
+      <c r="F41">
+        <v>0.6757711108980449</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>20113326.34050805</v>
       </c>
@@ -1071,16 +1197,19 @@
         <v>230547.6157965454</v>
       </c>
       <c r="C42">
-        <v>35138.26445238898</v>
+        <v>38823.03179726487</v>
       </c>
       <c r="D42">
-        <v>334034.92272606</v>
+        <v>369063.4306643753</v>
       </c>
       <c r="E42">
-        <v>1.448876066542543</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>1.600812176648437</v>
+      </c>
+      <c r="F42">
+        <v>0.6456685570591851</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>20465529.13736008</v>
       </c>
@@ -1088,16 +1217,19 @@
         <v>234584.7160611384</v>
       </c>
       <c r="C43">
-        <v>35251.64102914004</v>
+        <v>39091.00626611964</v>
       </c>
       <c r="D43">
-        <v>335112.7146046345</v>
+        <v>371610.8766578377</v>
       </c>
       <c r="E43">
-        <v>1.428536011345667</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>1.584122285959103</v>
+      </c>
+      <c r="F43">
+        <v>0.6170926353091142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>20817731.93421211</v>
       </c>
@@ -1105,16 +1237,19 @@
         <v>238621.8163257313</v>
       </c>
       <c r="C44">
-        <v>35360.55407526922</v>
+        <v>39347.160963758</v>
       </c>
       <c r="D44">
-        <v>336148.0748170581</v>
+        <v>374045.9603469449</v>
       </c>
       <c r="E44">
-        <v>1.408706378959911</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>1.567526247626715</v>
+      </c>
+      <c r="F44">
+        <v>0.5899654883695904</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>21169934.73106413</v>
       </c>
@@ -1122,16 +1257,19 @@
         <v>242658.9165903243</v>
       </c>
       <c r="C45">
-        <v>35465.23383845756</v>
+        <v>39592.09492280726</v>
       </c>
       <c r="D45">
-        <v>337143.1921671189</v>
+        <v>376374.3763162329</v>
       </c>
       <c r="E45">
-        <v>1.389370713858046</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>1.551042844849</v>
+      </c>
+      <c r="F45">
+        <v>0.5642121995460563</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>21522137.52791616</v>
       </c>
@@ -1139,16 +1277,19 @@
         <v>246696.0168549173</v>
       </c>
       <c r="C46">
-        <v>35565.89615581738</v>
+        <v>39826.37600045213</v>
       </c>
       <c r="D46">
-        <v>338100.1184673997</v>
+        <v>378601.5227870928</v>
       </c>
       <c r="E46">
-        <v>1.370513082366618</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>1.534688429970678</v>
+      </c>
+      <c r="F46">
+        <v>0.5397609083372295</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>21874340.32476819</v>
       </c>
@@ -1156,16 +1297,19 @@
         <v>250733.1171195102</v>
       </c>
       <c r="C47">
-        <v>35662.74349537478</v>
+        <v>40050.5421944242</v>
       </c>
       <c r="D47">
-        <v>339020.7784399238</v>
+        <v>380732.5141279632</v>
       </c>
       <c r="E47">
-        <v>1.352118070140419</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>1.51847717007598</v>
+      </c>
+      <c r="F47">
+        <v>0.5165428710942548</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>22226543.12162021</v>
       </c>
@@ -1173,16 +1317,19 @@
         <v>254770.2173841032</v>
       </c>
       <c r="C48">
-        <v>35755.96591382857</v>
+        <v>40265.10297431884</v>
       </c>
       <c r="D48">
-        <v>339906.9788209</v>
+        <v>382772.1935102293</v>
       </c>
       <c r="E48">
-        <v>1.33417077675308</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>1.502421269803073</v>
+      </c>
+      <c r="F48">
+        <v>0.494492477442805</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>22578745.91847224</v>
       </c>
@@ -1190,16 +1337,19 @@
         <v>258807.3176486962</v>
       </c>
       <c r="C49">
-        <v>35845.74193782173</v>
+        <v>40470.54061153283</v>
       </c>
       <c r="D49">
-        <v>340760.4167383544</v>
+        <v>384725.1455510104</v>
       </c>
       <c r="E49">
-        <v>1.316656807984467</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>1.486531173253897</v>
+      </c>
+      <c r="F49">
+        <v>0.4735472314717729</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>22930948.71532426</v>
       </c>
@@ -1207,16 +1357,19 @@
         <v>262844.4179132891</v>
       </c>
       <c r="C50">
-        <v>35932.23937531502</v>
+        <v>40667.31149460381</v>
       </c>
       <c r="D50">
-        <v>341582.6874252924</v>
+        <v>386595.7088171732</v>
       </c>
       <c r="E50">
-        <v>1.299562266290847</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>1.470815746768908</v>
+      </c>
+      <c r="F50">
+        <v>0.4536477052233712</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>23283151.51217629</v>
       </c>
@@ -1224,16 +1377,19 @@
         <v>266881.5181778821</v>
       </c>
       <c r="C51">
-        <v>36015.61606306212</v>
+        <v>40855.84741964462</v>
       </c>
       <c r="D51">
-        <v>342375.2913254221</v>
+        <v>388387.9880925889</v>
       </c>
       <c r="E51">
-        <v>1.282873739863927</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>1.455282444225757</v>
+      </c>
+      <c r="F51">
+        <v>0.4347374707617996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>23635354.30902832</v>
       </c>
@@ -1241,16 +1397,19 @@
         <v>270918.618442475</v>
       </c>
       <c r="C52">
-        <v>36096.02055564706</v>
+        <v>41036.55684798511</v>
       </c>
       <c r="D52">
-        <v>343139.6406433525</v>
+        <v>390105.8663336551</v>
       </c>
       <c r="E52">
-        <v>1.266578290617602</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>1.439937456408104</v>
+      </c>
+      <c r="F52">
+        <v>0.4167630160255559</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>23987557.10588034</v>
       </c>
@@ -1258,16 +1417,19 @@
         <v>274955.718707068</v>
       </c>
       <c r="C53">
-        <v>36173.59276105477</v>
+        <v>41209.82612513544</v>
       </c>
       <c r="D53">
-        <v>343877.0653865171</v>
+        <v>391753.0162571276</v>
       </c>
       <c r="E53">
-        <v>1.250663441384452</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>1.424785845878306</v>
+      </c>
+      <c r="F53">
+        <v>0.3996736487584328</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>24339759.90273237</v>
       </c>
@@ -1275,16 +1437,19 @@
         <v>278992.8189716609</v>
       </c>
       <c r="C54">
-        <v>36248.46452729899</v>
+        <v>41376.0206568314</v>
       </c>
       <c r="D54">
-        <v>344588.8189418369</v>
+        <v>393332.9115199621</v>
       </c>
       <c r="E54">
-        <v>1.235117162556213</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>1.409831668677879</v>
+      </c>
+      <c r="F54">
+        <v>0.3834213920434504</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>24691962.69958439</v>
       </c>
@@ -1292,16 +1457,19 @@
         <v>283029.9192362539</v>
       </c>
       <c r="C55">
-        <v>36320.76018422662</v>
+        <v>41535.48603926924</v>
       </c>
       <c r="D55">
-        <v>345276.0832262744</v>
+        <v>394848.837463666</v>
       </c>
       <c r="E55">
-        <v>1.219927858362076</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>1.395078084073767</v>
+      </c>
+      <c r="F55">
+        <v>0.367960874314699</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>25044165.49643642</v>
       </c>
@@ -1309,16 +1477,19 @@
         <v>287067.0195008469</v>
       </c>
       <c r="C56">
-        <v>36390.59704424888</v>
+        <v>41688.54914173228</v>
       </c>
       <c r="D56">
-        <v>345939.9734469362</v>
+        <v>396303.9014060735</v>
       </c>
       <c r="E56">
-        <v>1.205084352944681</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>1.380527453467724</v>
+      </c>
+      <c r="F56">
+        <v>0.3532492161755836</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>25396368.29328845</v>
       </c>
@@ -1326,16 +1497,19 @@
         <v>291104.1197654398</v>
       </c>
       <c r="C57">
-        <v>36458.08586541543</v>
+        <v>41835.51914069447</v>
       </c>
       <c r="D57">
-        <v>346581.5425031935</v>
+        <v>397701.0424718454</v>
       </c>
       <c r="E57">
-        <v>1.190575876364976</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>1.366181429490923</v>
+      </c>
+      <c r="F57">
+        <v>0.3392459158941219</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>25748571.09014047</v>
       </c>
@@ -1343,16 +1517,19 @@
         <v>295141.2200300328</v>
       </c>
       <c r="C58">
-        <v>36523.33127994333</v>
+        <v>41976.68850519222</v>
       </c>
       <c r="D58">
-        <v>347201.7850604089</v>
+        <v>399043.04095971</v>
       </c>
       <c r="E58">
-        <v>1.176392050643006</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>1.352041036216847</v>
+      </c>
+      <c r="F58">
+        <v>0.3259127350644078</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>26100773.8869925</v>
       </c>
@@ -1360,16 +1537,19 @@
         <v>299178.3202946258</v>
       </c>
       <c r="C59">
-        <v>36586.43219103755</v>
+        <v>42112.33393381421</v>
       </c>
       <c r="D59">
-        <v>347801.6413222302</v>
+        <v>400332.5272497709</v>
       </c>
       <c r="E59">
-        <v>1.16252287592136</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>1.338106741342522</v>
+      </c>
+      <c r="F59">
+        <v>0.3132135856047135</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>26452976.68384453</v>
       </c>
@@ -1377,16 +1557,19 @@
         <v>303215.4205592187</v>
       </c>
       <c r="C60">
-        <v>36647.4821405892</v>
+        <v>42242.71724409475</v>
       </c>
       <c r="D60">
-        <v>348382.000526042</v>
+        <v>401571.9902583478</v>
       </c>
       <c r="E60">
-        <v>1.148958716820941</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>1.324378521111263</v>
+      </c>
+      <c r="F60">
+        <v>0.301114418999453</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>26805179.48069655</v>
       </c>
@@ -1394,13 +1577,16 @@
         <v>307252.5208238117</v>
       </c>
       <c r="C61">
-        <v>36706.56965011059</v>
+        <v>42368.08621543104</v>
       </c>
       <c r="D61">
-        <v>348943.7041839957</v>
+        <v>402763.7854510018</v>
       </c>
       <c r="E61">
-        <v>1.135690289044337</v>
+        <v>1.310855918679213</v>
+      </c>
+      <c r="F61">
+        <v>0.2952106993988948</v>
       </c>
     </row>
   </sheetData>
@@ -1410,10 +1596,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1429,8 +1615,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>3667025.860918613</v>
       </c>
@@ -1438,16 +1627,19 @@
         <v>33337.86217631619</v>
       </c>
       <c r="C2">
-        <v>13619.76605946531</v>
+        <v>5420.973556981114</v>
       </c>
       <c r="D2">
-        <v>129473.597348124</v>
+        <v>51533.40699737061</v>
       </c>
       <c r="E2">
-        <v>3.883680263100505</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>1.545792190417682</v>
+      </c>
+      <c r="F2">
+        <v>3.199197785607728</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>3878680.416742722</v>
       </c>
@@ -1455,16 +1647,19 @@
         <v>35262.06742565849</v>
       </c>
       <c r="C3">
-        <v>14342.77448103218</v>
+        <v>6068.53490549152</v>
       </c>
       <c r="D3">
-        <v>136346.7331159881</v>
+        <v>57689.32017012125</v>
       </c>
       <c r="E3">
-        <v>3.866668719962097</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>1.63601638763085</v>
+      </c>
+      <c r="F3">
+        <v>3.270619944194959</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>4090334.97256683</v>
       </c>
@@ -1472,16 +1667,19 @@
         <v>37186.27267500078</v>
       </c>
       <c r="C4">
-        <v>15043.22103467147</v>
+        <v>6745.009895750702</v>
       </c>
       <c r="D4">
-        <v>143005.3889734981</v>
+        <v>64120.09512781769</v>
       </c>
       <c r="E4">
-        <v>3.845649985502213</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>1.724294760279207</v>
+      </c>
+      <c r="F4">
+        <v>3.408698826716651</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4301989.528390937</v>
       </c>
@@ -1489,16 +1687,19 @@
         <v>39110.47792434307</v>
       </c>
       <c r="C5">
-        <v>15721.23925446304</v>
+        <v>7448.469349572885</v>
       </c>
       <c r="D5">
-        <v>149450.8343358269</v>
+        <v>70807.39252171142</v>
       </c>
       <c r="E5">
-        <v>3.821247969020753</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>1.810445596156717</v>
+      </c>
+      <c r="F5">
+        <v>3.537088604077776</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4513644.084215046</v>
       </c>
@@ -1506,16 +1707,19 @@
         <v>41034.68317368537</v>
       </c>
       <c r="C6">
-        <v>16377.0994062613</v>
+        <v>8176.920030573635</v>
       </c>
       <c r="D6">
-        <v>155685.6384315694</v>
+        <v>77732.26404652823</v>
       </c>
       <c r="E6">
-        <v>3.794001229949964</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>1.894306426529843</v>
+      </c>
+      <c r="F6">
+        <v>3.655517645073399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>4725298.640039154</v>
       </c>
@@ -1523,16 +1727,19 @@
         <v>42958.88842302767</v>
       </c>
       <c r="C7">
-        <v>17011.1784274774</v>
+        <v>8928.322796831786</v>
       </c>
       <c r="D7">
-        <v>161713.384541259</v>
+        <v>84875.32500513869</v>
       </c>
       <c r="E7">
-        <v>3.764375440742881</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>1.975733733362667</v>
+      </c>
+      <c r="F7">
+        <v>3.763802226996099</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>4936953.195863263</v>
       </c>
@@ -1540,16 +1747,19 @@
         <v>44883.09367236996</v>
       </c>
       <c r="C8">
-        <v>17623.93520041449</v>
+        <v>9700.61003598983</v>
       </c>
       <c r="D8">
-        <v>167538.4349382485</v>
+        <v>92216.92005187244</v>
       </c>
       <c r="E8">
-        <v>3.732773773599863</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>2.054602579871654</v>
+      </c>
+      <c r="F8">
+        <v>3.861842588313349</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>5148607.75168737</v>
       </c>
@@ -1557,16 +1767,19 @@
         <v>46807.29892171224</v>
       </c>
       <c r="C9">
-        <v>18215.89024473419</v>
+        <v>10491.70221993179</v>
       </c>
       <c r="D9">
-        <v>173165.7378391803</v>
+        <v>99737.280566271</v>
       </c>
       <c r="E9">
-        <v>3.69954562276301</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>2.130806153396867</v>
+      </c>
+      <c r="F9">
+        <v>3.949618227489297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>5360262.307511479</v>
       </c>
@@ -1574,16 +1787,19 @@
         <v>48731.50417105455</v>
       </c>
       <c r="C10">
-        <v>18787.60907601094</v>
+        <v>11299.52343671813</v>
       </c>
       <c r="D10">
-        <v>178600.6692053929</v>
+        <v>107416.6723043383</v>
       </c>
       <c r="E10">
-        <v>3.664993975529239</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>2.20425521706226</v>
+      </c>
+      <c r="F10">
+        <v>4.02718255811842</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>5571916.863335587</v>
       </c>
@@ -1591,16 +1807,19 @@
         <v>50655.70942039684</v>
       </c>
       <c r="C11">
-        <v>19339.68860769894</v>
+        <v>12122.0157815157</v>
       </c>
       <c r="D11">
-        <v>183848.9034759247</v>
+        <v>115235.5322030534</v>
       </c>
       <c r="E11">
-        <v>3.629381674435633</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>2.274877472284557</v>
+      </c>
+      <c r="F11">
+        <v>4.094657044101082</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>5783571.419159696</v>
       </c>
@@ -1608,16 +1827,19 @@
         <v>52579.91466973913</v>
       </c>
       <c r="C12">
-        <v>19872.74608013415</v>
+        <v>12957.15251429142</v>
       </c>
       <c r="D12">
-        <v>188916.3083232731</v>
+        <v>123174.5934613697</v>
       </c>
       <c r="E12">
-        <v>3.592936761306662</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>2.342616838293564</v>
+      </c>
+      <c r="F12">
+        <v>4.152224945116812</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>5995225.974983804</v>
       </c>
@@ -1625,16 +1847,19 @@
         <v>54504.11991908143</v>
       </c>
       <c r="C13">
-        <v>20387.41008746068</v>
+        <v>13802.94991873886</v>
       </c>
       <c r="D13">
-        <v>193808.8593526543</v>
+        <v>131214.998274741</v>
       </c>
       <c r="E13">
-        <v>3.555857055216911</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>2.407432657743066</v>
+      </c>
+      <c r="F13">
+        <v>4.200124803289835</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>6206880.530807912</v>
       </c>
@@ -1642,16 +1867,19 @@
         <v>56428.32516842373</v>
       </c>
       <c r="C14">
-        <v>20884.31334537701</v>
+        <v>14657.47782319614</v>
       </c>
       <c r="D14">
-        <v>198532.5713500214</v>
+        <v>139338.3978501359</v>
       </c>
       <c r="E14">
-        <v>3.518314087073359</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>2.469298839443619</v>
+      </c>
+      <c r="F14">
+        <v>4.238643797762805</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>6418535.08663202</v>
       </c>
@@ -1659,16 +1887,19 @@
         <v>58352.53041776601</v>
       </c>
       <c r="C15">
-        <v>21364.08690223187</v>
+        <v>15518.8687693223</v>
       </c>
       <c r="D15">
-        <v>203093.4432509989</v>
+        <v>147527.0395662357</v>
       </c>
       <c r="E15">
-        <v>3.480456490866505</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>2.528202950412577</v>
+      </c>
+      <c r="F15">
+        <v>4.268111085903049</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>6630189.642456128</v>
       </c>
@@ -1676,16 +1907,19 @@
         <v>60276.73566710831</v>
       </c>
       <c r="C16">
-        <v>21827.35554551972</v>
+        <v>16385.32583735357</v>
       </c>
       <c r="D16">
-        <v>207497.4144736455</v>
+        <v>155763.8413626772</v>
       </c>
       <c r="E16">
-        <v>3.442412933898679</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>2.584145269958176</v>
+      </c>
+      <c r="F16">
+        <v>4.288891239008601</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>6841844.198280236</v>
       </c>
@@ -1693,16 +1927,19 @@
         <v>62200.9409164506</v>
       </c>
       <c r="C17">
-        <v>22274.73419703012</v>
+        <v>17255.1291573741</v>
       </c>
       <c r="D17">
-        <v>211750.3306496578</v>
+        <v>164032.4536381527</v>
       </c>
       <c r="E17">
-        <v>3.404294654225321</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>2.637137818517633</v>
+      </c>
+      <c r="F17">
+        <v>4.301377867529855</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>7053498.754104344</v>
       </c>
@@ -1710,16 +1947,19 @@
         <v>64125.14616579289</v>
       </c>
       <c r="C18">
-        <v>22706.82512423839</v>
+        <v>18126.64115388773</v>
       </c>
       <c r="D18">
-        <v>215857.9171150113</v>
+        <v>172317.3091068886</v>
       </c>
       <c r="E18">
-        <v>3.366197662254363</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>2.687203373562212</v>
+      </c>
+      <c r="F18">
+        <v>4.305987516765077</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>7265153.309928453</v>
       </c>
@@ -1727,16 +1967,19 @@
         <v>66049.35141513518</v>
       </c>
       <c r="C19">
-        <v>23124.21582416393</v>
+        <v>18998.31058589943</v>
       </c>
       <c r="D19">
-        <v>219825.7587932797</v>
+        <v>180603.6612048762</v>
       </c>
       <c r="E19">
-        <v>3.328204654298948</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>2.734374484160202</v>
+      </c>
+      <c r="F19">
+        <v>4.303153899417362</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>7476807.865752561</v>
       </c>
@@ -1744,16 +1987,19 @@
         <v>67973.5566644775</v>
       </c>
       <c r="C20">
-        <v>23527.47745982853</v>
+        <v>19868.67545666853</v>
       </c>
       <c r="D20">
-        <v>223659.2853321367</v>
+        <v>188877.6117508619</v>
       </c>
       <c r="E20">
-        <v>3.290386678398123</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>2.77869249483554</v>
+      </c>
+      <c r="F20">
+        <v>4.293322516898286</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>7688462.421576669</v>
       </c>
@@ -1761,16 +2007,19 @@
         <v>69897.76191381979</v>
       </c>
       <c r="C21">
-        <v>23917.16374941538</v>
+        <v>20736.36487634688</v>
       </c>
       <c r="D21">
-        <v>227363.7605433675</v>
+        <v>197126.1286531466</v>
       </c>
       <c r="E21">
-        <v>3.252804586557362</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>2.820206588248027</v>
+      </c>
+      <c r="F21">
+        <v>4.276945707311247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>7900116.977400778</v>
       </c>
@@ -1778,16 +2027,19 @@
         <v>71821.96716316207</v>
       </c>
       <c r="C22">
-        <v>24293.81022491314</v>
+        <v>21600.09996702036</v>
       </c>
       <c r="D22">
-        <v>230944.2753553159</v>
+        <v>205337.0545131825</v>
       </c>
       <c r="E22">
-        <v>3.215510302449201</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>2.858972855013934</v>
+      </c>
+      <c r="F22">
+        <v>4.254478145015995</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>8111771.533224885</v>
       </c>
@@ -1795,16 +2047,19 @@
         <v>73746.17241250437</v>
       </c>
       <c r="C23">
-        <v>24657.93379097441</v>
+        <v>22458.69390344781</v>
       </c>
       <c r="D23">
-        <v>234405.7436192598</v>
+        <v>213499.1070128502</v>
       </c>
       <c r="E23">
-        <v>3.17854792935008</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>2.895053397736062</v>
+      </c>
+      <c r="F23">
+        <v>4.226372804831072</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>8323426.089048994</v>
       </c>
@@ -1812,16 +2067,19 @@
         <v>75670.37766184665</v>
       </c>
       <c r="C24">
-        <v>25010.03252637377</v>
+        <v>23311.05118430136</v>
       </c>
       <c r="D24">
-        <v>237752.9002220121</v>
+        <v>221601.8719866494</v>
       </c>
       <c r="E24">
-        <v>3.141954719513554</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>2.928515475063924</v>
+      </c>
+      <c r="F24">
+        <v>4.193077393454023</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>8535080.644873101</v>
       </c>
@@ -1829,16 +2087,19 @@
         <v>77594.58291118896</v>
       </c>
       <c r="C25">
-        <v>25350.58568019613</v>
+        <v>24156.16622824675</v>
       </c>
       <c r="D25">
-        <v>240990.3010496854</v>
+        <v>229635.7900756157</v>
       </c>
       <c r="E25">
-        <v>3.105761923168159</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>2.959430690392986</v>
+      </c>
+      <c r="F25">
+        <v>4.155031241664103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>8746735.20069721</v>
       </c>
@@ -1846,16 +2107,19 @@
         <v>79518.78816053126</v>
       </c>
       <c r="C26">
-        <v>25680.05382303169</v>
+        <v>24993.12138706237</v>
       </c>
       <c r="D26">
-        <v>244122.3244249974</v>
+        <v>237592.137839432</v>
       </c>
       <c r="E26">
-        <v>3.069995532781097</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>2.987874228663858</v>
+      </c>
+      <c r="F26">
+        <v>4.112662643340637</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>8958389.756521318</v>
       </c>
@@ -1863,16 +2127,19 @@
         <v>81442.99340987354</v>
       </c>
       <c r="C27">
-        <v>25998.87912026399</v>
+        <v>25821.08446448148</v>
       </c>
       <c r="D27">
-        <v>247153.1737052288</v>
+        <v>245463.0041697957</v>
       </c>
       <c r="E27">
-        <v>3.034676936067355</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>3.013924143657981</v>
+      </c>
+      <c r="F27">
+        <v>4.066386621258729</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>9170044.312345427</v>
       </c>
@@ -1880,16 +2147,19 @@
         <v>83367.19865921584</v>
       </c>
       <c r="C28">
-        <v>26307.48570022884</v>
+        <v>26639.30582484433</v>
       </c>
       <c r="D28">
-        <v>250086.8807820535</v>
+        <v>253241.2628043946</v>
       </c>
       <c r="E28">
-        <v>2.999823489383946</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>3.037660697219554</v>
+      </c>
+      <c r="F28">
+        <v>4.016603094931042</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>9381698.868169535</v>
       </c>
@@ -1897,16 +2167,19 @@
         <v>85291.40390855813</v>
       </c>
       <c r="C29">
-        <v>26606.28009477718</v>
+        <v>27447.11517023262</v>
       </c>
       <c r="D29">
-        <v>252927.3102696615</v>
+        <v>260920.5416893773</v>
       </c>
       <c r="E29">
-        <v>2.965449021578161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>3.059165750971964</v>
+      </c>
+      <c r="F29">
+        <v>3.963695422345011</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>9593353.423993643</v>
       </c>
@@ -1914,16 +2187,19 @@
         <v>87215.60915790043</v>
       </c>
       <c r="C30">
-        <v>26895.65173374738</v>
+        <v>28243.91805877701</v>
       </c>
       <c r="D30">
-        <v>255678.1642053616</v>
+        <v>268495.1898813352</v>
       </c>
       <c r="E30">
-        <v>2.931564277014523</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>3.078522210344656</v>
+      </c>
+      <c r="F30">
+        <v>3.908029285174749</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>9805007.979817752</v>
       </c>
@@ -1931,16 +2207,19 @@
         <v>89139.81440724272</v>
       </c>
       <c r="C31">
-        <v>27175.97347816871</v>
+        <v>29029.19223049489</v>
       </c>
       <c r="D31">
-        <v>258342.987118374</v>
+        <v>275960.2426196107</v>
       </c>
       <c r="E31">
-        <v>2.898177305352156</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>3.095813520082767</v>
+      </c>
+      <c r="F31">
+        <v>3.849951885779361</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>10016662.53564186</v>
       </c>
@@ -1948,16 +2227,19 @@
         <v>91064.01965658503</v>
       </c>
       <c r="C32">
-        <v>27447.60217978472</v>
+        <v>29802.48380052085</v>
       </c>
       <c r="D32">
-        <v>260925.171348828</v>
+        <v>283311.3851379991</v>
       </c>
       <c r="E32">
-        <v>2.865293804653175</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>3.111123209873729</v>
+      </c>
+      <c r="F32">
+        <v>3.789791423893853</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>10228317.09146597</v>
       </c>
@@ -1965,16 +2247,19 @@
         <v>92988.22490592733</v>
       </c>
       <c r="C33">
-        <v>27710.8792567932</v>
+        <v>30563.40337309462</v>
       </c>
       <c r="D33">
-        <v>263427.96252092</v>
+        <v>290544.9157231487</v>
       </c>
       <c r="E33">
-        <v>2.832917423549273</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>3.124534488286899</v>
+      </c>
+      <c r="F33">
+        <v>3.72785682123194</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>10439971.64729008</v>
       </c>
@@ -1982,16 +2267,19 @@
         <v>94912.43015526961</v>
       </c>
       <c r="C34">
-        <v>27966.13127762107</v>
+        <v>31311.62212330328</v>
       </c>
       <c r="D34">
-        <v>265854.4650924523</v>
+        <v>297657.7084664211</v>
       </c>
       <c r="E34">
-        <v>2.80105002745725</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>3.136129882877041</v>
+      </c>
+      <c r="F34">
+        <v>3.664437663112547</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>10651626.20311419</v>
       </c>
@@ -1999,16 +2287,19 @@
         <v>96836.63540461191</v>
       </c>
       <c r="C35">
-        <v>28213.67054615288</v>
+        <v>32046.86788743799</v>
       </c>
       <c r="D35">
-        <v>268207.6479181928</v>
+        <v>304647.1760976462</v>
       </c>
       <c r="E35">
-        <v>2.769691933198034</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>3.14599092404172</v>
+      </c>
+      <c r="F35">
+        <v>3.599804327569984</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>10863280.75893829</v>
       </c>
@@ -2016,16 +2307,19 @@
         <v>98760.8406539542</v>
       </c>
       <c r="C36">
-        <v>28453.79568316092</v>
+        <v>32768.92129700348</v>
       </c>
       <c r="D36">
-        <v>270490.3497771234</v>
+        <v>311511.2332338516</v>
       </c>
       <c r="E36">
-        <v>2.738842115822892</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>3.154197870037868</v>
+      </c>
+      <c r="F36">
+        <v>3.534208274095556</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>11074935.3147624</v>
       </c>
@@ -2033,16 +2327,19 @@
         <v>100685.0459032965</v>
       </c>
       <c r="C37">
-        <v>28686.79219978877</v>
+        <v>33477.6119859653</v>
       </c>
       <c r="D37">
-        <v>272705.2848241483</v>
+        <v>318248.2603242134</v>
       </c>
       <c r="E37">
-        <v>2.70849839097327</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>3.160829470444665</v>
+      </c>
+      <c r="F37">
+        <v>3.467882466082511</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>11286589.87058651</v>
       </c>
@@ -2050,16 +2347,19 @@
         <v>102609.2511526388</v>
       </c>
       <c r="C38">
-        <v>28912.93305985435</v>
+        <v>34172.81489577664</v>
       </c>
       <c r="D38">
-        <v>274855.0479355155</v>
+        <v>324857.0685245277</v>
       </c>
       <c r="E38">
-        <v>2.678657575686314</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>3.165962765299583</v>
+      </c>
+      <c r="F38">
+        <v>3.40104190312364</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>11498244.42641062</v>
       </c>
@@ -2067,16 +2367,19 @@
         <v>104533.4564019811</v>
       </c>
       <c r="C39">
-        <v>29132.47922849401</v>
+        <v>34854.4466981141</v>
       </c>
       <c r="D39">
-        <v>276942.1199243931</v>
+        <v>331336.8656906607</v>
       </c>
       <c r="E39">
-        <v>2.649315630198033</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>3.169672917123415</v>
+      </c>
+      <c r="F39">
+        <v>3.333884241461227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>11709898.98223473</v>
       </c>
@@ -2084,16 +2387,19 @@
         <v>106457.6616513234</v>
       </c>
       <c r="C40">
-        <v>29345.6802052929</v>
+        <v>35522.46235107963</v>
       </c>
       <c r="D40">
-        <v>278968.8726089667</v>
+        <v>337687.2236407662</v>
       </c>
       <c r="E40">
-        <v>2.620467782982709</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>3.172033073080076</v>
+      </c>
+      <c r="F40">
+        <v>3.266590483057519</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>11921553.53805883</v>
       </c>
@@ -2101,16 +2407,19 @@
         <v>108381.8669006656</v>
       </c>
       <c r="C41">
-        <v>29552.77454055861</v>
+        <v>36176.85180089092</v>
       </c>
       <c r="D41">
-        <v>280937.5737202928</v>
+        <v>343908.0468005623</v>
       </c>
       <c r="E41">
-        <v>2.592108640994145</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>3.173114254580626</v>
+      </c>
+      <c r="F41">
+        <v>3.199325715885806</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>12133208.09388294</v>
       </c>
@@ -2118,16 +2427,19 @@
         <v>110306.072150008</v>
       </c>
       <c r="C42">
-        <v>29753.99033381504</v>
+        <v>36817.63683777332</v>
       </c>
       <c r="D42">
-        <v>282850.3916411308</v>
+        <v>349999.5423144927</v>
       </c>
       <c r="E42">
-        <v>2.564232286836173</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>3.172985271731185</v>
+      </c>
+      <c r="F42">
+        <v>3.132239890102318</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>12344862.64970705</v>
       </c>
@@ -2135,16 +2447,19 @@
         <v>112230.2773993503</v>
       </c>
       <c r="C43">
-        <v>29949.54571393549</v>
+        <v>37444.86811186586</v>
       </c>
       <c r="D43">
-        <v>284709.3999702333</v>
+        <v>355962.1916780308</v>
       </c>
       <c r="E43">
-        <v>2.536832364381927</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>3.171712660135433</v>
+      </c>
+      <c r="F43">
+        <v>3.065468616720413</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>12556517.20553116</v>
       </c>
@@ -2152,16 +2467,19 @@
         <v>114154.4826486925</v>
       </c>
       <c r="C44">
-        <v>30139.64930061153</v>
+        <v>38058.62231243831</v>
       </c>
       <c r="D44">
-        <v>286516.5819092082</v>
+        <v>361796.7239224677</v>
       </c>
       <c r="E44">
-        <v>2.509902154179573</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>3.169360637688558</v>
+      </c>
+      <c r="F44">
+        <v>2.999133977244062</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>12768171.76135527</v>
       </c>
@@ -2169,16 +2487,19 @@
         <v>116078.6878980348</v>
       </c>
       <c r="C45">
-        <v>30324.50064707816</v>
+        <v>38658.99951155899</v>
       </c>
       <c r="D45">
-        <v>288273.8344711966</v>
+        <v>367504.0903630185</v>
       </c>
       <c r="E45">
-        <v>2.483434639823121</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>3.165991079136243</v>
+      </c>
+      <c r="F45">
+        <v>2.933345334421256</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>12979826.31717937</v>
       </c>
@@ -2186,16 +2507,19 @@
         <v>118002.8931473771</v>
       </c>
       <c r="C46">
-        <v>30504.29066419416</v>
+        <v>39246.12067152691</v>
       </c>
       <c r="D46">
-        <v>289982.9725123093</v>
+        <v>373085.4409037219</v>
       </c>
       <c r="E46">
-        <v>2.457422566327602</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>3.161663506315604</v>
+      </c>
+      <c r="F46">
+        <v>2.868200135840076</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>13191480.87300348</v>
       </c>
@@ -2203,16 +2527,19 @@
         <v>119927.0983967194</v>
       </c>
       <c r="C47">
-        <v>30679.20202611879</v>
+        <v>39820.12531385726</v>
       </c>
       <c r="D47">
-        <v>291645.7325881114</v>
+        <v>378542.101878114</v>
       </c>
       <c r="E47">
-        <v>2.431858491425732</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>3.156435092141518</v>
+      </c>
+      <c r="F47">
+        <v>2.803784703504481</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>13403135.42882759</v>
       </c>
@@ -2220,16 +2547,19 @@
         <v>121851.3036460617</v>
       </c>
       <c r="C48">
-        <v>30849.40955793625</v>
+        <v>40381.16934635544</v>
       </c>
       <c r="D48">
-        <v>293263.7766384963</v>
+        <v>383875.5553927398</v>
       </c>
       <c r="E48">
-        <v>2.406734830595919</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>3.150360676548632</v>
+      </c>
+      <c r="F48">
+        <v>2.740175003799537</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>13614789.9846517</v>
       </c>
@@ -2237,16 +2567,19 @@
         <v>123775.508895404</v>
       </c>
       <c r="C49">
-        <v>31015.08060566438</v>
+        <v>40929.42304380544</v>
       </c>
       <c r="D49">
-        <v>294838.6955051009</v>
+        <v>389087.4201309693</v>
       </c>
       <c r="E49">
-        <v>2.382043896537344</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>3.14349279274437</v>
+      </c>
+      <c r="F49">
+        <v>2.677437393389252</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>13826444.54047581</v>
       </c>
@@ -2254,16 +2587,19 @@
         <v>125699.7141447463</v>
       </c>
       <c r="C50">
-        <v>31176.37538914833</v>
+        <v>41465.06917700375</v>
       </c>
       <c r="D50">
-        <v>296372.0122860188</v>
+        <v>394179.4335670297</v>
       </c>
       <c r="E50">
-        <v>2.357777933724965</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>3.135881702269604</v>
+      </c>
+      <c r="F50">
+        <v>2.615629337588623</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>14038099.09629992</v>
       </c>
@@ -2271,16 +2607,19 @@
         <v>127623.9193940886</v>
       </c>
       <c r="C51">
-        <v>31333.44733838622</v>
+        <v>41988.30128426441</v>
       </c>
       <c r="D51">
-        <v>297865.1855330128</v>
+        <v>399153.4355344127</v>
       </c>
       <c r="E51">
-        <v>2.333929148604486</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>3.127575437499853</v>
+      </c>
+      <c r="F51">
+        <v>2.554800098626016</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>14249753.65212402</v>
       </c>
@@ -2288,16 +2627,19 @@
         <v>129548.1246434309</v>
       </c>
       <c r="C52">
-        <v>31486.44341386592</v>
+        <v>42499.32207908027</v>
       </c>
       <c r="D52">
-        <v>299319.6122967335</v>
+        <v>404011.3530886225</v>
       </c>
       <c r="E52">
-        <v>2.3104897359231</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>3.118619850350022</v>
+      </c>
+      <c r="F52">
+        <v>2.494991391968801</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>14461408.20794813</v>
       </c>
@@ -2305,16 +2647,19 @@
         <v>131472.3298927732</v>
       </c>
       <c r="C53">
-        <v>31635.50441151296</v>
+        <v>42998.34198732664</v>
       </c>
       <c r="D53">
-        <v>300736.6310256456</v>
+        <v>408755.1866013932</v>
       </c>
       <c r="E53">
-        <v>2.287451901635285</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>3.10905866606888</v>
+      </c>
+      <c r="F53">
+        <v>2.436238009535503</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>14673062.76377224</v>
       </c>
@@ -2322,16 +2667,19 @@
         <v>133396.5351421155</v>
       </c>
       <c r="C54">
-        <v>31780.76525286055</v>
+        <v>43485.57780721584</v>
       </c>
       <c r="D54">
-        <v>302117.5243244712</v>
+        <v>413386.9970218134</v>
       </c>
       <c r="E54">
-        <v>2.264807882773019</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>3.098933541125389</v>
+      </c>
+      <c r="F54">
+        <v>2.378568409168982</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>14884717.31959635</v>
       </c>
@@ -2339,16 +2687,19 @@
         <v>135320.7403914578</v>
       </c>
       <c r="C55">
-        <v>31922.35526105576</v>
+        <v>43961.2514851357</v>
       </c>
       <c r="D55">
-        <v>303463.5215779882</v>
+        <v>417908.8942390785</v>
       </c>
       <c r="E55">
-        <v>2.242549964625708</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>3.088284124297175</v>
+      </c>
+      <c r="F55">
+        <v>2.322005270210438</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>15096371.87542046</v>
       </c>
@@ -2356,16 +2707,19 @@
         <v>137244.9456408001</v>
       </c>
       <c r="C56">
-        <v>32060.39842331396</v>
+        <v>44425.58900051572</v>
       </c>
       <c r="D56">
-        <v>304775.8014460009</v>
+        <v>422323.0264816922</v>
       </c>
       <c r="E56">
-        <v>2.220670495536248</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>3.07714812017197</v>
+      </c>
+      <c r="F56">
+        <v>2.266566015398132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>15308026.43124457</v>
       </c>
@@ -2373,16 +2727,19 @@
         <v>139169.1508901424</v>
       </c>
       <c r="C57">
-        <v>32195.01364042524</v>
+        <v>44878.81935294432</v>
       </c>
       <c r="D57">
-        <v>306055.4942352235</v>
+        <v>426631.5706886984</v>
       </c>
       <c r="E57">
-        <v>2.19916189958519</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>3.065561354365621</v>
+      </c>
+      <c r="F57">
+        <v>2.212263299629484</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>15519680.98706867</v>
       </c>
@@ -2390,16 +2747,19 @@
         <v>141093.3561394847</v>
       </c>
       <c r="C58">
-        <v>32326.3149639058</v>
+        <v>45321.17364489933</v>
       </c>
       <c r="D58">
-        <v>307303.6841537121</v>
+        <v>430836.7237898409</v>
       </c>
       <c r="E58">
-        <v>2.178016687404559</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>3.05355783984553</v>
+      </c>
+      <c r="F58">
+        <v>2.159105466380492</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>15731335.54289278</v>
       </c>
@@ -2407,16 +2767,19 @@
         <v>143017.561388827</v>
       </c>
       <c r="C59">
-        <v>32454.41182137255</v>
+        <v>45752.88425363626</v>
       </c>
       <c r="D59">
-        <v>308521.4114533439</v>
+        <v>434940.6948332844</v>
       </c>
       <c r="E59">
-        <v>2.157227465335923</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>3.041169843826351</v>
+      </c>
+      <c r="F59">
+        <v>2.107096972773835</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>15942990.09871689</v>
       </c>
@@ -2424,16 +2787,19 @@
         <v>144941.7666381693</v>
       </c>
       <c r="C60">
-        <v>32579.40923070295</v>
+        <v>46174.18408599802</v>
       </c>
       <c r="D60">
-        <v>309709.6744656852</v>
+        <v>438945.6979016102</v>
       </c>
       <c r="E60">
-        <v>2.136786943123443</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>3.028427954775717</v>
+      </c>
+      <c r="F60">
+        <v>2.056238784440921</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>16154644.654541</v>
       </c>
@@ -2441,13 +2807,16 @@
         <v>146865.9718875116</v>
       </c>
       <c r="C61">
-        <v>32701.40800352383</v>
+        <v>46585.30591015414</v>
       </c>
       <c r="D61">
-        <v>310869.4315364169</v>
+        <v>442853.9457591292</v>
       </c>
       <c r="E61">
-        <v>2.116687940311455</v>
+        <v>3.015361149132098</v>
+      </c>
+      <c r="F61">
+        <v>2.03109718095557</v>
       </c>
     </row>
   </sheetData>
@@ -2457,10 +2826,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2476,8 +2845,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>2664160.128129908</v>
       </c>
@@ -2485,16 +2857,19 @@
         <v>20075.2102041675</v>
       </c>
       <c r="C2">
-        <v>5980.283494727851</v>
+        <v>1554.816007392002</v>
       </c>
       <c r="D2">
-        <v>56850.37568511827</v>
+        <v>14780.54915279455</v>
       </c>
       <c r="E2">
-        <v>2.831869510054567</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>0.7362587490977397</v>
+      </c>
+      <c r="F2">
+        <v>1.924961069615654</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2838386.199005636</v>
       </c>
@@ -2502,16 +2877,19 @@
         <v>21388.05358732089</v>
       </c>
       <c r="C3">
-        <v>6416.393822278665</v>
+        <v>1820.657828634074</v>
       </c>
       <c r="D3">
-        <v>60996.17178045071</v>
+        <v>17307.72155586732</v>
       </c>
       <c r="E3">
-        <v>2.851880444913885</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>0.8092237793030199</v>
+      </c>
+      <c r="F3">
+        <v>2.009142824086419</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3012612.269881365</v>
       </c>
@@ -2519,16 +2897,19 @@
         <v>22700.89697047428</v>
       </c>
       <c r="C4">
-        <v>6841.622786189674</v>
+        <v>2109.751061322436</v>
       </c>
       <c r="D4">
-        <v>65038.52635642463</v>
+        <v>20055.92887761848</v>
       </c>
       <c r="E4">
-        <v>2.865020110924093</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>0.8834861857531026</v>
+      </c>
+      <c r="F4">
+        <v>2.176929635148023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3186838.340757093</v>
       </c>
@@ -2536,16 +2917,19 @@
         <v>24013.74035362767</v>
       </c>
       <c r="C5">
-        <v>7255.238934368367</v>
+        <v>2421.936418687992</v>
       </c>
       <c r="D5">
-        <v>68970.48600919363</v>
+        <v>23023.65689005653</v>
       </c>
       <c r="E5">
-        <v>2.872125915976871</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>0.9587701270609612</v>
+      </c>
+      <c r="F5">
+        <v>2.343035475815619</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>3361064.411632822</v>
       </c>
@@ -2553,16 +2937,19 @@
         <v>25326.58373678106</v>
       </c>
       <c r="C6">
-        <v>7656.732817230187</v>
+        <v>2756.908895272789</v>
       </c>
       <c r="D6">
-        <v>72787.20775760131</v>
+        <v>26208.00611945486</v>
       </c>
       <c r="E6">
-        <v>2.873944962892669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>1.034802261206423</v>
+      </c>
+      <c r="F6">
+        <v>2.506423188857095</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>3535290.48250855</v>
       </c>
@@ -2570,16 +2957,19 @@
         <v>26639.42711993445</v>
       </c>
       <c r="C7">
-        <v>8045.780583421165</v>
+        <v>3114.222736418222</v>
       </c>
       <c r="D7">
-        <v>76485.61297315868</v>
+        <v>29604.73908780304</v>
       </c>
       <c r="E7">
-        <v>2.871143310582833</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>1.111312903033475</v>
+      </c>
+      <c r="F7">
+        <v>2.666096516194592</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>3709516.553384279</v>
       </c>
@@ -2587,16 +2977,19 @@
         <v>27952.27050308784</v>
       </c>
       <c r="C8">
-        <v>8422.21231643037</v>
+        <v>3493.297765322851</v>
       </c>
       <c r="D8">
-        <v>80064.08637834754</v>
+        <v>33208.34045972361</v>
       </c>
       <c r="E8">
-        <v>2.864314237711137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>1.188037317256755</v>
+      </c>
+      <c r="F8">
+        <v>2.821109756942894</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>3883742.624260007</v>
       </c>
@@ -2604,16 +2997,19 @@
         <v>29265.11388624123</v>
       </c>
       <c r="C9">
-        <v>8785.984666072236</v>
+        <v>3893.427020127941</v>
       </c>
       <c r="D9">
-        <v>83522.21587325026</v>
+        <v>37012.08964290693</v>
       </c>
       <c r="E9">
-        <v>2.853985677209943</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>1.264717088981085</v>
+      </c>
+      <c r="F9">
+        <v>2.970576929753685</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>4057968.695135736</v>
       </c>
@@ -2621,16 +3017,19 @@
         <v>30577.95726939462</v>
       </c>
       <c r="C10">
-        <v>9137.157332605479</v>
+        <v>4313.785611659483</v>
       </c>
       <c r="D10">
-        <v>86860.56898650315</v>
+        <v>41008.14499247408</v>
       </c>
       <c r="E10">
-        <v>2.840626933357698</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>1.341101520653867</v>
+      </c>
+      <c r="F10">
+        <v>3.113680157325005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>4232194.766011464</v>
       </c>
@@ -2638,16 +3037,19 @@
         <v>31890.80065254801</v>
       </c>
       <c r="C11">
-        <v>9475.872975777502</v>
+        <v>4753.440676356173</v>
       </c>
       <c r="D11">
-        <v>90080.50188462276</v>
+        <v>45187.63842650722</v>
       </c>
       <c r="E11">
-        <v>2.824654760664515</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>1.416949010431848</v>
+      </c>
+      <c r="F11">
+        <v>3.24967703426154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>4406420.836887193</v>
       </c>
@@ -2655,16 +3057,19 @@
         <v>33203.6440357014</v>
       </c>
       <c r="C12">
-        <v>9802.34014394219</v>
+        <v>5211.362269050394</v>
       </c>
       <c r="D12">
-        <v>93183.99709105927</v>
+        <v>49540.77897610568</v>
       </c>
       <c r="E12">
-        <v>2.806438865290372</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>1.492028372633985</v>
+      </c>
+      <c r="F12">
+        <v>3.37790678621527</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>4580646.907762921</v>
       </c>
@@ -2672,16 +3077,19 @@
         <v>34516.48741885479</v>
       </c>
       <c r="C13">
-        <v>10116.81884695816</v>
+        <v>5686.435017080914</v>
       </c>
       <c r="D13">
-        <v>96173.5263378229</v>
+        <v>54056.96357289053</v>
       </c>
       <c r="E13">
-        <v>2.786306879108668</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>1.566120066532658</v>
+      </c>
+      <c r="F13">
+        <v>3.497795077562317</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>4754872.978638649</v>
       </c>
@@ -2689,16 +3097,19 @@
         <v>35829.33080200817</v>
       </c>
       <c r="C14">
-        <v>10419.60842843939</v>
+        <v>6177.470340977668</v>
       </c>
       <c r="D14">
-        <v>99051.93527544652</v>
+        <v>58724.89322251403</v>
       </c>
       <c r="E14">
-        <v>2.764548850292644</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>1.639017305319657</v>
+      </c>
+      <c r="F14">
+        <v>3.608857375423682</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>4929099.049514377</v>
       </c>
@@ -2706,16 +3117,19 @@
         <v>37142.17418516156</v>
       </c>
       <c r="C15">
-        <v>10711.03742613817</v>
+        <v>6683.219037733414</v>
       </c>
       <c r="D15">
-        <v>101822.3470827327</v>
+        <v>63532.69262502906</v>
       </c>
       <c r="E15">
-        <v>2.741421290394226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>1.710527022685996</v>
+      </c>
+      <c r="F15">
+        <v>3.710700827981413</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>5103325.120390106</v>
       </c>
@@ -2723,16 +3137,19 @@
         <v>38455.01756831495</v>
       </c>
       <c r="C16">
-        <v>10991.45514229609</v>
+        <v>7202.384020288601</v>
       </c>
       <c r="D16">
-        <v>104488.0823319722</v>
+        <v>68468.03128026842</v>
       </c>
       <c r="E16">
-        <v>2.717150815140057</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>1.780470680025972</v>
+      </c>
+      <c r="F16">
+        <v>3.803024663064524</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>5277551.191265834</v>
       </c>
@@ -2740,16 +3157,19 @@
         <v>39767.86095146834</v>
       </c>
       <c r="C17">
-        <v>11261.22467763657</v>
+        <v>7733.633010894392</v>
       </c>
       <c r="D17">
-        <v>107052.5927679785</v>
+        <v>73518.24415477589</v>
       </c>
       <c r="E17">
-        <v>2.691937413948985</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>1.848684902728252</v>
+      </c>
+      <c r="F17">
+        <v>3.885619157254692</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>5451777.262141563</v>
       </c>
@@ -2757,16 +3177,19 @@
         <v>41080.70433462173</v>
       </c>
       <c r="C18">
-        <v>11520.71721258634</v>
+        <v>8275.61099585951</v>
       </c>
       <c r="D18">
-        <v>109519.4069436583</v>
+        <v>78670.45008038018</v>
       </c>
       <c r="E18">
-        <v>2.665957381148361</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>1.915021939243598</v>
+      </c>
+      <c r="F18">
+        <v>3.958363264878376</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>5626003.333017292</v>
       </c>
@@ -2774,16 +3197,19 @@
         <v>42393.54771777512</v>
       </c>
       <c r="C19">
-        <v>11770.30734688677</v>
+        <v>8826.952264029303</v>
       </c>
       <c r="D19">
-        <v>111892.0859169523</v>
+        <v>83911.66619560192</v>
       </c>
       <c r="E19">
-        <v>2.639365939879508</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>1.979349941510527</v>
+      </c>
+      <c r="F19">
+        <v>4.021221029102788</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>5800229.40389302</v>
       </c>
@@ -2791,16 +3217,19 @@
         <v>43706.39110092851</v>
       </c>
       <c r="C20">
-        <v>12010.36933378615</v>
+        <v>9386.291870259789</v>
       </c>
       <c r="D20">
-        <v>114174.1874519343</v>
+        <v>89228.91692088988</v>
       </c>
       <c r="E20">
-        <v>2.612299587679953</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>2.041553069775058</v>
+      </c>
+      <c r="F20">
+        <v>4.074236923192797</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>5974455.474768749</v>
       </c>
@@ -2808,16 +3237,19 @@
         <v>45019.2344840819</v>
       </c>
       <c r="C21">
-        <v>12241.27406744856</v>
+        <v>9952.276387129132</v>
       </c>
       <c r="D21">
-        <v>116369.2373802115</v>
+        <v>94609.33616762771</v>
       </c>
       <c r="E21">
-        <v>2.584878190706638</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>2.10153142877363</v>
+      </c>
+      <c r="F21">
+        <v>4.117530288450366</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>6148681.545644477</v>
       </c>
@@ -2825,16 +3257,19 @@
         <v>46332.07786723529</v>
       </c>
       <c r="C22">
-        <v>12463.38670213683</v>
+        <v>10523.57383214341</v>
       </c>
       <c r="D22">
-        <v>118480.706968162</v>
+        <v>100040.2617091414</v>
       </c>
       <c r="E22">
-        <v>2.557206851539635</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>2.159200845595724</v>
+      </c>
+      <c r="F22">
+        <v>4.151289046456101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>6322907.616520206</v>
       </c>
@@ -2842,16 +3277,19 @@
         <v>47644.92125038867</v>
       </c>
       <c r="C23">
-        <v>12677.06479926384</v>
+        <v>11098.88268273853</v>
       </c>
       <c r="D23">
-        <v>120511.9953022453</v>
+        <v>105509.3208800218</v>
       </c>
       <c r="E23">
-        <v>2.529377573507106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>2.214492502265623</v>
+      </c>
+      <c r="F23">
+        <v>4.175762867307474</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>6497133.687395934</v>
       </c>
@@ -2859,16 +3297,19 @@
         <v>48957.76463354206</v>
       </c>
       <c r="C24">
-        <v>12882.65691373243</v>
+        <v>11676.93991652005</v>
       </c>
       <c r="D24">
-        <v>122466.4158503248</v>
+        <v>111004.5070090658</v>
       </c>
       <c r="E24">
-        <v>2.501470742526923</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>2.267352438166961</v>
+      </c>
+      <c r="F24">
+        <v>4.191255973226672</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>6671359.758271663</v>
       </c>
@@ -2876,16 +3317,19 @@
         <v>50270.60801669546</v>
       </c>
       <c r="C25">
-        <v>13080.50154430097</v>
+        <v>12256.52803858644</v>
       </c>
       <c r="D25">
-        <v>124347.1864835265</v>
+        <v>116514.2462231273</v>
       </c>
       <c r="E25">
-        <v>2.473556445592012</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>2.317740938888814</v>
+      </c>
+      <c r="F25">
+        <v>4.1981197490316</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>6845585.829147391</v>
       </c>
@@ -2893,16 +3337,19 @@
         <v>51583.45139984885</v>
       </c>
       <c r="C26">
-        <v>13270.9263842215</v>
+        <v>12836.48108074495</v>
       </c>
       <c r="D26">
-        <v>126157.4223525793</v>
+        <v>122027.4544774692</v>
       </c>
       <c r="E26">
-        <v>2.445695643253312</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>2.365631828928508</v>
+      </c>
+      <c r="F26">
+        <v>4.196745318512543</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>7019811.90002312</v>
       </c>
@@ -2910,16 +3357,19 @@
         <v>52896.29478300223</v>
       </c>
       <c r="C27">
-        <v>13454.24781830312</v>
+        <v>13415.68957839387</v>
       </c>
       <c r="D27">
-        <v>127900.1311067483</v>
+        <v>127533.5848675056</v>
       </c>
       <c r="E27">
-        <v>2.417941211788769</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>2.411011685992181</v>
+      </c>
+      <c r="F27">
+        <v>4.187556229787675</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>7194037.970898848</v>
       </c>
@@ -2927,16 +3377,19 @@
         <v>54209.13816615562</v>
       </c>
       <c r="C28">
-        <v>13630.77062104533</v>
+        <v>13993.10454939787</v>
       </c>
       <c r="D28">
-        <v>129578.2100241997</v>
+        <v>133022.6654531882</v>
       </c>
       <c r="E28">
-        <v>2.390338869196396</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>2.45387899445039</v>
+      </c>
+      <c r="F28">
+        <v>4.171001374286108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>7368264.041774577</v>
       </c>
@@ -2944,16 +3397,19 @@
         <v>55521.98154930901</v>
       </c>
       <c r="C29">
-        <v>13800.78781774194</v>
+        <v>14567.74051515884</v>
       </c>
       <c r="D29">
-        <v>131194.4446916119</v>
+        <v>138485.327978216</v>
       </c>
       <c r="E29">
-        <v>2.362927997717413</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>2.494243254903058</v>
+      </c>
+      <c r="F29">
+        <v>4.147548244144125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>7542490.112650305</v>
       </c>
@@ -2961,16 +3417,19 @@
         <v>56834.8249324624</v>
       </c>
       <c r="C30">
-        <v>13964.58067663757</v>
+        <v>15138.67761715116</v>
       </c>
       <c r="D30">
-        <v>132751.5089296143</v>
+        <v>143912.8279904564</v>
       </c>
       <c r="E30">
-        <v>2.335742374281344</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>2.532124065860499</v>
+      </c>
+      <c r="F30">
+        <v>4.117676612420775</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>7716716.183526034</v>
       </c>
@@ -2978,16 +3437,19 @@
         <v>58147.66831561578</v>
       </c>
       <c r="C31">
-        <v>14122.4188054709</v>
+        <v>15705.06289243724</v>
       </c>
       <c r="D31">
-        <v>134251.9657105548</v>
+        <v>149297.0569673801</v>
       </c>
       <c r="E31">
-        <v>2.308810819065997</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>2.567550192331372</v>
+      </c>
+      <c r="F31">
+        <v>4.081872700443356</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>7890942.254401762</v>
       </c>
@@ -2995,16 +3457,19 @@
         <v>59460.51169876917</v>
       </c>
       <c r="C32">
-        <v>14274.56033018992</v>
+        <v>16266.11077919513</v>
       </c>
       <c r="D32">
-        <v>135698.268857422</v>
+        <v>154630.5471217594</v>
       </c>
       <c r="E32">
-        <v>2.282157771276478</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>2.600558634697391</v>
+      </c>
+      <c r="F32">
+        <v>4.040623877443352</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>8065168.325277491</v>
       </c>
@@ -3012,16 +3477,19 @@
         <v>60773.35508192256</v>
       </c>
       <c r="C33">
-        <v>14421.2521373899</v>
+        <v>16821.10292824764</v>
       </c>
       <c r="D33">
-        <v>137092.7653485331</v>
+        <v>159906.4696100063</v>
       </c>
       <c r="E33">
-        <v>2.255803800262992</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>2.631193709717889</v>
+      </c>
+      <c r="F33">
+        <v>3.994413919951355</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>8239394.396153219</v>
       </c>
@@ -3029,16 +3497,19 @@
         <v>62086.19846507596</v>
       </c>
       <c r="C34">
-        <v>14562.73016520182</v>
+        <v>17369.38739921173</v>
       </c>
       <c r="D34">
-        <v>138437.6980828069</v>
+        <v>165118.6268905273</v>
       </c>
       <c r="E34">
-        <v>2.229766059210073</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>2.659506153906459</v>
+      </c>
+      <c r="F34">
+        <v>3.943718842548631</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>8413620.467028948</v>
       </c>
@@ -3046,16 +3517,19 @@
         <v>63399.04184822935</v>
       </c>
       <c r="C35">
-        <v>14699.21973003561</v>
+        <v>17910.37732046082</v>
       </c>
       <c r="D35">
-        <v>139735.2089858837</v>
+        <v>170261.439984921</v>
       </c>
       <c r="E35">
-        <v>2.204058687833093</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>2.685552257911232</v>
+      </c>
+      <c r="F35">
+        <v>3.889003297757927</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>8587846.537904676</v>
       </c>
@@ -3063,16 +3537,19 @@
         <v>64711.88523138273</v>
       </c>
       <c r="C36">
-        <v>14830.93587883279</v>
+        <v>18443.54909090643</v>
       </c>
       <c r="D36">
-        <v>140987.3423587444</v>
+        <v>175329.9313835737</v>
       </c>
       <c r="E36">
-        <v>2.178693169803853</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>2.709393038955161</v>
+      </c>
+      <c r="F36">
+        <v>3.830717531204471</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>8762072.608780405</v>
       </c>
@@ -3080,16 +3557,19 @@
         <v>66024.72861453613</v>
       </c>
       <c r="C37">
-        <v>14958.08375837092</v>
+        <v>18968.44019896118</v>
       </c>
       <c r="D37">
-        <v>142196.0483884304</v>
+        <v>180319.704312064</v>
       </c>
       <c r="E37">
-        <v>2.153678649988789</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>2.731093456889491</v>
+      </c>
+      <c r="F37">
+        <v>3.769294868694986</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>8936298.679656133</v>
       </c>
@@ -3097,16 +3577,19 @@
         <v>67337.57199768951</v>
       </c>
       <c r="C38">
-        <v>15080.8589947442</v>
+        <v>19484.64673023931</v>
       </c>
       <c r="D38">
-        <v>143363.1867555</v>
+        <v>185226.9190386141</v>
       </c>
       <c r="E38">
-        <v>2.129022216013655</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>2.750721678010155</v>
+      </c>
+      <c r="F38">
+        <v>3.705149704475157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>9110524.750531862</v>
       </c>
@@ -3114,16 +3597,19 @@
         <v>68650.41538084291</v>
       </c>
       <c r="C39">
-        <v>15199.44807746574</v>
+        <v>19991.82063086661</v>
       </c>
       <c r="D39">
-        <v>144490.5302854207</v>
+        <v>190048.2668582899</v>
       </c>
       <c r="E39">
-        <v>2.104729148161006</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>2.768348389503312</v>
+      </c>
+      <c r="F39">
+        <v>3.638675954495886</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>9284750.82140759</v>
       </c>
@@ -3131,16 +3617,19 @@
         <v>69963.25876399629</v>
       </c>
       <c r="C40">
-        <v>15314.02874374016</v>
+        <v>20489.66678796553</v>
       </c>
       <c r="D40">
-        <v>145579.7686015799</v>
+        <v>194780.9423392127</v>
       </c>
       <c r="E40">
-        <v>2.080803141155233</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>2.784046166235022</v>
+      </c>
+      <c r="F40">
+        <v>3.570245934857153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>9458976.892283319</v>
       </c>
@@ -3148,16 +3637,19 @@
         <v>71276.10214714968</v>
       </c>
       <c r="C41">
-        <v>15424.77035937244</v>
+        <v>20977.93998318581</v>
       </c>
       <c r="D41">
-        <v>146632.5117463191</v>
+        <v>199422.6143619048</v>
       </c>
       <c r="E41">
-        <v>2.057246500988451</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>2.797888890587709</v>
+      </c>
+      <c r="F41">
+        <v>3.500209623503493</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>9633202.963159047</v>
       </c>
@@ -3165,16 +3657,19 @@
         <v>72588.94553030307</v>
       </c>
       <c r="C42">
-        <v>15531.83429354095</v>
+        <v>21456.4417692663</v>
       </c>
       <c r="D42">
-        <v>147650.2937436396</v>
+        <v>203971.3964269454</v>
       </c>
       <c r="E42">
-        <v>2.034060319584079</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>2.809951225173746</v>
+      </c>
+      <c r="F42">
+        <v>3.428894262487472</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>9807429.034034776</v>
       </c>
@@ -3182,16 +3677,19 @@
         <v>73901.78891345646</v>
       </c>
       <c r="C43">
-        <v>15635.37428529357</v>
+        <v>21925.01731370882</v>
       </c>
       <c r="D43">
-        <v>148634.5760832242</v>
+        <v>208425.8166499834</v>
       </c>
       <c r="E43">
-        <v>2.011244629778644</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>2.82030813752104</v>
+      </c>
+      <c r="F43">
+        <v>3.356604258472387</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>9981655.104910504</v>
       </c>
@@ -3199,16 +3697,19 @@
         <v>75214.63229660985</v>
       </c>
       <c r="C44">
-        <v>15735.53680014605</v>
+        <v>22383.55224785833</v>
       </c>
       <c r="D44">
-        <v>149586.7511103697</v>
+        <v>212784.7878081454</v>
       </c>
       <c r="E44">
-        <v>1.988798542821727</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>2.829034475220538</v>
+      </c>
+      <c r="F44">
+        <v>3.283621340400762</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>10155881.17578623</v>
       </c>
@@ -3216,16 +3717,19 @@
         <v>76527.47567976324</v>
       </c>
       <c r="C45">
-        <v>15832.46137559086</v>
+        <v>22831.96955412558</v>
       </c>
       <c r="D45">
-        <v>150508.1453104968</v>
+        <v>217047.5777490363</v>
       </c>
       <c r="E45">
-        <v>1.966720370345324</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>2.836204589542365</v>
+      </c>
+      <c r="F45">
+        <v>3.210204935201793</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>10330107.24666196</v>
       </c>
@@ -3233,16 +3737,19 @@
         <v>77840.31906291662</v>
       </c>
       <c r="C46">
-        <v>15926.28095467509</v>
+        <v>23270.22651883954</v>
       </c>
       <c r="D46">
-        <v>151400.022480243</v>
+        <v>221213.7804236374</v>
       </c>
       <c r="E46">
-        <v>1.945007732533441</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>2.841892005155261</v>
+      </c>
+      <c r="F46">
+        <v>3.136592724869784</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>10504333.31753769</v>
       </c>
@@ -3250,16 +3757,19 @@
         <v>79153.16244607003</v>
       </c>
       <c r="C47">
-        <v>16017.12220709268</v>
+        <v>23698.31177333784</v>
       </c>
       <c r="D47">
-        <v>152263.5867798618</v>
+        <v>225283.287758021</v>
       </c>
       <c r="E47">
-        <v>1.923657654027464</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>2.846169133311822</v>
+      </c>
+      <c r="F47">
+        <v>3.063001351055465</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>10678559.38841342</v>
       </c>
@@ -3267,16 +3777,19 @@
         <v>80466.0058292234</v>
       </c>
       <c r="C48">
-        <v>16105.10583746821</v>
+        <v>24116.24244143074</v>
       </c>
       <c r="D48">
-        <v>153099.985663861</v>
+        <v>229256.2625362835</v>
       </c>
       <c r="E48">
-        <v>1.902666648929884</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>2.849107025677953</v>
+      </c>
+      <c r="F48">
+        <v>2.989627236327975</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>10852785.45928915</v>
       </c>
@@ -3284,16 +3797,19 @@
         <v>81778.84921237681</v>
       </c>
       <c r="C49">
-        <v>16190.34688069663</v>
+        <v>24524.06140732812</v>
       </c>
       <c r="D49">
-        <v>153910.3126885915</v>
+        <v>233133.1124286377</v>
       </c>
       <c r="E49">
-        <v>1.882030796115653</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>2.850775165876926</v>
+      </c>
+      <c r="F49">
+        <v>2.916647494380125</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>11027011.53016488</v>
       </c>
@@ -3301,16 +3817,19 @@
         <v>83091.69259553018</v>
       </c>
       <c r="C50">
-        <v>16272.95498435284</v>
+        <v>24921.83471450663</v>
       </c>
       <c r="D50">
-        <v>154695.6101969171</v>
+        <v>236914.4652642593</v>
       </c>
       <c r="E50">
-        <v>1.861745805924752</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>2.851241295775503</v>
+      </c>
+      <c r="F50">
+        <v>2.844220904559633</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>11201237.6010406</v>
       </c>
@@ -3318,16 +3837,19 @@
         <v>84404.53597868356</v>
       </c>
       <c r="C51">
-        <v>16353.03467830319</v>
+        <v>25309.64910280694</v>
       </c>
       <c r="D51">
-        <v>155456.8718812235</v>
+        <v>240601.1456181929</v>
       </c>
       <c r="E51">
-        <v>1.841807079189255</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>2.850571273550475</v>
+      </c>
+      <c r="F51">
+        <v>2.77248892914429</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>11375463.67191633</v>
       </c>
@@ -3335,16 +3857,19 @@
         <v>85717.37936183697</v>
       </c>
       <c r="C52">
-        <v>16430.68563174387</v>
+        <v>25687.60968827726</v>
       </c>
       <c r="D52">
-        <v>156195.0452269023</v>
+        <v>244194.1527552455</v>
       </c>
       <c r="E52">
-        <v>1.822209759441658</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>2.848828960629254</v>
+      </c>
+      <c r="F52">
+        <v>2.701576754683835</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>11549689.74279206</v>
       </c>
@@ -3352,16 +3877,19 @@
         <v>87030.22274499034</v>
       </c>
       <c r="C53">
-        <v>16506.00289796175</v>
+        <v>26055.83778789427</v>
       </c>
       <c r="D53">
-        <v>156911.0338391206</v>
+        <v>247694.6399511283</v>
       </c>
       <c r="E53">
-        <v>1.802948779056787</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>2.84607613468835</v>
+      </c>
+      <c r="F53">
+        <v>2.631594341458679</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>11723915.81366779</v>
       </c>
@@ -3369,16 +3897,19 @@
         <v>88343.06612814374</v>
       </c>
       <c r="C54">
-        <v>16579.07714716702</v>
+        <v>26414.46888927231</v>
       </c>
       <c r="D54">
-        <v>157605.6996561993</v>
+        <v>251103.8951919013</v>
       </c>
       <c r="E54">
-        <v>1.784018899995937</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>2.842372426010991</v>
+      </c>
+      <c r="F54">
+        <v>2.562637467636612</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>11898141.88454352</v>
       </c>
@@ -3386,16 +3917,19 @@
         <v>89655.90951129713</v>
       </c>
       <c r="C55">
-        <v>16649.99488778603</v>
+        <v>26763.65076378548</v>
       </c>
       <c r="D55">
-        <v>158279.8650532887</v>
+        <v>254423.3232367437</v>
       </c>
       <c r="E55">
-        <v>1.765414749747696</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>2.837775274642492</v>
+      </c>
+      <c r="F55">
+        <v>2.494788757017665</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>12072367.95541925</v>
       </c>
@@ -3403,16 +3937,19 @@
         <v>90968.75289445052</v>
       </c>
       <c r="C56">
-        <v>16718.83867662972</v>
+        <v>27103.54172014493</v>
       </c>
       <c r="D56">
-        <v>158934.3148402932</v>
+        <v>257654.4290159335</v>
       </c>
       <c r="E56">
-        <v>1.747130852994126</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>2.832339905933255</v>
+      </c>
+      <c r="F56">
+        <v>2.428118681344674</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>12246594.02629497</v>
       </c>
@@ -3420,16 +3957,19 @@
         <v>92281.59627760391</v>
       </c>
       <c r="C57">
-        <v>16785.6873183707</v>
+        <v>27434.30899436408</v>
       </c>
       <c r="D57">
-        <v>159569.7981581601</v>
+        <v>260798.8023253726</v>
       </c>
       <c r="E57">
-        <v>1.729161659472579</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>2.826119322219252</v>
+      </c>
+      <c r="F57">
+        <v>2.362686530019737</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>12420820.0971707</v>
       </c>
@@ -3437,16 +3977,19 @@
         <v>93594.4396607573</v>
       </c>
       <c r="C58">
-        <v>16850.61605477174</v>
+        <v>27756.12727117633</v>
       </c>
       <c r="D58">
-        <v>160187.0302777433</v>
+        <v>263858.1037707377</v>
       </c>
       <c r="E58">
-        <v>1.711501568451691</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>2.819164308554211</v>
+      </c>
+      <c r="F58">
+        <v>2.298541341709127</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>12595046.16804643</v>
       </c>
@@ -3454,16 +3997,19 @@
         <v>94907.28304391068</v>
       </c>
       <c r="C59">
-        <v>16913.69674411196</v>
+        <v>28069.17733131404</v>
       </c>
       <c r="D59">
-        <v>160786.6943054821</v>
+        <v>266834.0519081073</v>
       </c>
       <c r="E59">
-        <v>1.694144950194086</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>2.811523450572823</v>
+      </c>
+      <c r="F59">
+        <v>2.235722793754943</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>12769272.23892216</v>
       </c>
@@ -3471,16 +4017,19 @@
         <v>96220.12642706408</v>
       </c>
       <c r="C60">
-        <v>16974.99803125547</v>
+        <v>28373.64481858616</v>
       </c>
       <c r="D60">
-        <v>161369.4428001248</v>
+        <v>269728.4115234304</v>
       </c>
       <c r="E60">
-        <v>1.677086164737526</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>2.803243162727369</v>
+      </c>
+      <c r="F60">
+        <v>2.174262046550118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>12943498.30979789</v>
       </c>
@@ -3488,13 +4037,16 @@
         <v>97532.96981021746</v>
       </c>
       <c r="C61">
-        <v>17034.58550880147</v>
+        <v>28669.71912037766</v>
       </c>
       <c r="D61">
-        <v>161935.8993046709</v>
+        <v>272542.982990217</v>
       </c>
       <c r="E61">
-        <v>1.660319578289994</v>
+        <v>2.794367725298832</v>
+      </c>
+      <c r="F61">
+        <v>2.143874511540111</v>
       </c>
     </row>
   </sheetData>
@@ -3504,10 +4056,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3523,8 +4075,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>3012631.922031096</v>
       </c>
@@ -3532,16 +4087,19 @@
         <v>30287.18702759737</v>
       </c>
       <c r="C2">
-        <v>8411.010447165374</v>
+        <v>3061.683650620165</v>
       </c>
       <c r="D2">
-        <v>79957.59803600523</v>
+        <v>29105.28671762604</v>
       </c>
       <c r="E2">
-        <v>2.639980991405663</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>0.9609768873915432</v>
+      </c>
+      <c r="F2">
+        <v>2.091869939539614</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>3211575.904954182</v>
       </c>
@@ -3549,16 +4107,19 @@
         <v>32287.2500206046</v>
       </c>
       <c r="C3">
-        <v>8951.418645110525</v>
+        <v>3501.799274915058</v>
       </c>
       <c r="D3">
-        <v>85094.88109350312</v>
+        <v>33289.1583698835</v>
       </c>
       <c r="E3">
-        <v>2.635556792207405</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>1.031031083435087</v>
+      </c>
+      <c r="F3">
+        <v>2.15003904337075</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3410519.887877267</v>
       </c>
@@ -3566,16 +4127,19 @@
         <v>34287.31301361182</v>
       </c>
       <c r="C4">
-        <v>9472.600200125549</v>
+        <v>3966.391690011721</v>
       </c>
       <c r="D4">
-        <v>90049.3898937764</v>
+        <v>37705.71376595904</v>
       </c>
       <c r="E4">
-        <v>2.626318074502584</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>1.099698706369617</v>
+      </c>
+      <c r="F4">
+        <v>2.262107679736299</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3609463.870800353</v>
       </c>
@@ -3583,16 +4147,19 @@
         <v>36287.37600661905</v>
       </c>
       <c r="C5">
-        <v>9974.447240806192</v>
+        <v>4453.664316685793</v>
       </c>
       <c r="D5">
-        <v>94820.09897877401</v>
+        <v>42337.87408275953</v>
       </c>
       <c r="E5">
-        <v>2.61303266903284</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>1.166738374112166</v>
+      </c>
+      <c r="F5">
+        <v>2.365393728567169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>3808407.853723438</v>
       </c>
@@ -3600,16 +4167,19 @@
         <v>38287.43899962628</v>
       </c>
       <c r="C6">
-        <v>10457.06207961074</v>
+        <v>4961.718137296184</v>
       </c>
       <c r="D6">
-        <v>99407.98096153277</v>
+        <v>47167.58668675621</v>
       </c>
       <c r="E6">
-        <v>2.596360152542537</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>1.231933707742025</v>
+      </c>
+      <c r="F6">
+        <v>2.459474127500929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>4007351.836646524</v>
       </c>
@@ -3617,16 +4187,19 @@
         <v>40287.50199263351</v>
       </c>
       <c r="C7">
-        <v>10920.7093983449</v>
+        <v>5488.578553562715</v>
       </c>
       <c r="D7">
-        <v>103815.5519869987</v>
+        <v>52176.08045210623</v>
       </c>
       <c r="E7">
-        <v>2.576867436605556</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>1.295093462524594</v>
+      </c>
+      <c r="F7">
+        <v>2.544051629487719</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>4206295.81956961</v>
       </c>
@@ -3634,16 +4207,19 @@
         <v>42287.56498564074</v>
       </c>
       <c r="C8">
-        <v>11365.77723421343</v>
+        <v>6032.221470210703</v>
       </c>
       <c r="D8">
-        <v>108046.5008536862</v>
+        <v>57344.11371963246</v>
       </c>
       <c r="E8">
-        <v>2.555041911029275</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>1.356051447727112</v>
+      </c>
+      <c r="F8">
+        <v>2.618950121579768</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>4405239.802492695</v>
       </c>
@@ -3651,16 +4227,19 @@
         <v>44287.62797864796</v>
       </c>
       <c r="C9">
-        <v>11792.74528854747</v>
+        <v>6590.598182957016</v>
       </c>
       <c r="D9">
-        <v>112105.3877468967</v>
+        <v>62652.21088951318</v>
       </c>
       <c r="E9">
-        <v>2.5313025976678</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>1.414666211514403</v>
+      </c>
+      <c r="F9">
+        <v>2.684108061368568</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>4604183.785415781</v>
       </c>
@@ -3668,16 +4247,19 @@
         <v>46287.6909716552</v>
       </c>
       <c r="C10">
-        <v>12202.15930964021</v>
+        <v>7161.658700294107</v>
       </c>
       <c r="D10">
-        <v>115997.4007142412</v>
+        <v>68080.88412518376</v>
       </c>
       <c r="E10">
-        <v>2.506009660003857</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>1.470820485879796</v>
+      </c>
+      <c r="F10">
+        <v>2.739570302759328</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>4803127.768338867</v>
       </c>
@@ -3685,16 +4267,19 @@
         <v>48287.75396466242</v>
       </c>
       <c r="C11">
-        <v>12594.61049783993</v>
+        <v>7743.373191869883</v>
       </c>
       <c r="D11">
-        <v>119728.1598842529</v>
+        <v>73610.83724809426</v>
       </c>
       <c r="E11">
-        <v>2.479472538148522</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>1.524420400707881</v>
+      </c>
+      <c r="F11">
+        <v>2.785478629022353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>5002071.751261951</v>
       </c>
@@ -3702,16 +4287,19 @@
         <v>50287.81695766964</v>
       </c>
       <c r="C12">
-        <v>12970.71904977733</v>
+        <v>8333.751326704767</v>
       </c>
       <c r="D12">
-        <v>123303.5610328568</v>
+        <v>79223.14957262395</v>
       </c>
       <c r="E12">
-        <v>2.451956925007284</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>1.57539448648787</v>
+      </c>
+      <c r="F12">
+        <v>2.822061333841242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>5201015.734185038</v>
       </c>
@@ -3719,16 +4307,19 @@
         <v>52287.87995067688</v>
       </c>
       <c r="C13">
-        <v>13331.12110288271</v>
+        <v>8930.859337414253</v>
       </c>
       <c r="D13">
-        <v>126729.6514740192</v>
+        <v>84899.43812371926</v>
       </c>
       <c r="E13">
-        <v>2.423690759571113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>1.623692492482098</v>
+      </c>
+      <c r="F13">
+        <v>2.849622193604552</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>5399959.717108123</v>
       </c>
@@ -3736,16 +4327,19 @@
         <v>54287.9429436841</v>
       </c>
       <c r="C14">
-        <v>13676.458464188</v>
+        <v>9532.834718111853</v>
       </c>
       <c r="D14">
-        <v>130012.5324186469</v>
+        <v>90621.99735958506</v>
       </c>
       <c r="E14">
-        <v>2.394869382940446</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>1.669284051775406</v>
+      </c>
+      <c r="F14">
+        <v>2.868529159983445</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>5598903.700031209</v>
       </c>
@@ -3753,16 +4347,19 @@
         <v>56288.00593669133</v>
       </c>
       <c r="C15">
-        <v>14007.37061150062</v>
+        <v>10137.89853061769</v>
       </c>
       <c r="D15">
-        <v>133158.2829353367</v>
+        <v>96373.91615820923</v>
       </c>
       <c r="E15">
-        <v>2.365659978879044</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>1.71215722700505</v>
+      </c>
+      <c r="F15">
+        <v>2.879203074602914</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>5797847.682954295</v>
       </c>
@@ -3770,16 +4367,19 @@
         <v>58288.06892969856</v>
       </c>
       <c r="C16">
-        <v>14324.48854283355</v>
+        <v>10744.36535364412</v>
       </c>
       <c r="D16">
-        <v>136172.9014812063</v>
+        <v>102139.1723973169</v>
       </c>
       <c r="E16">
-        <v>2.336205401579608</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>1.75231697108558</v>
+      </c>
+      <c r="F16">
+        <v>2.882106671038374</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>5996791.665877379</v>
       </c>
@@ -3787,16 +4387,19 @@
         <v>60288.13192270578</v>
       </c>
       <c r="C17">
-        <v>14628.43012371021</v>
+        <v>11350.65096118964</v>
       </c>
       <c r="D17">
-        <v>139062.2616719732</v>
+        <v>107902.7059474954</v>
       </c>
       <c r="E17">
-        <v>2.306627477697636</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>1.789783536266065</v>
+      </c>
+      <c r="F17">
+        <v>2.877734086951566</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>6195735.648800466</v>
       </c>
@@ -3804,16 +4407,19 @@
         <v>62288.19491571302</v>
       </c>
       <c r="C18">
-        <v>14919.79664364248</v>
+        <v>11955.27785856985</v>
       </c>
       <c r="D18">
-        <v>141832.0795467977</v>
+        <v>113650.4712993715</v>
       </c>
       <c r="E18">
-        <v>2.277029856760525</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>1.824590862733472</v>
+      </c>
+      <c r="F18">
+        <v>2.866601064061821</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>6394679.631723551</v>
       </c>
@@ -3821,16 +4427,19 @@
         <v>64288.25790872025</v>
       </c>
       <c r="C19">
-        <v>15199.17034449599</v>
+        <v>12556.87883708869</v>
       </c>
       <c r="D19">
-        <v>144487.8900721792</v>
+        <v>119369.4713553858</v>
       </c>
       <c r="E19">
-        <v>2.247500473217527</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>1.856784975024097</v>
+      </c>
+      <c r="F19">
+        <v>2.849235968507659</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>6593623.614646637</v>
       </c>
@@ -3838,16 +4447,19 @@
         <v>66288.32090172748</v>
       </c>
       <c r="C20">
-        <v>15467.1127261831</v>
+        <v>13154.19873155605</v>
       </c>
       <c r="D20">
-        <v>147035.0310353637</v>
+        <v>125047.774137286</v>
       </c>
       <c r="E20">
-        <v>2.218113674252563</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>1.886422411010674</v>
+      </c>
+      <c r="F20">
+        <v>2.826171721134485</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>6792567.597569723</v>
       </c>
@@ -3855,16 +4467,19 @@
         <v>68288.3838947347</v>
       </c>
       <c r="C21">
-        <v>15724.16347053138</v>
+        <v>13746.09457933069</v>
       </c>
       <c r="D21">
-        <v>149478.6328143132</v>
+        <v>130674.5142980351</v>
       </c>
       <c r="E21">
-        <v>2.188932059729687</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>1.913568704444192</v>
+      </c>
+      <c r="F21">
+        <v>2.797938687941175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>6991511.580492808</v>
       </c>
@@ -3872,16 +4487,19 @@
         <v>70288.44688774191</v>
       </c>
       <c r="C22">
-        <v>15970.83985344614</v>
+        <v>14331.53438623167</v>
       </c>
       <c r="D22">
-        <v>151823.6127895456</v>
+        <v>136239.8813901946</v>
       </c>
       <c r="E22">
-        <v>2.160008074044146</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>1.938296938155201</v>
+      </c>
+      <c r="F22">
+        <v>2.765058546406209</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>7190455.563415894</v>
       </c>
@@ -3889,16 +4507,19 @@
         <v>72288.50988074916</v>
       </c>
       <c r="C23">
-        <v>16207.63653963048</v>
+        <v>14909.59470461222</v>
       </c>
       <c r="D23">
-        <v>154074.6733926824</v>
+        <v>141735.0968423659</v>
       </c>
       <c r="E23">
-        <v>2.131385384023711</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>1.960686381226829</v>
+      </c>
+      <c r="F23">
+        <v>2.728039114288039</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>7389399.546338979</v>
       </c>
@@ -3906,16 +4527,19 @@
         <v>74288.57287375638</v>
       </c>
       <c r="C24">
-        <v>16435.02567400383</v>
+        <v>15479.45722329869</v>
       </c>
       <c r="D24">
-        <v>156236.3029754999</v>
+        <v>147152.3815421221</v>
       </c>
       <c r="E24">
-        <v>2.103100072214376</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>1.980821219869012</v>
+      </c>
+      <c r="F24">
+        <v>2.687370103953426</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>7588343.529262066</v>
       </c>
@@ -3923,16 +4547,19 @@
         <v>76288.63586676362</v>
       </c>
       <c r="C25">
-        <v>16653.45720029408</v>
+        <v>16040.40455914189</v>
       </c>
       <c r="D25">
-        <v>158312.7788385626</v>
+        <v>152484.9158292284</v>
       </c>
       <c r="E25">
-        <v>2.075181670767482</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>1.998789388442334</v>
+      </c>
+      <c r="F25">
+        <v>2.643519747208111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>7787287.512185151</v>
       </c>
@@ -3940,16 +4567,19 @@
         <v>78288.69885977084</v>
       </c>
       <c r="C26">
-        <v>16863.35935067921</v>
+        <v>16591.81542672928</v>
       </c>
       <c r="D26">
-        <v>160308.1718859037</v>
+        <v>157726.7935774717</v>
       </c>
       <c r="E26">
-        <v>2.047654057618769</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>2.014681504159224</v>
+      </c>
+      <c r="F26">
+        <v>2.596932222622883</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>7986231.495108236</v>
       </c>
@@ -3957,16 +4587,19 @@
         <v>80288.76185277806</v>
       </c>
       <c r="C27">
-        <v>17065.13926132967</v>
+        <v>17133.15934738913</v>
       </c>
       <c r="D27">
-        <v>162226.3524765565</v>
+        <v>162872.9718968604</v>
       </c>
       <c r="E27">
-        <v>2.020536233626616</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>2.028589906461796</v>
+      </c>
+      <c r="F27">
+        <v>2.548025808941346</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>8185175.478031322</v>
       </c>
@@ -3974,16 +4607,19 @@
         <v>82288.8248457853</v>
       </c>
       <c r="C28">
-        <v>17259.18367767804</v>
+        <v>17663.99104188108</v>
       </c>
       <c r="D28">
-        <v>164070.9971290599</v>
+        <v>167919.2178288535</v>
       </c>
       <c r="E28">
-        <v>1.993842996743967</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>2.040607799947869</v>
+      </c>
+      <c r="F28">
+        <v>2.497191683703464</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>8384119.460954407</v>
       </c>
@@ -3991,16 +4627,19 @@
         <v>84288.88783879252</v>
       </c>
       <c r="C29">
-        <v>17445.8597205695</v>
+        <v>18183.94463387692</v>
       </c>
       <c r="D29">
-        <v>165845.5958047158</v>
+        <v>172862.0532429019</v>
       </c>
       <c r="E29">
-        <v>1.967585527073335</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>2.050828497980786</v>
+      </c>
+      <c r="F29">
+        <v>2.444793285062347</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>8583063.443877494</v>
       </c>
@@ -4008,16 +4647,19 @@
         <v>86288.95083179977</v>
       </c>
       <c r="C30">
-        <v>17625.51569041907</v>
+        <v>18692.72777411213</v>
       </c>
       <c r="D30">
-        <v>167553.4595521496</v>
+        <v>177698.698978865</v>
       </c>
       <c r="E30">
-        <v>1.941771894744162</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>2.059344762752386</v>
+      </c>
+      <c r="F30">
+        <v>2.391166156258612</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>8782007.426800579</v>
       </c>
@@ -4025,16 +4667,19 @@
         <v>88289.01382480699</v>
       </c>
       <c r="C31">
-        <v>17798.48189136002</v>
+        <v>19190.11577842349</v>
       </c>
       <c r="D31">
-        <v>169197.7283419134</v>
+        <v>182427.0191214303</v>
       </c>
       <c r="E31">
-        <v>1.916407500911208</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>2.066248236540761</v>
+      </c>
+      <c r="F31">
+        <v>2.336618195729196</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>8980951.409723664</v>
       </c>
@@ -4042,16 +4687,19 @@
         <v>90289.0768178142</v>
       </c>
       <c r="C32">
-        <v>17965.07146131274</v>
+        <v>19675.94585714313</v>
       </c>
       <c r="D32">
-        <v>170781.3789573706</v>
+        <v>187045.4661429955</v>
       </c>
       <c r="E32">
-        <v>1.891495460762926</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>2.071628958178595</v>
+      </c>
+      <c r="F32">
+        <v>2.281430240807185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33">
         <v>9179895.39264675</v>
       </c>
@@ -4059,16 +4707,19 @@
         <v>92289.13981082145</v>
       </c>
       <c r="C33">
-        <v>18125.58119709966</v>
+        <v>20150.11149874929</v>
       </c>
       <c r="D33">
-        <v>172307.2328384868</v>
+        <v>191553.0275129623</v>
       </c>
       <c r="E33">
-        <v>1.867036936216874</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>2.075574958284546</v>
+      </c>
+      <c r="F33">
+        <v>2.225856918931735</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34">
         <v>9378839.375569835</v>
       </c>
@@ -4076,16 +4727,19 @@
         <v>94289.20280382867</v>
       </c>
       <c r="C34">
-        <v>18280.29236631437</v>
+        <v>20612.55705743826</v>
       </c>
       <c r="D34">
-        <v>173777.963799702</v>
+        <v>195949.1742455645</v>
       </c>
       <c r="E34">
-        <v>1.843031424936872</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>2.078171926569814</v>
+      </c>
+      <c r="F34">
+        <v>2.170127706815625</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35">
         <v>9577783.358492922</v>
       </c>
@@ -4093,16 +4747,19 @@
         <v>96289.2657968359</v>
       </c>
       <c r="C35">
-        <v>18429.47149973451</v>
+        <v>21063.27258245892</v>
       </c>
       <c r="D35">
-        <v>175196.1055628462</v>
+        <v>200233.8117459654</v>
       </c>
       <c r="E35">
-        <v>1.819477011409544</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>2.079502944476135</v>
+      </c>
+      <c r="F35">
+        <v>2.1144481447821</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36">
         <v>9776727.341416007</v>
       </c>
@@ -4110,16 +4767,19 @@
         <v>98289.32878984312</v>
       </c>
       <c r="C36">
-        <v>18573.37115973908</v>
+        <v>21502.28891666155</v>
       </c>
       <c r="D36">
-        <v>176564.0590619457</v>
+        <v>204407.2332155874</v>
       </c>
       <c r="E36">
-        <v>1.796370585045558</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>2.079648276494387</v>
+      </c>
+      <c r="F36">
+        <v>2.059001160214964</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37">
         <v>9975671.324339092</v>
       </c>
@@ -4127,16 +4787,19 @@
         <v>100289.3917828503</v>
       </c>
       <c r="C37">
-        <v>18712.23068152768</v>
+        <v>21929.67308272267</v>
       </c>
       <c r="D37">
-        <v>177884.0994894769</v>
+        <v>208470.0757921752</v>
       </c>
       <c r="E37">
-        <v>1.773708029605334</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>2.078685213721916</v>
+      </c>
+      <c r="F37">
+        <v>2.003948460565351</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38">
         <v>10174615.30726218</v>
       </c>
@@ -4144,16 +4807,19 @@
         <v>102289.4547758576</v>
       </c>
       <c r="C38">
-        <v>18846.27688500344</v>
+        <v>22345.52396785275</v>
       </c>
       <c r="D38">
-        <v>179158.3830637386</v>
+        <v>212423.2795273285</v>
       </c>
       <c r="E38">
-        <v>1.751484387675353</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>2.076687963512978</v>
+      </c>
+      <c r="F38">
+        <v>1.949431962485592</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39">
         <v>10373559.29018526</v>
       </c>
@@ -4161,16 +4827,19 @@
         <v>104289.5177688648</v>
       </c>
       <c r="C39">
-        <v>18975.7247560229</v>
+        <v>22749.96831138166</v>
       </c>
       <c r="D39">
-        <v>180388.95350502</v>
+        <v>216268.049243281</v>
       </c>
       <c r="E39">
-        <v>1.729694003426242</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>2.073727579435092</v>
+      </c>
+      <c r="F39">
+        <v>1.895575229316954</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40">
         <v>10572503.27310835</v>
       </c>
@@ -4178,16 +4847,19 @@
         <v>106289.580761872</v>
       </c>
       <c r="C40">
-        <v>19100.77809637863</v>
+        <v>23143.15699434232</v>
       </c>
       <c r="D40">
-        <v>181577.74821453</v>
+        <v>220005.8192605646</v>
       </c>
       <c r="E40">
-        <v>1.708330646456601</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>2.069871926143532</v>
+      </c>
+      <c r="F40">
+        <v>1.842484894287753</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41">
         <v>10771447.25603143</v>
       </c>
@@ -4195,16 +4867,19 @@
         <v>108289.6437548793</v>
       </c>
       <c r="C41">
-        <v>19221.63014239488</v>
+        <v>23525.26162591902</v>
       </c>
       <c r="D41">
-        <v>182726.6041549542</v>
+        <v>223638.2209477605</v>
       </c>
       <c r="E41">
-        <v>1.687387619157451</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>2.065185674208887</v>
+      </c>
+      <c r="F41">
+        <v>1.790252051357895</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42">
         <v>10970391.23895452</v>
       </c>
@@ -4212,16 +4887,19 @@
         <v>110289.7067478865</v>
       </c>
       <c r="C42">
-        <v>19338.46415241404</v>
+        <v>23896.47141828016</v>
       </c>
       <c r="D42">
-        <v>183837.2634352783</v>
+        <v>227167.053012717</v>
       </c>
       <c r="E42">
-        <v>1.666857849713171</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>2.059730320364373</v>
+      </c>
+      <c r="F42">
+        <v>1.738953599674941</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43">
         <v>11169335.22187761</v>
       </c>
@@ -4229,16 +4907,19 @@
         <v>112289.7697408937</v>
       </c>
       <c r="C43">
-        <v>19451.45396375252</v>
+        <v>24256.99033875595</v>
       </c>
       <c r="D43">
-        <v>184911.3786053779</v>
+        <v>230594.2544302937</v>
       </c>
       <c r="E43">
-        <v>1.646733972578775</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>2.053564229068997</v>
+      </c>
+      <c r="F43">
+        <v>1.688653531099135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44">
         <v>11368279.20480069</v>
       </c>
@@ -4246,16 +4927,19 @@
         <v>114289.8327339009</v>
       </c>
       <c r="C44">
-        <v>19560.76451992908</v>
+        <v>24607.03452644456</v>
       </c>
       <c r="D44">
-        <v>185950.5176680101</v>
+        <v>233921.8798838417</v>
       </c>
       <c r="E44">
-        <v>1.627008398034456</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>2.046742691701002</v>
+      </c>
+      <c r="F44">
+        <v>1.639404153246367</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45">
         <v>11567223.18772378</v>
       </c>
@@ -4263,16 +4947,19 @@
         <v>116289.8957269082</v>
       </c>
       <c r="C45">
-        <v>19666.55236913084</v>
+        <v>24946.82995903029</v>
       </c>
       <c r="D45">
-        <v>186956.1688173816</v>
+        <v>237152.0775852744</v>
       </c>
       <c r="E45">
-        <v>1.607673372211324</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>2.039318000096892</v>
+      </c>
+      <c r="F45">
+        <v>1.591247243020474</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46">
         <v>11766167.17064686</v>
       </c>
@@ -4280,16 +4967,19 @@
         <v>118289.9587199154</v>
       </c>
       <c r="C46">
-        <v>19768.96613499554</v>
+        <v>25276.61035478082</v>
       </c>
       <c r="D46">
-        <v>187929.7449145464</v>
+        <v>240287.0693308217</v>
       </c>
       <c r="E46">
-        <v>1.588721028802814</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>2.031339531530049</v>
+      </c>
+      <c r="F46">
+        <v>1.544215127705821</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47">
         <v>11965111.15356995</v>
       </c>
@@ -4297,16 +4987,19 @@
         <v>120290.0217129226</v>
       </c>
       <c r="C47">
-        <v>19868.14696086196</v>
+        <v>25596.61529427483</v>
       </c>
       <c r="D47">
-        <v>188872.5877105839</v>
+        <v>243329.1326456071</v>
       </c>
       <c r="E47">
-        <v>1.570143433520501</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>2.022853842576592</v>
+      </c>
+      <c r="F47">
+        <v>1.498331692412895</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48">
         <v>12164055.13649303</v>
       </c>
@@ -4314,16 +5007,19 @@
         <v>122290.0847059299</v>
       </c>
       <c r="C48">
-        <v>19964.22892868374</v>
+        <v>25907.08854631911</v>
       </c>
       <c r="D48">
-        <v>189785.9718289203</v>
+        <v>246280.5848693116</v>
       </c>
       <c r="E48">
-        <v>1.551932622217879</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>2.013904769642942</v>
+      </c>
+      <c r="F48">
+        <v>1.453613314054601</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49">
         <v>12362999.11941612</v>
       </c>
@@ -4331,16 +5027,19 @@
         <v>124290.1476989371</v>
       </c>
       <c r="C49">
-        <v>20057.33945381984</v>
+        <v>26208.27658268104</v>
       </c>
       <c r="D49">
-        <v>190671.1085183251</v>
+        <v>249143.7690367735</v>
       </c>
       <c r="E49">
-        <v>1.534080633488182</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>2.00453353422883</v>
+      </c>
+      <c r="F49">
+        <v>1.410069723127158</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50">
         <v>12561943.10233921</v>
       </c>
@@ -4348,16 +5047,19 @@
         <v>126290.2106919443</v>
       </c>
       <c r="C50">
-        <v>20147.5996569149</v>
+        <v>26500.42726663173</v>
       </c>
       <c r="D50">
-        <v>191529.1491881183</v>
+        <v>251921.0414108848</v>
       </c>
       <c r="E50">
-        <v>1.516579536440154</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>1.994778851271281</v>
+      </c>
+      <c r="F50">
+        <v>1.367704795413331</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51">
         <v>12760887.08526229</v>
       </c>
@@ -4365,16 +5067,19 @@
         <v>128290.2736849515</v>
       </c>
       <c r="C51">
-        <v>20235.12471406756</v>
+        <v>26783.78870081677</v>
       </c>
       <c r="D51">
-        <v>192361.1887369752</v>
+        <v>254614.760530103</v>
       </c>
       <c r="E51">
-        <v>1.499421454266795</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>1.984677039160213</v>
+      </c>
+      <c r="F51">
+        <v>1.326517276356851</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52">
         <v>12959831.06818538</v>
       </c>
@@ -4382,16 +5087,19 @@
         <v>130290.3366779588</v>
       </c>
       <c r="C52">
-        <v>20320.02418645937</v>
+        <v>27058.60822060657</v>
       </c>
       <c r="D52">
-        <v>193168.2686864789</v>
+        <v>257227.2776389369</v>
       </c>
       <c r="E52">
-        <v>1.482598584144708</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>1.974262130235573</v>
+      </c>
+      <c r="F52">
+        <v>1.286501441309512</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53">
         <v>13158775.05110846</v>
       </c>
@@ -4399,16 +5107,19 @@
         <v>132290.399670966</v>
       </c>
       <c r="C53">
-        <v>20402.40233058273</v>
+        <v>27325.13151979034</v>
       </c>
       <c r="D53">
-        <v>193951.3801302399</v>
+        <v>259760.9283765302</v>
       </c>
       <c r="E53">
-        <v>1.466103213934176</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>1.963565980771169</v>
+      </c>
+      <c r="F53">
+        <v>1.247647695154908</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54">
         <v>13357719.03403155</v>
       </c>
@@ -4416,16 +5127,19 @@
         <v>134290.4626639732</v>
       </c>
       <c r="C54">
-        <v>20482.358390167</v>
+        <v>27583.60189624018</v>
       </c>
       <c r="D54">
-        <v>194711.4665090336</v>
+        <v>262218.0256057171</v>
       </c>
       <c r="E54">
-        <v>1.449927736091342</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>1.952618379622752</v>
+      </c>
+      <c r="F54">
+        <v>1.209943114994367</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55">
         <v>13556663.01695463</v>
       </c>
@@ -4433,16 +5147,19 @@
         <v>136290.5256569805</v>
       </c>
       <c r="C55">
-        <v>20559.986870858</v>
+        <v>27834.25960596021</v>
       </c>
       <c r="D55">
-        <v>195449.4262219868</v>
+        <v>264600.8532724185</v>
       </c>
       <c r="E55">
-        <v>1.434064659152456</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>1.941447154869538</v>
+      </c>
+      <c r="F55">
+        <v>1.173371939663482</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56">
         <v>13755606.99987772</v>
       </c>
@@ -4450,16 +5167,19 @@
         <v>138290.5886499877</v>
       </c>
       <c r="C56">
-        <v>20635.37779866038</v>
+        <v>28077.34131473267</v>
       </c>
       <c r="D56">
-        <v>196166.1150834084</v>
+        <v>266911.6611928252</v>
       </c>
       <c r="E56">
-        <v>1.4185066171054</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>1.9300782779107</v>
+      </c>
+      <c r="F56">
+        <v>1.137916009850715</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57">
         <v>13954550.9828008</v>
       </c>
@@ -4467,16 +5187,19 @@
         <v>140290.6516429949</v>
       </c>
       <c r="C57">
-        <v>20708.61696310471</v>
+        <v>28313.07963736314</v>
       </c>
       <c r="D57">
-        <v>196862.3486344089</v>
+        <v>269152.6606733242</v>
       </c>
       <c r="E57">
-        <v>1.403246376924494</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>1.91853596459336</v>
+      </c>
+      <c r="F57">
+        <v>1.103555162533511</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58">
         <v>14153494.96572389</v>
       </c>
@@ -4484,16 +5207,19 @@
         <v>142290.7146360021</v>
       </c>
       <c r="C58">
-        <v>20779.78614605312</v>
+        <v>28541.70275530022</v>
       </c>
       <c r="D58">
-        <v>197538.904317996</v>
+        <v>271326.0208754759</v>
       </c>
       <c r="E58">
-        <v>1.38827684451038</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>1.906842773047859</v>
+      </c>
+      <c r="F58">
+        <v>1.070267583342525</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59">
         <v>14352438.94864698</v>
       </c>
@@ -4501,16 +5227,19 @@
         <v>144290.7776290094</v>
       </c>
       <c r="C59">
-        <v>20848.96333701007</v>
+        <v>28763.43410415093</v>
       </c>
       <c r="D59">
-        <v>198196.5235258832</v>
+        <v>273433.8658454415</v>
       </c>
       <c r="E59">
-        <v>1.3735910692468</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>1.895019697991206</v>
+      </c>
+      <c r="F59">
+        <v>1.038030120326147</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60">
         <v>14551382.93157006</v>
       </c>
@@ -4518,16 +5247,19 @@
         <v>146290.8406220166</v>
       </c>
       <c r="C60">
-        <v>20916.22293575742</v>
+        <v>28978.49212332832</v>
       </c>
       <c r="D60">
-        <v>198835.9135248002</v>
+        <v>275478.2721340582</v>
       </c>
       <c r="E60">
-        <v>1.359182247359891</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>1.883086261332202</v>
+      </c>
+      <c r="F60">
+        <v>1.006818562424545</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61">
         <v>14750326.91449315</v>
       </c>
@@ -4535,13 +5267,16 @@
         <v>148290.9036150238</v>
       </c>
       <c r="C61">
-        <v>20981.63594308747</v>
+        <v>29187.09006074514</v>
       </c>
       <c r="D61">
-        <v>199457.7492696583</v>
+        <v>277461.2669401977</v>
       </c>
       <c r="E61">
-        <v>1.345043724242642</v>
+        <v>1.87106059897316</v>
+      </c>
+      <c r="F61">
+        <v>0.9914661753517496</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/response_curves.xlsx
+++ b/outputs/response_curves.xlsx
@@ -397,16 +397,16 @@
         <v>69063.60521282686</v>
       </c>
       <c r="C2">
-        <v>10047.61751458828</v>
+        <v>10054.00330671036</v>
       </c>
       <c r="D2">
-        <v>95515.67763439489</v>
+        <v>95576.38289719849</v>
       </c>
       <c r="E2">
-        <v>1.383010303908305</v>
+        <v>1.383889280072618</v>
       </c>
       <c r="F2">
-        <v>2.629196656444142</v>
+        <v>2.630867649918145</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -417,16 +417,16 @@
         <v>73100.70547741983</v>
       </c>
       <c r="C3">
-        <v>11164.17487829617</v>
+        <v>11171.27030165239</v>
       </c>
       <c r="D3">
-        <v>106130.0081517925</v>
+        <v>106197.4593827921</v>
       </c>
       <c r="E3">
-        <v>1.451832885314289</v>
+        <v>1.452755601867558</v>
       </c>
       <c r="F3">
-        <v>2.64765485992821</v>
+        <v>2.649337584566363</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -437,16 +437,16 @@
         <v>77137.8057420128</v>
       </c>
       <c r="C4">
-        <v>12296.40976309815</v>
+        <v>12304.224781582</v>
       </c>
       <c r="D4">
-        <v>116893.373905529</v>
+        <v>116967.6658244964</v>
       </c>
       <c r="E4">
-        <v>1.51538370557854</v>
+        <v>1.516346812037854</v>
       </c>
       <c r="F4">
-        <v>2.675637665401252</v>
+        <v>2.677338174591661</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -457,16 +457,16 @@
         <v>81174.90600660577</v>
       </c>
       <c r="C5">
-        <v>13436.73439231778</v>
+        <v>13445.27414738951</v>
       </c>
       <c r="D5">
-        <v>127733.6432056851</v>
+        <v>127814.8246888898</v>
       </c>
       <c r="E5">
-        <v>1.573560715860768</v>
+        <v>1.574560796885784</v>
       </c>
       <c r="F5">
-        <v>2.686415157098405</v>
+        <v>2.688122515954567</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -477,16 +477,16 @@
         <v>85212.00627119873</v>
       </c>
       <c r="C6">
-        <v>14578.123166531</v>
+        <v>14587.38833451102</v>
       </c>
       <c r="D6">
-        <v>138584.028588586</v>
+        <v>138672.1060653334</v>
       </c>
       <c r="E6">
-        <v>1.626343923267381</v>
+        <v>1.627377550811216</v>
       </c>
       <c r="F6">
-        <v>2.681402476513121</v>
+        <v>2.683106649545761</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -497,16 +497,16 @@
         <v>89249.1065357917</v>
       </c>
       <c r="C7">
-        <v>15714.19026301286</v>
+        <v>15724.17746169362</v>
       </c>
       <c r="D7">
-        <v>149383.8245005078</v>
+        <v>149478.7658185145</v>
       </c>
       <c r="E7">
-        <v>1.673785097676022</v>
+        <v>1.674848876594286</v>
       </c>
       <c r="F7">
-        <v>2.662161728778765</v>
+        <v>2.663853673299013</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -517,16 +517,16 @@
         <v>93286.20680038465</v>
       </c>
       <c r="C8">
-        <v>16839.23686022432</v>
+        <v>16849.93908549591</v>
       </c>
       <c r="D8">
-        <v>160078.85622787</v>
+        <v>160180.5948039581</v>
       </c>
       <c r="E8">
-        <v>1.715997055924992</v>
+        <v>1.717087662774361</v>
       </c>
       <c r="F8">
-        <v>2.630334509008536</v>
+        <v>2.632006225647995</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -537,16 +537,16 @@
         <v>97323.30706497761</v>
       </c>
       <c r="C9">
-        <v>17948.27142833771</v>
+        <v>17959.67850370912</v>
       </c>
       <c r="D9">
-        <v>170621.6727850805</v>
+        <v>170730.1118784621</v>
       </c>
       <c r="E9">
-        <v>1.753142982196088</v>
+        <v>1.754257197245411</v>
       </c>
       <c r="F9">
-        <v>2.587583310384733</v>
+        <v>2.589227856377319</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -557,16 +557,16 @@
         <v>101360.4073295706</v>
       </c>
       <c r="C10">
-        <v>19037.00718853836</v>
+        <v>19049.10621304403</v>
       </c>
       <c r="D10">
-        <v>180971.5227618911</v>
+        <v>181086.5397321029</v>
       </c>
       <c r="E10">
-        <v>1.785426159283942</v>
+        <v>1.786560891999032</v>
       </c>
       <c r="F10">
-        <v>2.535542904072138</v>
+        <v>2.537154375635279</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -577,16 +577,16 @@
         <v>105397.5075941635</v>
       </c>
       <c r="C11">
-        <v>20101.84110795835</v>
+        <v>20114.61689071483</v>
       </c>
       <c r="D11">
-        <v>191094.1546429133</v>
+        <v>191215.6050808429</v>
       </c>
       <c r="E11">
-        <v>1.813080394450384</v>
+        <v>1.814232702893931</v>
       </c>
       <c r="F11">
-        <v>2.475781934132283</v>
+        <v>2.477355424439617</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -597,16 +597,16 @@
         <v>109434.6078587565</v>
       </c>
       <c r="C12">
-        <v>21139.81873952292</v>
+        <v>21153.25421193946</v>
       </c>
       <c r="D12">
-        <v>200961.4825646109</v>
+        <v>201089.2042110948</v>
       </c>
       <c r="E12">
-        <v>1.836361334834635</v>
+        <v>1.837528439546599</v>
       </c>
       <c r="F12">
-        <v>2.409774312935995</v>
+        <v>2.411305851910404</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -617,16 +617,16 @@
         <v>113471.7081233495</v>
       </c>
       <c r="C13">
-        <v>22148.58892150667</v>
+        <v>22162.66552070493</v>
       </c>
       <c r="D13">
-        <v>210551.1556756398</v>
+        <v>210684.972066367</v>
       </c>
       <c r="E13">
-        <v>1.8555387872258</v>
+        <v>1.856718080222621</v>
       </c>
       <c r="F13">
-        <v>2.338879541330148</v>
+        <v>2.34036602292918</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -637,16 +637,16 @@
         <v>117508.8083879425</v>
       </c>
       <c r="C14">
-        <v>23126.35190226461</v>
+        <v>23141.04992152893</v>
       </c>
       <c r="D14">
-        <v>219846.064994921</v>
+        <v>219985.7887919184</v>
       </c>
       <c r="E14">
-        <v>1.870890089099732</v>
+        <v>1.872079138660478</v>
       </c>
       <c r="F14">
-        <v>2.264330797719208</v>
+        <v>2.265769899650476</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -657,16 +657,16 @@
         <v>121545.9086525354</v>
       </c>
       <c r="C15">
-        <v>24071.80392322001</v>
+        <v>24087.10282722726</v>
       </c>
       <c r="D15">
-        <v>228833.8166008363</v>
+        <v>228979.2525891384</v>
       </c>
       <c r="E15">
-        <v>1.882694523721123</v>
+        <v>1.88389107562414</v>
       </c>
       <c r="F15">
-        <v>2.187229512560227</v>
+        <v>2.188619612548633</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -677,16 +677,16 @@
         <v>125583.0089171284</v>
       </c>
       <c r="C16">
-        <v>24984.08073542937</v>
+        <v>24999.9594395805</v>
       </c>
       <c r="D16">
-        <v>237506.1946826858</v>
+        <v>237657.1424257452</v>
       </c>
       <c r="E16">
-        <v>1.891228731742007</v>
+        <v>1.892430707585403</v>
       </c>
       <c r="F16">
-        <v>2.108545135115937</v>
+        <v>2.109885227022632</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -697,16 +697,16 @@
         <v>129620.1091817213</v>
       </c>
       <c r="C17">
-        <v>25862.70198446146</v>
+        <v>25879.13909886678</v>
       </c>
       <c r="D17">
-        <v>245858.6328466018</v>
+        <v>246014.8890056862</v>
       </c>
       <c r="E17">
-        <v>1.896763043934174</v>
+        <v>1.897968537125553</v>
       </c>
       <c r="F17">
-        <v>2.029118873231217</v>
+        <v>2.030408485549421</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -717,16 +717,16 @@
         <v>133657.2094463143</v>
       </c>
       <c r="C18">
-        <v>26707.51790335056</v>
+        <v>26724.49194293557</v>
       </c>
       <c r="D18">
-        <v>253889.7073627105</v>
+        <v>254051.067694232</v>
       </c>
       <c r="E18">
-        <v>1.899558642698504</v>
+        <v>1.900765912640694</v>
       </c>
       <c r="F18">
-        <v>1.949670313604066</v>
+        <v>1.950909432162395</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -737,16 +737,16 @@
         <v>137694.3097109073</v>
       </c>
       <c r="C19">
-        <v>27518.65932041933</v>
+        <v>27536.14888325783</v>
       </c>
       <c r="D19">
-        <v>261600.6619244418</v>
+        <v>261766.9229752456</v>
       </c>
       <c r="E19">
-        <v>1.89986545176543</v>
+        <v>1.901072916701002</v>
       </c>
       <c r="F19">
-        <v>1.870805984251907</v>
+        <v>1.871994980359576</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -757,16 +757,16 @@
         <v>141731.4099755002</v>
       </c>
       <c r="C20">
-        <v>28296.49162478404</v>
+        <v>28314.47554117396</v>
       </c>
       <c r="D20">
-        <v>268994.9700307614</v>
+        <v>269165.9305552847</v>
       </c>
       <c r="E20">
-        <v>1.897920652008331</v>
+        <v>1.899126880920841</v>
       </c>
       <c r="F20">
-        <v>1.793029083438709</v>
+        <v>1.794168648214046</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -777,16 +777,16 @@
         <v>145768.5102400932</v>
       </c>
       <c r="C21">
-        <v>29041.57303746591</v>
+        <v>29060.03049248411</v>
       </c>
       <c r="D21">
-        <v>276077.9382987884</v>
+        <v>276253.4004241042</v>
       </c>
       <c r="E21">
-        <v>1.893947724677055</v>
+        <v>1.895151428584207</v>
       </c>
       <c r="F21">
-        <v>1.716749756786525</v>
+        <v>1.717840842017086</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -797,16 +797,16 @@
         <v>149805.6105046861</v>
       </c>
       <c r="C22">
-        <v>29754.61730578667</v>
+        <v>29773.52793813419</v>
       </c>
       <c r="D22">
-        <v>282856.351825487</v>
+        <v>283036.1219909562</v>
       </c>
       <c r="E22">
-        <v>1.888155930025323</v>
+        <v>1.889355952940777</v>
       </c>
       <c r="F22">
-        <v>1.642295448126845</v>
+        <v>1.643339213708043</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -817,16 +817,16 @@
         <v>153842.7107692791</v>
       </c>
       <c r="C23">
-        <v>30436.46076600121</v>
+        <v>30455.804745915</v>
       </c>
       <c r="D23">
-        <v>289338.1610751338</v>
+        <v>289522.0507730577</v>
       </c>
       <c r="E23">
-        <v>1.880740137952066</v>
+        <v>1.881935447739604</v>
       </c>
       <c r="F23">
-        <v>1.569920975236504</v>
+        <v>1.570918743013933</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -837,16 +837,16 @@
         <v>157879.811033872</v>
       </c>
       <c r="C24">
-        <v>31088.03359554455</v>
+        <v>31107.79168443849</v>
       </c>
       <c r="D24">
-        <v>295532.2085945216</v>
+        <v>295720.0349371074</v>
       </c>
       <c r="E24">
-        <v>1.871880936892667</v>
+        <v>1.873070616189568</v>
       </c>
       <c r="F24">
-        <v>1.499818087221903</v>
+        <v>1.500771300907838</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -857,16 +857,16 @@
         <v>161916.911298465</v>
       </c>
       <c r="C25">
-        <v>31710.33499325263</v>
+        <v>31730.48858758427</v>
       </c>
       <c r="D25">
-        <v>301447.9930686635</v>
+        <v>301639.5792050348</v>
       </c>
       <c r="E25">
-        <v>1.861744957035388</v>
+        <v>1.862928194381227</v>
       </c>
       <c r="F25">
-        <v>1.432124346216329</v>
+        <v>1.433034536951062</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -877,16 +877,16 @@
         <v>165954.011563058</v>
       </c>
       <c r="C26">
-        <v>32304.41197530093</v>
+        <v>32324.94313696198</v>
       </c>
       <c r="D26">
-        <v>307095.4677486016</v>
+        <v>307290.6431536993</v>
       </c>
       <c r="E26">
-        <v>1.850485353479471</v>
+        <v>1.851661434751984</v>
       </c>
       <c r="F26">
-        <v>1.366931243727859</v>
+        <v>1.367800000799371</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -897,16 +897,16 @@
         <v>169991.111827651</v>
       </c>
       <c r="C27">
-        <v>32871.34144906557</v>
+        <v>32892.2329243793</v>
       </c>
       <c r="D27">
-        <v>312484.8700401318</v>
+        <v>312683.4706953096</v>
       </c>
       <c r="E27">
-        <v>1.838242403855509</v>
+        <v>1.839410704086283</v>
       </c>
       <c r="F27">
-        <v>1.304291513586095</v>
+        <v>1.305120459797495</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -917,16 +917,16 @@
         <v>174028.2120922439</v>
       </c>
       <c r="C28">
-        <v>33412.21522033156</v>
+        <v>33433.45044952153</v>
       </c>
       <c r="D28">
-        <v>317626.5789778112</v>
+        <v>317828.4474608477</v>
       </c>
       <c r="E28">
-        <v>1.825144182998632</v>
+        <v>1.826304158617582</v>
       </c>
       <c r="F28">
-        <v>1.244225641415804</v>
+        <v>1.245016412589908</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -937,16 +937,16 @@
         <v>178065.3123568369</v>
       </c>
       <c r="C29">
-        <v>33928.12759599143</v>
+        <v>33949.69071477108</v>
       </c>
       <c r="D29">
-        <v>322530.997372478</v>
+        <v>322735.9828726882</v>
       </c>
       <c r="E29">
-        <v>1.811307284408862</v>
+        <v>1.812458465947237</v>
       </c>
       <c r="F29">
-        <v>1.186727597340933</v>
+        <v>1.187481825468263</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -957,16 +957,16 @@
         <v>182102.4126214298</v>
       </c>
       <c r="C30">
-        <v>34420.16526033995</v>
+        <v>34442.04109506805</v>
       </c>
       <c r="D30">
-        <v>327208.4555722608</v>
+        <v>327416.4138444422</v>
       </c>
       <c r="E30">
-        <v>1.796837564434085</v>
+        <v>1.79797954970044</v>
       </c>
       <c r="F30">
-        <v>1.131769836449804</v>
+        <v>1.132489136014615</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -977,16 +977,16 @@
         <v>186139.5128860228</v>
       </c>
       <c r="C31">
-        <v>34889.3991249303</v>
+        <v>34911.57318258653</v>
       </c>
       <c r="D31">
-        <v>331669.1339848576</v>
+        <v>331879.9272539947</v>
       </c>
       <c r="E31">
-        <v>1.781830890402865</v>
+        <v>1.782963338134509</v>
       </c>
       <c r="F31">
-        <v>1.079307622425665</v>
+        <v>1.079993579479926</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -997,16 +997,16 @@
         <v>190176.6131506157</v>
       </c>
       <c r="C32">
-        <v>35336.87787715522</v>
+        <v>35359.33633121553</v>
       </c>
       <c r="D32">
-        <v>335923.0017484045</v>
+        <v>336136.4985753964</v>
       </c>
       <c r="E32">
-        <v>1.76637387838199</v>
+        <v>1.767496502365323</v>
       </c>
       <c r="F32">
-        <v>1.02928273536715</v>
+        <v>1.029936898961007</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1017,16 +1017,16 @@
         <v>194213.7134152087</v>
       </c>
       <c r="C33">
-        <v>35763.6229793497</v>
+        <v>35786.35265248337</v>
       </c>
       <c r="D33">
-        <v>339979.769191441</v>
+        <v>340195.8443086137</v>
       </c>
       <c r="E33">
-        <v>1.750544609919484</v>
+        <v>1.751657173565856</v>
       </c>
       <c r="F33">
-        <v>0.9816266265934026</v>
+        <v>0.9822505022106592</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1037,16 +1037,16 @@
         <v>198250.8136798017</v>
       </c>
       <c r="C34">
-        <v>36170.62489691367</v>
+        <v>36193.61324128309</v>
       </c>
       <c r="D34">
-        <v>343848.851976308</v>
+        <v>344067.3861001388</v>
       </c>
       <c r="E34">
-        <v>1.734413320147398</v>
+        <v>1.7355156315063</v>
       </c>
       <c r="F34">
-        <v>0.9362630822786575</v>
+        <v>0.9368581269652443</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1057,16 +1057,16 @@
         <v>202287.9139443946</v>
       </c>
       <c r="C35">
-        <v>36558.84035977945</v>
+        <v>36582.07543559946</v>
       </c>
       <c r="D35">
-        <v>347539.3450658326</v>
+        <v>347760.2246931287</v>
       </c>
       <c r="E35">
-        <v>1.718043052049887</v>
+        <v>1.719134959237959</v>
       </c>
       <c r="F35">
-        <v>0.8931104549778219</v>
+        <v>0.8936780738884034</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1077,16 +1077,16 @@
         <v>206325.0142089876</v>
       </c>
       <c r="C36">
-        <v>36929.19048588614</v>
+        <v>36952.66093879075</v>
       </c>
       <c r="D36">
-        <v>351060.0048845114</v>
+        <v>351283.1220772504</v>
       </c>
       <c r="E36">
-        <v>1.701490273636531</v>
+        <v>1.702571660658819</v>
       </c>
       <c r="F36">
-        <v>0.8520835181668056</v>
+        <v>0.8526250622900584</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1097,16 +1097,16 @@
         <v>210362.1144735806</v>
       </c>
       <c r="C37">
-        <v>37282.55961780558</v>
+        <v>37306.25465547524</v>
       </c>
       <c r="D37">
-        <v>354419.2382591256</v>
+        <v>354644.4904222682</v>
       </c>
       <c r="E37">
-        <v>1.684805456277334</v>
+        <v>1.685876239216107</v>
       </c>
       <c r="F37">
-        <v>0.8130949943386796</v>
+        <v>0.8136117591938101</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1117,16 +1117,16 @@
         <v>214399.2147381735</v>
       </c>
       <c r="C38">
-        <v>37619.79474410904</v>
+        <v>37643.70411253022</v>
       </c>
       <c r="D38">
-        <v>357625.0969180792</v>
+        <v>357852.386573885</v>
       </c>
       <c r="E38">
-        <v>1.668033613625006</v>
+        <v>1.669093737171089</v>
       </c>
       <c r="F38">
-        <v>0.7760568023388366</v>
+        <v>0.7765500274648378</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1137,16 +1137,16 @@
         <v>218436.3150027665</v>
       </c>
       <c r="C39">
-        <v>37941.70539542036</v>
+        <v>37965.81935507903</v>
       </c>
       <c r="D39">
-        <v>360685.2765032482</v>
+        <v>360914.5110649642</v>
       </c>
       <c r="E39">
-        <v>1.651214801433911</v>
+        <v>1.65226423573568</v>
       </c>
       <c r="F39">
-        <v>0.7408810647507785</v>
+        <v>0.7413519338358985</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1157,16 +1157,16 @@
         <v>222473.4152673595</v>
       </c>
       <c r="C40">
-        <v>38249.06392140826</v>
+        <v>38273.37322365945</v>
       </c>
       <c r="D40">
-        <v>363607.1192031538</v>
+        <v>363838.2107503758</v>
       </c>
       <c r="E40">
-        <v>1.634384579236964</v>
+        <v>1.635423317042757</v>
       </c>
       <c r="F40">
-        <v>0.7074809114357545</v>
+        <v>0.707930552957649</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1177,16 +1177,16 @@
         <v>226510.5155319524</v>
       </c>
       <c r="C41">
-        <v>38542.60606932789</v>
+        <v>38567.10193313289</v>
       </c>
       <c r="D41">
-        <v>366397.6192527517</v>
+        <v>366630.4843102817</v>
       </c>
       <c r="E41">
-        <v>1.617574435307249</v>
+        <v>1.618602489377865</v>
       </c>
       <c r="F41">
-        <v>0.6757711108980449</v>
+        <v>0.6762005991652968</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1197,16 +1197,16 @@
         <v>230547.6157965454</v>
       </c>
       <c r="C42">
-        <v>38823.03179726487</v>
+        <v>38847.70588644536</v>
       </c>
       <c r="D42">
-        <v>369063.4306643753</v>
+        <v>369297.9899859921</v>
       </c>
       <c r="E42">
-        <v>1.600812176648437</v>
+        <v>1.601829577417498</v>
       </c>
       <c r="F42">
-        <v>0.6456685570591851</v>
+        <v>0.6460789135620364</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1217,16 +1217,16 @@
         <v>234584.7160611384</v>
       </c>
       <c r="C43">
-        <v>39091.00626611964</v>
+        <v>39115.85066724221</v>
       </c>
       <c r="D43">
-        <v>371610.8766578377</v>
+        <v>371847.0550160602</v>
       </c>
       <c r="E43">
-        <v>1.584122285959103</v>
+        <v>1.585129079420281</v>
       </c>
       <c r="F43">
-        <v>0.6170926353091142</v>
+        <v>0.6174848303029281</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1237,16 +1237,16 @@
         <v>238621.8163257313</v>
       </c>
       <c r="C44">
-        <v>39347.160963758</v>
+        <v>39372.16816473315</v>
       </c>
       <c r="D44">
-        <v>374045.9603469449</v>
+        <v>374283.6863295883</v>
       </c>
       <c r="E44">
-        <v>1.567526247626715</v>
+        <v>1.568522493428142</v>
       </c>
       <c r="F44">
-        <v>0.5899654883695904</v>
+        <v>0.5903404426273968</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1257,16 +1257,16 @@
         <v>242658.9165903243</v>
       </c>
       <c r="C45">
-        <v>39592.09492280726</v>
+        <v>39617.25779226242</v>
       </c>
       <c r="D45">
-        <v>376374.3763162329</v>
+        <v>376613.5821303222</v>
       </c>
       <c r="E45">
-        <v>1.551042844849</v>
+        <v>1.552028614576527</v>
       </c>
       <c r="F45">
-        <v>0.5642121995460563</v>
+        <v>0.5645707862273147</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1277,16 +1277,16 @@
         <v>246696.0168549173</v>
       </c>
       <c r="C46">
-        <v>39826.37600045213</v>
+        <v>39851.68776791796</v>
       </c>
       <c r="D46">
-        <v>378601.5227870928</v>
+        <v>378842.1440705078</v>
       </c>
       <c r="E46">
-        <v>1.534688429970678</v>
+        <v>1.535663805602934</v>
       </c>
       <c r="F46">
-        <v>0.5397609083372295</v>
+        <v>0.5401039549302316</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1297,16 +1297,16 @@
         <v>250733.1171195102</v>
       </c>
       <c r="C47">
-        <v>40050.5421944242</v>
+        <v>40075.99643135738</v>
       </c>
       <c r="D47">
-        <v>380732.5141279632</v>
+        <v>380974.4897690353</v>
       </c>
       <c r="E47">
-        <v>1.51847717007598</v>
+        <v>1.519442242595526</v>
       </c>
       <c r="F47">
-        <v>0.5165428710942548</v>
+        <v>0.5168711613971189</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1317,16 +1317,16 @@
         <v>254770.2173841032</v>
       </c>
       <c r="C48">
-        <v>40265.10297431884</v>
+        <v>40290.69357597092</v>
       </c>
       <c r="D48">
-        <v>382772.1935102293</v>
+        <v>383015.4654753814</v>
       </c>
       <c r="E48">
-        <v>1.502421269803073</v>
+        <v>1.503376137949161</v>
       </c>
       <c r="F48">
-        <v>0.494492477442805</v>
+        <v>0.4948067535547717</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1337,16 +1337,16 @@
         <v>258807.3176486962</v>
       </c>
       <c r="C49">
-        <v>40470.54061153283</v>
+        <v>40496.26177966432</v>
       </c>
       <c r="D49">
-        <v>384725.1455510104</v>
+        <v>384969.658720432</v>
       </c>
       <c r="E49">
-        <v>1.486531173253897</v>
+        <v>1.487475942403561</v>
       </c>
       <c r="F49">
-        <v>0.4735472314717729</v>
+        <v>0.4738481957725984</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1357,16 +1357,16 @@
         <v>262844.4179132891</v>
       </c>
       <c r="C50">
-        <v>40667.31149460381</v>
+        <v>40693.15772103426</v>
       </c>
       <c r="D50">
-        <v>386595.7088171732</v>
+        <v>386841.4108284423</v>
       </c>
       <c r="E50">
-        <v>1.470815746768908</v>
+        <v>1.471750527934206</v>
       </c>
       <c r="F50">
-        <v>0.4536477052233712</v>
+        <v>0.4539360223232138</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1377,16 +1377,16 @@
         <v>266881.5181778821</v>
       </c>
       <c r="C51">
-        <v>40855.84741964462</v>
+        <v>40881.81347062284</v>
       </c>
       <c r="D51">
-        <v>388387.9880925889</v>
+        <v>388634.8291920906</v>
       </c>
       <c r="E51">
-        <v>1.455282444225757</v>
+        <v>1.456207353156083</v>
       </c>
       <c r="F51">
-        <v>0.4347374707617996</v>
+        <v>0.4350137694079094</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1397,16 +1397,16 @@
         <v>270918.618442475</v>
       </c>
       <c r="C52">
-        <v>41036.55684798511</v>
+        <v>41062.63774935868</v>
       </c>
       <c r="D52">
-        <v>390105.8663336551</v>
+        <v>390353.7992355988</v>
       </c>
       <c r="E52">
-        <v>1.439937456408104</v>
+        <v>1.440852612787422</v>
       </c>
       <c r="F52">
-        <v>0.4167630160255559</v>
+        <v>0.417027890955437</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1417,16 +1417,16 @@
         <v>274955.718707068</v>
       </c>
       <c r="C53">
-        <v>41209.82612513544</v>
+        <v>41236.01714829494</v>
       </c>
       <c r="D53">
-        <v>391753.0162571276</v>
+        <v>392001.9960099283</v>
       </c>
       <c r="E53">
-        <v>1.424785845878306</v>
+        <v>1.425691372608107</v>
       </c>
       <c r="F53">
-        <v>0.3996736487584328</v>
+        <v>0.3999276624919303</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1437,16 +1437,16 @@
         <v>278992.8189716609</v>
       </c>
       <c r="C54">
-        <v>41376.0206568314</v>
+        <v>41402.31730540207</v>
       </c>
       <c r="D54">
-        <v>393332.9115199621</v>
+        <v>393582.8953797272</v>
       </c>
       <c r="E54">
-        <v>1.409831668677879</v>
+        <v>1.410727691237479</v>
       </c>
       <c r="F54">
-        <v>0.3834213920434504</v>
+        <v>0.3836650766085852</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -1457,16 +1457,16 @@
         <v>283029.9192362539</v>
       </c>
       <c r="C55">
-        <v>41535.48603926924</v>
+        <v>41561.88403652098</v>
       </c>
       <c r="D55">
-        <v>394848.837463666</v>
+        <v>395099.7847745115</v>
       </c>
       <c r="E55">
-        <v>1.395078084073767</v>
+        <v>1.395964729950367</v>
       </c>
       <c r="F55">
-        <v>0.367960874314699</v>
+        <v>0.3681947329034668</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1477,16 +1477,16 @@
         <v>287067.0195008469</v>
       </c>
       <c r="C56">
-        <v>41688.54914173228</v>
+        <v>41715.04441867767</v>
       </c>
       <c r="D56">
-        <v>396303.9014060735</v>
+        <v>396555.7734869798</v>
       </c>
       <c r="E56">
-        <v>1.380527453467724</v>
+        <v>1.38140485164932</v>
       </c>
       <c r="F56">
-        <v>0.3532492161755836</v>
+        <v>0.353473724727836</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1497,16 +1497,16 @@
         <v>291104.1197654398</v>
       </c>
       <c r="C57">
-        <v>41835.51914069447</v>
+        <v>41862.10782484413</v>
       </c>
       <c r="D57">
-        <v>397701.0424718454</v>
+        <v>397953.8025097623</v>
       </c>
       <c r="E57">
-        <v>1.366181429490923</v>
+        <v>1.367049710015845</v>
       </c>
       <c r="F57">
-        <v>0.3392459158941219</v>
+        <v>0.3394615246087361</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1517,16 +1517,16 @@
         <v>295141.2200300328</v>
       </c>
       <c r="C58">
-        <v>41976.68850519222</v>
+        <v>42003.36690993628</v>
       </c>
       <c r="D58">
-        <v>399043.04095971</v>
+        <v>399296.653908614</v>
       </c>
       <c r="E58">
-        <v>1.352041036216847</v>
+        <v>1.352900329774277</v>
       </c>
       <c r="F58">
-        <v>0.3259127350644078</v>
+        <v>0.326119869837703</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -1537,16 +1537,16 @@
         <v>299178.3202946258</v>
       </c>
       <c r="C59">
-        <v>42112.33393381421</v>
+        <v>42139.09854839938</v>
       </c>
       <c r="D59">
-        <v>400332.5272497709</v>
+        <v>400586.9597353839</v>
       </c>
       <c r="E59">
-        <v>1.338106741342522</v>
+        <v>1.338957178918889</v>
       </c>
       <c r="F59">
-        <v>0.3132135856047135</v>
+        <v>0.3134126493971574</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -1557,16 +1557,16 @@
         <v>303215.4205592187</v>
       </c>
       <c r="C60">
-        <v>42242.71724409475</v>
+        <v>42269.56472416664</v>
       </c>
       <c r="D60">
-        <v>401571.9902583478</v>
+        <v>401827.21048823</v>
       </c>
       <c r="E60">
-        <v>1.324378521111263</v>
+        <v>1.325220233677898</v>
       </c>
       <c r="F60">
-        <v>0.301114418999453</v>
+        <v>0.3013057931318713</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1577,16 +1577,16 @@
         <v>307252.5208238117</v>
       </c>
       <c r="C61">
-        <v>42368.08621543104</v>
+        <v>42395.01337411214</v>
       </c>
       <c r="D61">
-        <v>402763.7854510018</v>
+        <v>403019.7631297361</v>
       </c>
       <c r="E61">
-        <v>1.310855918679213</v>
+        <v>1.311689036917098</v>
       </c>
       <c r="F61">
-        <v>0.2952106993988948</v>
+        <v>0.2953983214053892</v>
       </c>
     </row>
   </sheetData>
@@ -1627,16 +1627,16 @@
         <v>33337.86217631619</v>
       </c>
       <c r="C2">
-        <v>5420.973556981114</v>
+        <v>5416.629980920686</v>
       </c>
       <c r="D2">
-        <v>51533.40699737061</v>
+        <v>51492.11565540164</v>
       </c>
       <c r="E2">
-        <v>1.545792190417682</v>
+        <v>1.544553618437554</v>
       </c>
       <c r="F2">
-        <v>3.199197785607728</v>
+        <v>3.196634415990065</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1647,16 +1647,16 @@
         <v>35262.06742565849</v>
       </c>
       <c r="C3">
-        <v>6068.53490549152</v>
+        <v>6063.672468392299</v>
       </c>
       <c r="D3">
-        <v>57689.32017012125</v>
+        <v>57643.09637887797</v>
       </c>
       <c r="E3">
-        <v>1.63601638763085</v>
+        <v>1.634705523163225</v>
       </c>
       <c r="F3">
-        <v>3.270619944194959</v>
+        <v>3.267999347296076</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1667,16 +1667,16 @@
         <v>37186.27267500078</v>
       </c>
       <c r="C4">
-        <v>6745.009895750702</v>
+        <v>6739.60543044524</v>
       </c>
       <c r="D4">
-        <v>64120.09512781769</v>
+        <v>64068.71865323023</v>
       </c>
       <c r="E4">
-        <v>1.724294760279207</v>
+        <v>1.722913162423555</v>
       </c>
       <c r="F4">
-        <v>3.408698826716651</v>
+        <v>3.405967593578304</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1687,16 +1687,16 @@
         <v>39110.47792434307</v>
       </c>
       <c r="C5">
-        <v>7448.469349572885</v>
+        <v>7442.50123465523</v>
       </c>
       <c r="D5">
-        <v>70807.39252171142</v>
+        <v>70750.65782418416</v>
       </c>
       <c r="E5">
-        <v>1.810445596156717</v>
+        <v>1.808994969610118</v>
       </c>
       <c r="F5">
-        <v>3.537088604077776</v>
+        <v>3.534254498133003</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1707,16 +1707,16 @@
         <v>41034.68317368537</v>
       </c>
       <c r="C6">
-        <v>8176.920030573635</v>
+        <v>8170.368241726207</v>
       </c>
       <c r="D6">
-        <v>77732.26404652823</v>
+        <v>77669.98076886853</v>
       </c>
       <c r="E6">
-        <v>1.894306426529843</v>
+        <v>1.892788606168076</v>
       </c>
       <c r="F6">
-        <v>3.655517645073399</v>
+        <v>3.652588647400797</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1727,16 +1727,16 @@
         <v>42958.88842302767</v>
       </c>
       <c r="C7">
-        <v>8928.322796831786</v>
+        <v>8921.168943607368</v>
       </c>
       <c r="D7">
-        <v>84875.32500513869</v>
+        <v>84807.31832221757</v>
       </c>
       <c r="E7">
-        <v>1.975733733362667</v>
+        <v>1.974150669055894</v>
       </c>
       <c r="F7">
-        <v>3.763802226996099</v>
+        <v>3.760786465882804</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1747,16 +1747,16 @@
         <v>44883.09367236996</v>
       </c>
       <c r="C8">
-        <v>9700.61003598983</v>
+        <v>9692.837384623619</v>
       </c>
       <c r="D8">
-        <v>92216.92005187244</v>
+        <v>92143.0308874828</v>
       </c>
       <c r="E8">
-        <v>2.054602579871654</v>
+        <v>2.052956321596122</v>
       </c>
       <c r="F8">
-        <v>3.861842588313349</v>
+        <v>3.858748271980796</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1767,16 +1767,16 @@
         <v>46807.29892171224</v>
       </c>
       <c r="C9">
-        <v>10491.70221993179</v>
+        <v>10483.29570288893</v>
       </c>
       <c r="D9">
-        <v>99737.280566271</v>
+        <v>99657.36568388944</v>
       </c>
       <c r="E9">
-        <v>2.130806153396867</v>
+        <v>2.129098836712877</v>
       </c>
       <c r="F9">
-        <v>3.949618227489297</v>
+        <v>3.946453580585853</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1787,16 +1787,16 @@
         <v>48731.50417105455</v>
       </c>
       <c r="C10">
-        <v>11299.52343671813</v>
+        <v>11290.46964979627</v>
       </c>
       <c r="D10">
-        <v>107416.6723043383</v>
+        <v>107330.6042795808</v>
       </c>
       <c r="E10">
-        <v>2.20425521706226</v>
+        <v>2.202489049031506</v>
       </c>
       <c r="F10">
-        <v>4.02718255811842</v>
+        <v>4.023955762494613</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1807,16 +1807,16 @@
         <v>50655.70942039684</v>
       </c>
       <c r="C11">
-        <v>12122.0157815157</v>
+        <v>12112.30296941668</v>
       </c>
       <c r="D11">
-        <v>115235.5322030534</v>
+        <v>115143.1992865161</v>
       </c>
       <c r="E11">
-        <v>2.274877472284557</v>
+        <v>2.273054717898254</v>
       </c>
       <c r="F11">
-        <v>4.094657044101082</v>
+        <v>4.091376184284026</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1827,16 +1827,16 @@
         <v>52579.91466973913</v>
       </c>
       <c r="C12">
-        <v>12957.15251429142</v>
+        <v>12946.7705456504</v>
       </c>
       <c r="D12">
-        <v>123174.5934613697</v>
+        <v>123075.8993412475</v>
       </c>
       <c r="E12">
-        <v>2.342616838293564</v>
+        <v>2.340739807477861</v>
       </c>
       <c r="F12">
-        <v>4.152224945116812</v>
+        <v>4.148897958796089</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1847,16 +1847,16 @@
         <v>54504.11991908143</v>
       </c>
       <c r="C13">
-        <v>13802.94991873886</v>
+        <v>13791.89025165137</v>
       </c>
       <c r="D13">
-        <v>131214.998274741</v>
+        <v>131109.861749118</v>
       </c>
       <c r="E13">
-        <v>2.407432657743066</v>
+        <v>2.405503693000969</v>
       </c>
       <c r="F13">
-        <v>4.200124803289835</v>
+        <v>4.196759437022207</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1867,16 +1867,16 @@
         <v>56428.32516842373</v>
       </c>
       <c r="C14">
-        <v>14657.47782319614</v>
+        <v>14645.73346231523</v>
       </c>
       <c r="D14">
-        <v>139338.3978501359</v>
+        <v>139226.7524191375</v>
       </c>
       <c r="E14">
-        <v>2.469298839443619</v>
+        <v>2.467320304183797</v>
       </c>
       <c r="F14">
-        <v>4.238643797762805</v>
+        <v>4.235247568001644</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1887,16 +1887,16 @@
         <v>58352.53041776601</v>
       </c>
       <c r="C15">
-        <v>15518.8687693223</v>
+        <v>15506.43421560924</v>
       </c>
       <c r="D15">
-        <v>147527.0395662357</v>
+        <v>147408.8329543439</v>
       </c>
       <c r="E15">
-        <v>2.528202950412577</v>
+        <v>2.526177218005679</v>
       </c>
       <c r="F15">
-        <v>4.268111085903049</v>
+        <v>4.264691245363138</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1907,16 +1907,16 @@
         <v>60276.73566710831</v>
       </c>
       <c r="C16">
-        <v>16385.32583735357</v>
+        <v>16372.19703155857</v>
       </c>
       <c r="D16">
-        <v>155763.8413626772</v>
+        <v>155639.0349814412</v>
       </c>
       <c r="E16">
-        <v>2.584145269958176</v>
+        <v>2.582074713551052</v>
       </c>
       <c r="F16">
-        <v>4.288891239008601</v>
+        <v>4.28545474829052</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1927,16 +1927,16 @@
         <v>62200.9409164506</v>
       </c>
       <c r="C17">
-        <v>17255.1291573741</v>
+        <v>17241.30341829979</v>
       </c>
       <c r="D17">
-        <v>164032.4536381527</v>
+        <v>163901.0219993028</v>
       </c>
       <c r="E17">
-        <v>2.637137818517633</v>
+        <v>2.635024801625712</v>
       </c>
       <c r="F17">
-        <v>4.301377867529855</v>
+        <v>4.297931371852298</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1947,16 +1947,16 @@
         <v>64125.14616579289</v>
       </c>
       <c r="C18">
-        <v>18126.64115388773</v>
+        <v>18112.11711245045</v>
       </c>
       <c r="D18">
-        <v>172317.3091068886</v>
+        <v>172179.2391955034</v>
       </c>
       <c r="E18">
-        <v>2.687203373562212</v>
+        <v>2.685050241450384</v>
       </c>
       <c r="F18">
-        <v>4.305987516765077</v>
+        <v>4.302537327588221</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1967,16 +1967,16 @@
         <v>66049.35141513518</v>
       </c>
       <c r="C19">
-        <v>18998.31058589943</v>
+        <v>18983.08811595338</v>
       </c>
       <c r="D19">
-        <v>180603.6612048762</v>
+        <v>180458.9518217757</v>
       </c>
       <c r="E19">
-        <v>2.734374484160202</v>
+        <v>2.732183556013293</v>
       </c>
       <c r="F19">
-        <v>4.303153899417362</v>
+        <v>4.299705980687394</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1987,16 +1987,16 @@
         <v>67973.5566644775</v>
       </c>
       <c r="C20">
-        <v>19868.67545666853</v>
+        <v>19852.75560349846</v>
       </c>
       <c r="D20">
-        <v>188877.6117508619</v>
+        <v>188726.2728328377</v>
       </c>
       <c r="E20">
-        <v>2.77869249483554</v>
+        <v>2.776466056710914</v>
       </c>
       <c r="F20">
-        <v>4.293322516898286</v>
+        <v>4.289882475601626</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2007,16 +2007,16 @@
         <v>69897.76191381979</v>
       </c>
       <c r="C21">
-        <v>20736.36487634688</v>
+        <v>20719.74978366834</v>
       </c>
       <c r="D21">
-        <v>197126.1286531466</v>
+        <v>196968.1805790041</v>
       </c>
       <c r="E21">
-        <v>2.820206588248027</v>
+        <v>2.81794688679525</v>
       </c>
       <c r="F21">
-        <v>4.276945707311247</v>
+        <v>4.273518787996707</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2027,16 +2027,16 @@
         <v>71821.96716316207</v>
       </c>
       <c r="C22">
-        <v>21600.09996702036</v>
+        <v>21582.79280325478</v>
       </c>
       <c r="D22">
-        <v>205337.0545131825</v>
+        <v>205172.52740289</v>
       </c>
       <c r="E22">
-        <v>2.858972855013934</v>
+        <v>2.856682091939752</v>
       </c>
       <c r="F22">
-        <v>4.254478145015995</v>
+        <v>4.251069227922779</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2047,16 +2047,16 @@
         <v>73746.17241250437</v>
       </c>
       <c r="C23">
-        <v>22458.69390344781</v>
+        <v>22440.69878796494</v>
       </c>
       <c r="D23">
-        <v>213499.1070128502</v>
+        <v>213328.040026377</v>
       </c>
       <c r="E23">
-        <v>2.895053397736062</v>
+        <v>2.892733724987268</v>
       </c>
       <c r="F23">
-        <v>4.226372804831072</v>
+        <v>4.222986407250534</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2067,16 +2067,16 @@
         <v>75670.37766184665</v>
       </c>
       <c r="C24">
-        <v>23311.05118430136</v>
+        <v>23292.37311424563</v>
       </c>
       <c r="D24">
-        <v>221601.8719866494</v>
+        <v>221424.3126283553</v>
       </c>
       <c r="E24">
-        <v>2.928515475063924</v>
+        <v>2.926168990696057</v>
       </c>
       <c r="F24">
-        <v>4.193077393454023</v>
+        <v>4.189717673950813</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2087,16 +2087,16 @@
         <v>77594.58291118896</v>
       </c>
       <c r="C25">
-        <v>24156.16622824675</v>
+        <v>24136.81100648855</v>
       </c>
       <c r="D25">
-        <v>229635.7900756157</v>
+        <v>229451.7935093337</v>
       </c>
       <c r="E25">
-        <v>2.959430690392986</v>
+        <v>2.957059435089087</v>
       </c>
       <c r="F25">
-        <v>4.155031241664103</v>
+        <v>4.151702006787385</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2107,16 +2107,16 @@
         <v>79518.78816053126</v>
       </c>
       <c r="C26">
-        <v>24993.12138706237</v>
+        <v>24973.09555174126</v>
       </c>
       <c r="D26">
-        <v>237592.137839432</v>
+        <v>237401.7662186858</v>
       </c>
       <c r="E26">
-        <v>2.987874228663858</v>
+        <v>2.985480182864745</v>
       </c>
       <c r="F26">
-        <v>4.112662643340637</v>
+        <v>4.109367356467452</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2127,16 +2127,16 @@
         <v>81442.99340987354</v>
       </c>
       <c r="C27">
-        <v>25821.08446448148</v>
+        <v>25800.39522053751</v>
       </c>
       <c r="D27">
-        <v>245463.0041697957</v>
+        <v>245266.3259869148</v>
       </c>
       <c r="E27">
-        <v>3.013924143657981</v>
+        <v>3.011509225263576</v>
       </c>
       <c r="F27">
-        <v>4.066386621258729</v>
+        <v>4.063128413227478</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2147,16 +2147,16 @@
         <v>83367.19865921584</v>
       </c>
       <c r="C28">
-        <v>26639.30582484433</v>
+        <v>26617.96097786602</v>
       </c>
       <c r="D28">
-        <v>253241.2628043946</v>
+        <v>253038.352261654</v>
       </c>
       <c r="E28">
-        <v>3.037660697219554</v>
+        <v>3.035226759819665</v>
       </c>
       <c r="F28">
-        <v>4.016603094931042</v>
+        <v>4.013384776143096</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2167,16 +2167,16 @@
         <v>85291.40390855813</v>
       </c>
       <c r="C29">
-        <v>27447.11517023262</v>
+        <v>27425.12306288731</v>
       </c>
       <c r="D29">
-        <v>260920.5416893773</v>
+        <v>260711.4780946848</v>
       </c>
       <c r="E29">
-        <v>3.059165750971964</v>
+        <v>3.056714582564457</v>
       </c>
       <c r="F29">
-        <v>3.963695422345011</v>
+        <v>3.960519496034674</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2187,16 +2187,16 @@
         <v>87215.60915790043</v>
       </c>
       <c r="C30">
-        <v>28243.91805877701</v>
+        <v>28221.28751003088</v>
       </c>
       <c r="D30">
-        <v>268495.1898813352</v>
+        <v>268280.0570704389</v>
       </c>
       <c r="E30">
-        <v>3.078522210344656</v>
+        <v>3.076055532499101</v>
       </c>
       <c r="F30">
-        <v>3.908029285174749</v>
+        <v>3.904897961572445</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2207,16 +2207,16 @@
         <v>89139.81440724272</v>
       </c>
       <c r="C31">
-        <v>29029.19223049489</v>
+        <v>29005.93247777695</v>
       </c>
       <c r="D31">
-        <v>275960.2426196107</v>
+        <v>275739.1284062922</v>
       </c>
       <c r="E31">
-        <v>3.095813520082767</v>
+        <v>3.093332987508308</v>
       </c>
       <c r="F31">
-        <v>3.849951885779361</v>
+        <v>3.846867096918251</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2227,16 +2227,16 @@
         <v>91064.01965658503</v>
       </c>
       <c r="C32">
-        <v>29802.48380052085</v>
+        <v>29778.6044449371</v>
       </c>
       <c r="D32">
-        <v>283311.3851379991</v>
+        <v>283084.3807932634</v>
       </c>
       <c r="E32">
-        <v>3.111123209873729</v>
+        <v>3.108630410351022</v>
       </c>
       <c r="F32">
-        <v>3.789791423893853</v>
+        <v>3.786754838835854</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2247,16 +2247,16 @@
         <v>92988.22490592733</v>
       </c>
       <c r="C33">
-        <v>30563.40337309462</v>
+        <v>30538.91432775597</v>
       </c>
       <c r="D33">
-        <v>290544.9157231487</v>
+        <v>290312.1154840129</v>
       </c>
       <c r="E33">
-        <v>3.124534488286899</v>
+        <v>3.122030942925415</v>
       </c>
       <c r="F33">
-        <v>3.72785682123194</v>
+        <v>3.724869861514243</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2267,16 +2267,16 @@
         <v>94912.43015526961</v>
       </c>
       <c r="C34">
-        <v>31311.62212330328</v>
+        <v>31286.53356479283</v>
       </c>
       <c r="D34">
-        <v>297657.7084664211</v>
+        <v>297419.2090745486</v>
       </c>
       <c r="E34">
-        <v>3.136129882877041</v>
+        <v>3.133617046660728</v>
       </c>
       <c r="F34">
-        <v>3.664437663112547</v>
+        <v>3.661501518240957</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2287,16 +2287,16 @@
         <v>96836.63540461191</v>
       </c>
       <c r="C35">
-        <v>32046.86788743799</v>
+        <v>32021.19021041109</v>
       </c>
       <c r="D35">
-        <v>304647.1760976462</v>
+        <v>304403.0763677609</v>
       </c>
       <c r="E35">
-        <v>3.14599092404172</v>
+        <v>3.143470186627978</v>
       </c>
       <c r="F35">
-        <v>3.599804327569984</v>
+        <v>3.596919970408846</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2307,16 +2307,16 @@
         <v>98760.8406539542</v>
       </c>
       <c r="C36">
-        <v>32768.92129700348</v>
+        <v>32742.66507188532</v>
       </c>
       <c r="D36">
-        <v>311511.2332338516</v>
+        <v>311261.6336515983</v>
       </c>
       <c r="E36">
-        <v>3.154197870037868</v>
+        <v>3.151670556776857</v>
       </c>
       <c r="F36">
-        <v>3.534208274095556</v>
+        <v>3.531376476026346</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2327,16 +2327,16 @@
         <v>100685.0459032965</v>
       </c>
       <c r="C37">
-        <v>33477.6119859653</v>
+        <v>33450.78791968754</v>
       </c>
       <c r="D37">
-        <v>318248.2603242134</v>
+        <v>317993.2626729084</v>
       </c>
       <c r="E37">
-        <v>3.160829470444665</v>
+        <v>3.158296843588142</v>
       </c>
       <c r="F37">
-        <v>3.467882466082511</v>
+        <v>3.465103811823878</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2347,16 +2347,16 @@
         <v>102609.2511526388</v>
       </c>
       <c r="C38">
-        <v>34172.81489577664</v>
+        <v>34145.43379547454</v>
       </c>
       <c r="D38">
-        <v>324857.0685245277</v>
+        <v>324596.7755400533</v>
       </c>
       <c r="E38">
-        <v>3.165962765299583</v>
+        <v>3.163426025370673</v>
       </c>
       <c r="F38">
-        <v>3.40104190312364</v>
+        <v>3.39831680512497</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2367,16 +2367,16 @@
         <v>104533.4564019811</v>
       </c>
       <c r="C39">
-        <v>34854.4466981141</v>
+        <v>34826.51943769011</v>
       </c>
       <c r="D39">
-        <v>331336.8656906607</v>
+        <v>331071.3807436076</v>
       </c>
       <c r="E39">
-        <v>3.169672917123415</v>
+        <v>3.167133204420985</v>
       </c>
       <c r="F39">
-        <v>3.333884241461227</v>
+        <v>3.331212953799098</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2387,16 +2387,16 @@
         <v>106457.6616513234</v>
       </c>
       <c r="C40">
-        <v>35522.46235107963</v>
+        <v>35493.99984052617</v>
       </c>
       <c r="D40">
-        <v>337687.2236407662</v>
+        <v>337416.6504448078</v>
       </c>
       <c r="E40">
-        <v>3.172033073080076</v>
+        <v>3.169491469293543</v>
       </c>
       <c r="F40">
-        <v>3.266590483057519</v>
+        <v>3.26397311477999</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2407,16 +2407,16 @@
         <v>108381.8669006656</v>
       </c>
       <c r="C41">
-        <v>36176.85180089092</v>
+        <v>36147.86495825605</v>
       </c>
       <c r="D41">
-        <v>343908.0468005623</v>
+        <v>343632.4891459511</v>
       </c>
       <c r="E41">
-        <v>3.173114254580626</v>
+        <v>3.170571784493229</v>
       </c>
       <c r="F41">
-        <v>3.199325715885806</v>
+        <v>3.196762243763509</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2427,16 +2427,16 @@
         <v>110306.072150008</v>
       </c>
       <c r="C42">
-        <v>36817.63683777332</v>
+        <v>36788.1365636456</v>
       </c>
       <c r="D42">
-        <v>349999.5423144927</v>
+        <v>349719.1038255058</v>
       </c>
       <c r="E42">
-        <v>3.172985271731185</v>
+        <v>3.170442904991795</v>
       </c>
       <c r="F42">
-        <v>3.132239890102318</v>
+        <v>3.129730170757777</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2447,16 +2447,16 @@
         <v>112230.2773993503</v>
       </c>
       <c r="C43">
-        <v>37444.86811186586</v>
+        <v>37414.86526625022</v>
       </c>
       <c r="D43">
-        <v>355962.1916780308</v>
+        <v>355676.9755931454</v>
       </c>
       <c r="E43">
-        <v>3.171712660135433</v>
+        <v>3.169171313081014</v>
       </c>
       <c r="F43">
-        <v>3.065468616720413</v>
+        <v>3.06301239811732</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2467,16 +2467,16 @@
         <v>114154.4826486925</v>
       </c>
       <c r="C44">
-        <v>38058.62231243831</v>
+        <v>38028.12769389211</v>
       </c>
       <c r="D44">
-        <v>361796.7239224677</v>
+        <v>361506.8328960215</v>
       </c>
       <c r="E44">
-        <v>3.169360637688558</v>
+        <v>3.166821175201235</v>
       </c>
       <c r="F44">
-        <v>2.999133977244062</v>
+        <v>2.996730909527789</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2487,16 +2487,16 @@
         <v>116078.6878980348</v>
       </c>
       <c r="C45">
-        <v>38658.99951155899</v>
+        <v>38628.02383845647</v>
       </c>
       <c r="D45">
-        <v>367504.0903630185</v>
+        <v>367209.6262871047</v>
       </c>
       <c r="E45">
-        <v>3.165991079136243</v>
+        <v>3.163454316520762</v>
       </c>
       <c r="F45">
-        <v>2.933345334421256</v>
+        <v>2.930994980109862</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2507,16 +2507,16 @@
         <v>118002.8931473771</v>
       </c>
       <c r="C46">
-        <v>39246.12067152691</v>
+        <v>39214.67456532078</v>
       </c>
       <c r="D46">
-        <v>373085.4409037219</v>
+        <v>372786.5047490682</v>
       </c>
       <c r="E46">
-        <v>3.161663506315604</v>
+        <v>3.159130211184607</v>
       </c>
       <c r="F46">
-        <v>2.868200135840076</v>
+        <v>2.865901979371381</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2527,16 +2527,16 @@
         <v>119927.0983967194</v>
       </c>
       <c r="C47">
-        <v>39820.12531385726</v>
+        <v>39788.21928420808</v>
       </c>
       <c r="D47">
-        <v>378542.101878114</v>
+        <v>378238.7935527184</v>
       </c>
       <c r="E47">
-        <v>3.156435092141518</v>
+        <v>3.153905986297631</v>
       </c>
       <c r="F47">
-        <v>2.803784703504481</v>
+        <v>2.801538160150459</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2547,16 +2547,16 @@
         <v>121851.3036460617</v>
       </c>
       <c r="C48">
-        <v>40381.16934635544</v>
+        <v>40348.81377800203</v>
       </c>
       <c r="D48">
-        <v>383875.5553927398</v>
+        <v>383567.9736170567</v>
       </c>
       <c r="E48">
-        <v>3.150360676548632</v>
+        <v>3.147836437853767</v>
       </c>
       <c r="F48">
-        <v>2.740175003799537</v>
+        <v>2.737979427963786</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2567,16 +2567,16 @@
         <v>123775.508895404</v>
       </c>
       <c r="C49">
-        <v>40929.42304380544</v>
+        <v>40896.62818505332</v>
       </c>
       <c r="D49">
-        <v>389087.4201309693</v>
+        <v>388775.6623284767</v>
       </c>
       <c r="E49">
-        <v>3.14349279274437</v>
+        <v>3.140974056968006</v>
       </c>
       <c r="F49">
-        <v>2.677437393389252</v>
+        <v>2.675292086306878</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2587,16 +2587,16 @@
         <v>125699.7141447463</v>
       </c>
       <c r="C50">
-        <v>41465.06917700375</v>
+        <v>41431.84512971261</v>
       </c>
       <c r="D50">
-        <v>394179.4335670297</v>
+        <v>393863.5957690479</v>
       </c>
       <c r="E50">
-        <v>3.135881702269604</v>
+        <v>3.133369064908964</v>
       </c>
       <c r="F50">
-        <v>2.615629337588623</v>
+        <v>2.613533554450351</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2607,16 +2607,16 @@
         <v>127623.9193940886</v>
       </c>
       <c r="C51">
-        <v>41988.30128426441</v>
+        <v>41954.6579952206</v>
       </c>
       <c r="D51">
-        <v>399153.4355344127</v>
+        <v>398833.6122980879</v>
       </c>
       <c r="E51">
-        <v>3.127575437499853</v>
+        <v>3.125069455566034</v>
       </c>
       <c r="F51">
-        <v>2.554800098626016</v>
+        <v>2.552753055151094</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2627,16 +2627,16 @@
         <v>129548.1246434309</v>
       </c>
       <c r="C52">
-        <v>42499.32207908027</v>
+        <v>42465.26933264521</v>
       </c>
       <c r="D52">
-        <v>404011.3530886225</v>
+        <v>403687.6374270406</v>
       </c>
       <c r="E52">
-        <v>3.118619850350022</v>
+        <v>3.116121044115096</v>
       </c>
       <c r="F52">
-        <v>2.494991391968801</v>
+        <v>2.492992270451785</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2647,16 +2647,16 @@
         <v>131472.3298927732</v>
       </c>
       <c r="C53">
-        <v>42998.34198732664</v>
+        <v>42963.88939925716</v>
       </c>
       <c r="D53">
-        <v>408755.1866013932</v>
+        <v>408427.6699248341</v>
       </c>
       <c r="E53">
-        <v>3.10905866606888</v>
+        <v>3.106567520769894</v>
       </c>
       <c r="F53">
-        <v>2.436238009535503</v>
+        <v>2.434285964393707</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2667,16 +2667,16 @@
         <v>133396.5351421155</v>
       </c>
       <c r="C54">
-        <v>43485.57780721584</v>
+        <v>43450.73481955838</v>
       </c>
       <c r="D54">
-        <v>413386.9970218134</v>
+        <v>413055.7690892138</v>
       </c>
       <c r="E54">
-        <v>3.098933541125389</v>
+        <v>3.096450508621984</v>
       </c>
       <c r="F54">
-        <v>2.378568409168982</v>
+        <v>2.37666257201785</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2687,16 +2687,16 @@
         <v>135320.7403914578</v>
       </c>
       <c r="C55">
-        <v>43961.2514851357</v>
+        <v>43926.02736210132</v>
       </c>
       <c r="D55">
-        <v>417908.8942390785</v>
+        <v>417574.0431188183</v>
       </c>
       <c r="E55">
-        <v>3.088284124297175</v>
+        <v>3.085809624680253</v>
       </c>
       <c r="F55">
-        <v>2.322005270210438</v>
+        <v>2.320144754493493</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2707,16 +2707,16 @@
         <v>137244.9456408001</v>
       </c>
       <c r="C56">
-        <v>44425.58900051572</v>
+        <v>44389.99282524855</v>
       </c>
       <c r="D56">
-        <v>422323.0264816922</v>
+        <v>421984.6385208745</v>
       </c>
       <c r="E56">
-        <v>3.07714812017197</v>
+        <v>3.074682543321488</v>
       </c>
       <c r="F56">
-        <v>2.266566015398132</v>
+        <v>2.264749920598836</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2727,16 +2727,16 @@
         <v>139169.1508901424</v>
       </c>
       <c r="C57">
-        <v>44878.81935294432</v>
+        <v>44842.8600251017</v>
       </c>
       <c r="D57">
-        <v>426631.5706886984</v>
+        <v>426289.7304901459</v>
       </c>
       <c r="E57">
-        <v>3.065561354365621</v>
+        <v>3.063105061456123</v>
       </c>
       <c r="F57">
-        <v>2.212263299629484</v>
+        <v>2.210490715091542</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2747,16 +2747,16 @@
         <v>141093.3561394847</v>
       </c>
       <c r="C58">
-        <v>45321.17364489933</v>
+        <v>45284.85987896682</v>
       </c>
       <c r="D58">
-        <v>430836.7237898409</v>
+        <v>430491.5141960777</v>
       </c>
       <c r="E58">
-        <v>3.05355783984553</v>
+        <v>3.051111164798535</v>
       </c>
       <c r="F58">
-        <v>2.159105466380492</v>
+        <v>2.157375474762368</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2767,16 +2767,16 @@
         <v>143017.561388827</v>
       </c>
       <c r="C59">
-        <v>45752.88425363626</v>
+        <v>45716.22457790631</v>
       </c>
       <c r="D59">
-        <v>434940.6948332844</v>
+        <v>434592.1969168261</v>
       </c>
       <c r="E59">
-        <v>3.041169843826351</v>
+        <v>3.03873309470915</v>
       </c>
       <c r="F59">
-        <v>2.107096972773835</v>
+        <v>2.10540865316265</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2787,16 +2787,16 @@
         <v>144941.7666381693</v>
       </c>
       <c r="C60">
-        <v>46174.18408599802</v>
+        <v>46137.1868421455</v>
       </c>
       <c r="D60">
-        <v>438945.6979016102</v>
+        <v>438593.9909609302</v>
       </c>
       <c r="E60">
-        <v>3.028427954775717</v>
+        <v>3.026001415146474</v>
       </c>
       <c r="F60">
-        <v>2.056238784440921</v>
+        <v>2.054591215150116</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2807,16 +2807,16 @@
         <v>146865.9718875116</v>
       </c>
       <c r="C61">
-        <v>46585.30591015414</v>
+        <v>46547.97925334755</v>
       </c>
       <c r="D61">
-        <v>442853.9457591292</v>
+        <v>442499.1073197149</v>
       </c>
       <c r="E61">
-        <v>3.015361149132098</v>
+        <v>3.01294507933149</v>
       </c>
       <c r="F61">
-        <v>2.03109718095557</v>
+        <v>2.029469756471949</v>
       </c>
     </row>
   </sheetData>
@@ -2857,16 +2857,16 @@
         <v>20075.2102041675</v>
       </c>
       <c r="C2">
-        <v>1554.816007392002</v>
+        <v>1555.106124179238</v>
       </c>
       <c r="D2">
-        <v>14780.54915279455</v>
+        <v>14783.30709033404</v>
       </c>
       <c r="E2">
-        <v>0.7362587490977397</v>
+        <v>0.7363961293548553</v>
       </c>
       <c r="F2">
-        <v>1.924961069615654</v>
+        <v>1.925320252643367</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2877,16 +2877,16 @@
         <v>21388.05358732089</v>
       </c>
       <c r="C3">
-        <v>1820.657828634074</v>
+        <v>1820.997549473961</v>
       </c>
       <c r="D3">
-        <v>17307.72155586732</v>
+        <v>17310.9510444681</v>
       </c>
       <c r="E3">
-        <v>0.8092237793030199</v>
+        <v>0.8093747742772744</v>
       </c>
       <c r="F3">
-        <v>2.009142824086419</v>
+        <v>2.009517714786316</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2897,16 +2897,16 @@
         <v>22700.89697047428</v>
       </c>
       <c r="C4">
-        <v>2109.751061322436</v>
+        <v>2110.144724750694</v>
       </c>
       <c r="D4">
-        <v>20055.92887761848</v>
+        <v>20059.67116070751</v>
       </c>
       <c r="E4">
-        <v>0.8834861857531026</v>
+        <v>0.8836510375249905</v>
       </c>
       <c r="F4">
-        <v>2.176929635148023</v>
+        <v>2.17733583358487</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2917,16 +2917,16 @@
         <v>24013.74035362767</v>
       </c>
       <c r="C5">
-        <v>2421.936418687992</v>
+        <v>2422.388333518647</v>
       </c>
       <c r="D5">
-        <v>23023.65689005653</v>
+        <v>23027.95292851743</v>
       </c>
       <c r="E5">
-        <v>0.9587701270609612</v>
+        <v>0.958949026241082</v>
       </c>
       <c r="F5">
-        <v>2.343035475815619</v>
+        <v>2.343472668333186</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2937,16 +2937,16 @@
         <v>25326.58373678106</v>
       </c>
       <c r="C6">
-        <v>2756.908895272789</v>
+        <v>2757.423313408181</v>
       </c>
       <c r="D6">
-        <v>26208.00611945486</v>
+        <v>26212.8963331516</v>
       </c>
       <c r="E6">
-        <v>1.034802261206423</v>
+        <v>1.034995347401844</v>
       </c>
       <c r="F6">
-        <v>2.506423188857095</v>
+        <v>2.506890868273533</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2957,16 +2957,16 @@
         <v>26639.42711993445</v>
       </c>
       <c r="C7">
-        <v>3114.222736418222</v>
+        <v>3114.803826586276</v>
       </c>
       <c r="D7">
-        <v>29604.73908780304</v>
+        <v>29610.26310591856</v>
       </c>
       <c r="E7">
-        <v>1.111312903033475</v>
+        <v>1.111520265530073</v>
       </c>
       <c r="F7">
-        <v>2.666096516194592</v>
+        <v>2.666593989433909</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2977,16 +2977,16 @@
         <v>27952.27050308784</v>
       </c>
       <c r="C8">
-        <v>3493.297765322851</v>
+        <v>3493.949587994934</v>
       </c>
       <c r="D8">
-        <v>33208.34045972361</v>
+        <v>33214.53688232141</v>
       </c>
       <c r="E8">
-        <v>1.188037317256755</v>
+        <v>1.188258995942825</v>
       </c>
       <c r="F8">
-        <v>2.821109756942894</v>
+        <v>2.82163615446854</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2997,16 +2997,16 @@
         <v>29265.11388624123</v>
       </c>
       <c r="C9">
-        <v>3893.427020127941</v>
+        <v>3894.153503861738</v>
       </c>
       <c r="D9">
-        <v>37012.08964290693</v>
+        <v>37018.99581603935</v>
       </c>
       <c r="E9">
-        <v>1.264717088981085</v>
+        <v>1.264953075526679</v>
       </c>
       <c r="F9">
-        <v>2.970576929753685</v>
+        <v>2.971131216711757</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3017,16 +3017,16 @@
         <v>30577.95726939462</v>
       </c>
       <c r="C10">
-        <v>4313.785611659483</v>
+        <v>4314.590531094665</v>
       </c>
       <c r="D10">
-        <v>41008.14499247408</v>
+        <v>41015.79679900243</v>
       </c>
       <c r="E10">
-        <v>1.341101520653867</v>
+        <v>1.341351759950787</v>
       </c>
       <c r="F10">
-        <v>3.113680157325005</v>
+        <v>3.114261146251946</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3037,16 +3037,16 @@
         <v>31890.80065254801</v>
       </c>
       <c r="C11">
-        <v>4753.440676356173</v>
+        <v>4754.327632067194</v>
       </c>
       <c r="D11">
-        <v>45187.63842650722</v>
+        <v>45196.07009457648</v>
       </c>
       <c r="E11">
-        <v>1.416949010431848</v>
+        <v>1.417213402290839</v>
       </c>
       <c r="F11">
-        <v>3.24967703426154</v>
+        <v>3.250283399166617</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3057,16 +3057,16 @@
         <v>33203.6440357014</v>
       </c>
       <c r="C12">
-        <v>5211.362269050394</v>
+        <v>5212.334669431812</v>
       </c>
       <c r="D12">
-        <v>49540.77897610568</v>
+        <v>49550.02290694084</v>
       </c>
       <c r="E12">
-        <v>1.492028372633985</v>
+        <v>1.492306773728311</v>
       </c>
       <c r="F12">
-        <v>3.37790678621527</v>
+        <v>3.378537077812306</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3077,16 +3077,16 @@
         <v>34516.48741885479</v>
       </c>
       <c r="C13">
-        <v>5686.435017080914</v>
+        <v>5687.496062407267</v>
       </c>
       <c r="D13">
-        <v>54056.96357289053</v>
+        <v>54067.05018926504</v>
       </c>
       <c r="E13">
-        <v>1.566120066532658</v>
+        <v>1.56641229257096</v>
       </c>
       <c r="F13">
-        <v>3.497795077562317</v>
+        <v>3.498447739398501</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3097,16 +3097,16 @@
         <v>35829.33080200817</v>
       </c>
       <c r="C14">
-        <v>6177.470340977668</v>
+        <v>6178.623009743652</v>
       </c>
       <c r="D14">
-        <v>58724.89322251403</v>
+        <v>58735.85083889533</v>
       </c>
       <c r="E14">
-        <v>1.639017305319657</v>
+        <v>1.639323133425737</v>
       </c>
       <c r="F14">
-        <v>3.608857375423682</v>
+        <v>3.609530760636067</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3117,16 +3117,16 @@
         <v>37142.17418516156</v>
       </c>
       <c r="C15">
-        <v>6683.219037733414</v>
+        <v>6684.466075341983</v>
       </c>
       <c r="D15">
-        <v>63532.69262502906</v>
+        <v>63544.54734004436</v>
       </c>
       <c r="E15">
-        <v>1.710527022685996</v>
+        <v>1.710846193958959</v>
       </c>
       <c r="F15">
-        <v>3.710700827981413</v>
+        <v>3.711393216403899</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3137,16 +3137,16 @@
         <v>38455.01756831495</v>
       </c>
       <c r="C16">
-        <v>7202.384020288601</v>
+        <v>7203.727930116178</v>
       </c>
       <c r="D16">
-        <v>68468.03128026842</v>
+        <v>68480.80689176779</v>
       </c>
       <c r="E16">
-        <v>1.780470680025972</v>
+        <v>1.780802902250983</v>
       </c>
       <c r="F16">
-        <v>3.803024663064524</v>
+        <v>3.803734278409221</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3157,16 +3157,16 @@
         <v>39767.86095146834</v>
       </c>
       <c r="C17">
-        <v>7733.633010894392</v>
+        <v>7735.076047724549</v>
       </c>
       <c r="D17">
-        <v>73518.24415477589</v>
+        <v>73531.96209741093</v>
       </c>
       <c r="E17">
-        <v>1.848684902728252</v>
+        <v>1.84902985320602</v>
       </c>
       <c r="F17">
-        <v>3.885619157254692</v>
+        <v>3.886344184100927</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3177,16 +3177,16 @@
         <v>41080.70433462173</v>
       </c>
       <c r="C18">
-        <v>8275.61099585951</v>
+        <v>8277.15516164062</v>
       </c>
       <c r="D18">
-        <v>78670.45008038018</v>
+        <v>78685.12938527492</v>
       </c>
       <c r="E18">
-        <v>1.915021939243598</v>
+        <v>1.915379267705524</v>
       </c>
       <c r="F18">
-        <v>3.958363264878376</v>
+        <v>3.959101865219292</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3197,16 +3197,16 @@
         <v>42393.54771777512</v>
       </c>
       <c r="C19">
-        <v>8826.952264029303</v>
+        <v>8828.59930587847</v>
       </c>
       <c r="D19">
-        <v>83911.66619560192</v>
+        <v>83927.32347137769</v>
       </c>
       <c r="E19">
-        <v>1.979349941510527</v>
+        <v>1.979719273086172</v>
       </c>
       <c r="F19">
-        <v>4.021221029102788</v>
+        <v>4.021971358222238</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3217,16 +3217,16 @@
         <v>43706.39110092851</v>
       </c>
       <c r="C20">
-        <v>9386.291870259789</v>
+        <v>9388.043280605782</v>
       </c>
       <c r="D20">
-        <v>89228.91692088988</v>
+        <v>89245.56635502394</v>
       </c>
       <c r="E20">
-        <v>2.041553069775058</v>
+        <v>2.041934007979167</v>
       </c>
       <c r="F20">
-        <v>4.074236923192797</v>
+        <v>4.074997144673013</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3237,16 +3237,16 @@
         <v>45019.2344840819</v>
       </c>
       <c r="C21">
-        <v>9952.276387129132</v>
+        <v>9954.133405861507</v>
       </c>
       <c r="D21">
-        <v>94609.33616762771</v>
+        <v>94626.98954688355</v>
       </c>
       <c r="E21">
-        <v>2.10153142877363</v>
+        <v>2.101923558481257</v>
       </c>
       <c r="F21">
-        <v>4.117530288450366</v>
+        <v>4.118298588141747</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3257,16 +3257,16 @@
         <v>46332.07786723529</v>
       </c>
       <c r="C22">
-        <v>10523.57383214341</v>
+        <v>10525.53745061396</v>
       </c>
       <c r="D22">
-        <v>100040.2617091414</v>
+        <v>100058.9284576076</v>
       </c>
       <c r="E22">
-        <v>2.159200845595724</v>
+        <v>2.1596037359759</v>
       </c>
       <c r="F22">
-        <v>4.151289046456101</v>
+        <v>4.152063645273781</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3277,16 +3277,16 @@
         <v>47644.92125038867</v>
       </c>
       <c r="C23">
-        <v>11098.88268273853</v>
+        <v>11100.95364944489</v>
       </c>
       <c r="D23">
-        <v>105509.3208800218</v>
+        <v>105529.0081131424</v>
       </c>
       <c r="E23">
-        <v>2.214492502265623</v>
+        <v>2.214905709646472</v>
       </c>
       <c r="F23">
-        <v>4.175762867307474</v>
+        <v>4.176542032753138</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3297,16 +3297,16 @@
         <v>48957.76463354206</v>
       </c>
       <c r="C24">
-        <v>11676.93991652005</v>
+        <v>11679.11874428953</v>
       </c>
       <c r="D24">
-        <v>111004.5070090658</v>
+        <v>111025.2196019315</v>
       </c>
       <c r="E24">
-        <v>2.267352438166961</v>
+        <v>2.267775508807967</v>
       </c>
       <c r="F24">
-        <v>4.191255973226672</v>
+        <v>4.192038029567525</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3317,16 +3317,16 @@
         <v>50270.60801669546</v>
       </c>
       <c r="C25">
-        <v>12256.52803858644</v>
+        <v>12258.81501307109</v>
       </c>
       <c r="D25">
-        <v>116514.2462231273</v>
+        <v>116535.9868912326</v>
       </c>
       <c r="E25">
-        <v>2.317740938888814</v>
+        <v>2.318173411639056</v>
       </c>
       <c r="F25">
-        <v>4.1981197490316</v>
+        <v>4.198903086100577</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3337,16 +3337,16 @@
         <v>51583.45139984885</v>
       </c>
       <c r="C26">
-        <v>12836.48108074495</v>
+        <v>12838.87627003607</v>
       </c>
       <c r="D26">
-        <v>122027.4544774692</v>
+        <v>122050.2238681105</v>
       </c>
       <c r="E26">
-        <v>2.365631828928508</v>
+        <v>2.366073237752916</v>
       </c>
       <c r="F26">
-        <v>4.196745318512543</v>
+        <v>4.19752839912328</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -3357,16 +3357,16 @@
         <v>52896.29478300223</v>
       </c>
       <c r="C27">
-        <v>13415.68957839387</v>
+        <v>13418.19284356514</v>
       </c>
       <c r="D27">
-        <v>127533.5848675056</v>
+        <v>127557.3816600074</v>
       </c>
       <c r="E27">
-        <v>2.411011685992181</v>
+        <v>2.411461562351186</v>
       </c>
       <c r="F27">
-        <v>4.187556229787675</v>
+        <v>4.188337595784674</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -3377,16 +3377,16 @@
         <v>54209.13816615562</v>
       </c>
       <c r="C28">
-        <v>13993.10454939787</v>
+        <v>13995.71555579093</v>
       </c>
       <c r="D28">
-        <v>133022.6654531882</v>
+        <v>133047.4864661875</v>
       </c>
       <c r="E28">
-        <v>2.45387899445039</v>
+        <v>2.454336869521622</v>
       </c>
       <c r="F28">
-        <v>4.171001374286108</v>
+        <v>4.171779651273541</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -3397,16 +3397,16 @@
         <v>55521.98154930901</v>
       </c>
       <c r="C29">
-        <v>14567.74051515884</v>
+        <v>14570.45874423254</v>
       </c>
       <c r="D29">
-        <v>138485.327978216</v>
+        <v>138511.1682823043</v>
       </c>
       <c r="E29">
-        <v>2.494243254903058</v>
+        <v>2.494708661636881</v>
       </c>
       <c r="F29">
-        <v>4.147548244144125</v>
+        <v>4.148322144956671</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -3417,16 +3417,16 @@
         <v>56834.8249324624</v>
       </c>
       <c r="C30">
-        <v>15138.67761715116</v>
+        <v>15141.50237872579</v>
       </c>
       <c r="D30">
-        <v>143912.8279904564</v>
+        <v>143939.6810245776</v>
       </c>
       <c r="E30">
-        <v>2.532124065860499</v>
+        <v>2.532596540864216</v>
       </c>
       <c r="F30">
-        <v>4.117676612420775</v>
+        <v>4.118444939415117</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -3437,16 +3437,16 @@
         <v>58147.66831561578</v>
       </c>
       <c r="C31">
-        <v>15705.06289243724</v>
+        <v>15707.9933371767</v>
       </c>
       <c r="D31">
-        <v>149297.0569673801</v>
+        <v>149324.9146574897</v>
       </c>
       <c r="E31">
-        <v>2.567550192331372</v>
+        <v>2.568029277579611</v>
       </c>
       <c r="F31">
-        <v>4.081872700443356</v>
+        <v>4.082634346701258</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -3457,16 +3457,16 @@
         <v>59460.51169876917</v>
       </c>
       <c r="C32">
-        <v>16266.11077919513</v>
+        <v>16269.14591118351</v>
       </c>
       <c r="D32">
-        <v>154630.5471217594</v>
+        <v>154659.4000003806</v>
       </c>
       <c r="E32">
-        <v>2.600558634697391</v>
+        <v>2.60104387906877</v>
       </c>
       <c r="F32">
-        <v>4.040623877443352</v>
+        <v>4.041377826986029</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -3477,16 +3477,16 @@
         <v>60773.35508192256</v>
       </c>
       <c r="C33">
-        <v>16821.10292824764</v>
+        <v>16824.24161753056</v>
       </c>
       <c r="D33">
-        <v>159906.4696100063</v>
+        <v>159936.3069354525</v>
       </c>
       <c r="E33">
-        <v>2.631193709717889</v>
+        <v>2.631684670360196</v>
       </c>
       <c r="F33">
-        <v>3.994413919951355</v>
+        <v>3.995159247069048</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -3497,16 +3497,16 @@
         <v>62086.19846507596</v>
       </c>
       <c r="C34">
-        <v>17369.38739921173</v>
+        <v>17372.6283941877</v>
       </c>
       <c r="D34">
-        <v>165118.6268905273</v>
+        <v>165149.4367646979</v>
       </c>
       <c r="E34">
-        <v>2.659506153906459</v>
+        <v>2.660002397434527</v>
       </c>
       <c r="F34">
-        <v>3.943718842548631</v>
+        <v>3.944454710352238</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -3517,16 +3517,16 @@
         <v>63399.04184822935</v>
       </c>
       <c r="C35">
-        <v>17910.37732046082</v>
+        <v>17913.7192600226</v>
       </c>
       <c r="D35">
-        <v>170261.439984921</v>
+        <v>170293.2094687209</v>
       </c>
       <c r="E35">
-        <v>2.685552257911232</v>
+        <v>2.6860533614433</v>
       </c>
       <c r="F35">
-        <v>3.889003297757927</v>
+        <v>3.889728956058944</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -3537,16 +3537,16 @@
         <v>64711.88523138273</v>
       </c>
       <c r="C36">
-        <v>18443.54909090643</v>
+        <v>18446.99051624682</v>
       </c>
       <c r="D36">
-        <v>175329.9313835737</v>
+        <v>175362.6466091422</v>
       </c>
       <c r="E36">
-        <v>2.709393038955161</v>
+        <v>2.709898590994814</v>
       </c>
       <c r="F36">
-        <v>3.830717531204471</v>
+        <v>3.831432313826786</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -3557,16 +3557,16 @@
         <v>66024.72861453613</v>
       </c>
       <c r="C37">
-        <v>18968.44019896118</v>
+        <v>18971.97956497185</v>
       </c>
       <c r="D37">
-        <v>180319.704312064</v>
+        <v>180353.350591136</v>
       </c>
       <c r="E37">
-        <v>2.731093456889491</v>
+        <v>2.731603058061326</v>
       </c>
       <c r="F37">
-        <v>3.769294868694986</v>
+        <v>3.769998190317769</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -3577,16 +3577,16 @@
         <v>67337.57199768951</v>
       </c>
       <c r="C38">
-        <v>19484.64673023931</v>
+        <v>19488.28241644458</v>
       </c>
       <c r="D38">
-        <v>185226.9190386141</v>
+        <v>185261.48096646</v>
       </c>
       <c r="E38">
-        <v>2.750721678010155</v>
+        <v>2.75123494165808</v>
       </c>
       <c r="F38">
-        <v>3.705149704475157</v>
+        <v>3.705841057100386</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -3597,16 +3597,16 @@
         <v>68650.41538084291</v>
       </c>
       <c r="C39">
-        <v>19991.82063086661</v>
+        <v>19995.55095184662</v>
       </c>
       <c r="D39">
-        <v>190048.2668582899</v>
+        <v>190083.7284128008</v>
       </c>
       <c r="E39">
-        <v>2.768348389503312</v>
+        <v>2.768864942160921</v>
       </c>
       <c r="F39">
-        <v>3.638675954495886</v>
+        <v>3.639354903627287</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -3617,16 +3617,16 @@
         <v>69963.25876399629</v>
       </c>
       <c r="C40">
-        <v>20489.66678796553</v>
+        <v>20493.4900032346</v>
       </c>
       <c r="D40">
-        <v>194780.9423392127</v>
+        <v>194817.2869748079</v>
       </c>
       <c r="E40">
-        <v>2.784046166235022</v>
+        <v>2.784565647977829</v>
       </c>
       <c r="F40">
-        <v>3.570245934857153</v>
+        <v>3.570912115469755</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -3637,16 +3637,16 @@
         <v>71276.10214714968</v>
       </c>
       <c r="C41">
-        <v>20977.93998318581</v>
+        <v>20981.85430650241</v>
       </c>
       <c r="D41">
-        <v>199422.6143619048</v>
+        <v>199459.8250980343</v>
       </c>
       <c r="E41">
-        <v>2.797888890587709</v>
+        <v>2.798410955277114</v>
       </c>
       <c r="F41">
-        <v>3.500209623503493</v>
+        <v>3.500862735875512</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -3657,16 +3657,16 @@
         <v>72588.94553030307</v>
       </c>
       <c r="C42">
-        <v>21456.4417692663</v>
+        <v>21460.44537736014</v>
       </c>
       <c r="D42">
-        <v>203971.3964269454</v>
+        <v>204009.4559310528</v>
       </c>
       <c r="E42">
-        <v>2.809951225173746</v>
+        <v>2.810475540602622</v>
       </c>
       <c r="F42">
-        <v>3.428894262487472</v>
+        <v>3.429534067957993</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -3677,16 +3677,16 @@
         <v>73901.78891345646</v>
       </c>
       <c r="C43">
-        <v>21925.01731370882</v>
+        <v>21929.10835441905</v>
       </c>
       <c r="D43">
-        <v>208425.8166499834</v>
+        <v>208464.7073148699</v>
       </c>
       <c r="E43">
-        <v>2.82030813752104</v>
+        <v>2.820834385470626</v>
       </c>
       <c r="F43">
-        <v>3.356604258472387</v>
+        <v>3.357230575180493</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -3697,16 +3697,16 @@
         <v>75214.63229660985</v>
       </c>
       <c r="C44">
-        <v>22383.55224785833</v>
+        <v>22387.72884768378</v>
       </c>
       <c r="D44">
-        <v>212784.7878081454</v>
+        <v>212824.4918237447</v>
       </c>
       <c r="E44">
-        <v>2.829034475220538</v>
+        <v>2.829562351438064</v>
       </c>
       <c r="F44">
-        <v>3.283621340400762</v>
+        <v>3.284234039054021</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -3717,16 +3717,16 @@
         <v>76527.47567976324</v>
       </c>
       <c r="C45">
-        <v>22831.96955412558</v>
+        <v>22836.2298251942</v>
       </c>
       <c r="D45">
-        <v>217047.5777490363</v>
+        <v>217088.0771686683</v>
       </c>
       <c r="E45">
-        <v>2.836204589542365</v>
+        <v>2.83673380364844</v>
       </c>
       <c r="F45">
-        <v>3.210204935201793</v>
+        <v>3.210803934914804</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -3737,16 +3737,16 @@
         <v>77840.31906291662</v>
       </c>
       <c r="C46">
-        <v>23270.22651883954</v>
+        <v>23274.56856530923</v>
       </c>
       <c r="D46">
-        <v>221213.7804236374</v>
+        <v>221255.0572248562</v>
       </c>
       <c r="E46">
-        <v>2.841892005155261</v>
+        <v>2.842422280489634</v>
       </c>
       <c r="F46">
-        <v>3.136592724869784</v>
+        <v>3.137177989106773</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -3757,16 +3757,16 @@
         <v>79153.16244607003</v>
       </c>
       <c r="C47">
-        <v>23698.31177333784</v>
+        <v>23702.73369724518</v>
       </c>
       <c r="D47">
-        <v>225283.287758021</v>
+        <v>225325.3238982148</v>
       </c>
       <c r="E47">
-        <v>2.846169133311822</v>
+        <v>2.846700206725629</v>
       </c>
       <c r="F47">
-        <v>3.063001351055465</v>
+        <v>3.063572883704364</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -3777,16 +3777,16 @@
         <v>80466.0058292234</v>
       </c>
       <c r="C48">
-        <v>24116.24244143074</v>
+        <v>24120.7423480075</v>
       </c>
       <c r="D48">
-        <v>229256.2625362835</v>
+        <v>229299.0400032151</v>
       </c>
       <c r="E48">
-        <v>2.849107025677953</v>
+        <v>2.849638647280028</v>
       </c>
       <c r="F48">
-        <v>2.989627236327975</v>
+        <v>2.990185077927695</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -3797,16 +3797,16 @@
         <v>81778.84921237681</v>
       </c>
       <c r="C49">
-        <v>24524.06140732812</v>
+        <v>24528.63740980794</v>
       </c>
       <c r="D49">
-        <v>233133.1124286377</v>
+        <v>233176.6132861376</v>
       </c>
       <c r="E49">
-        <v>2.850775165876926</v>
+        <v>2.851307098741217</v>
       </c>
       <c r="F49">
-        <v>2.916647494380125</v>
+        <v>2.917191718517608</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3817,16 +3817,16 @@
         <v>83091.69259553018</v>
       </c>
       <c r="C50">
-        <v>24921.83471450663</v>
+        <v>24926.48493844633</v>
       </c>
       <c r="D50">
-        <v>236914.4652642593</v>
+        <v>236958.6716933065</v>
       </c>
       <c r="E50">
-        <v>2.851241295775503</v>
+        <v>2.851773315616071</v>
       </c>
       <c r="F50">
-        <v>2.844220904559633</v>
+        <v>2.844751614448841</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -3837,16 +3837,16 @@
         <v>84404.53597868356</v>
       </c>
       <c r="C51">
-        <v>25309.64910280694</v>
+        <v>25314.37168994836</v>
       </c>
       <c r="D51">
-        <v>240601.1456181929</v>
+        <v>240646.0399536257</v>
       </c>
       <c r="E51">
-        <v>2.850571273550475</v>
+        <v>2.851103168370016</v>
       </c>
       <c r="F51">
-        <v>2.77248892914429</v>
+        <v>2.773006254394975</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -3857,16 +3857,16 @@
         <v>85717.37936183697</v>
       </c>
       <c r="C52">
-        <v>25687.60968827726</v>
+        <v>25692.40279997608</v>
       </c>
       <c r="D52">
-        <v>244194.1527552455</v>
+        <v>244239.7175183573</v>
       </c>
       <c r="E52">
-        <v>2.848828960629254</v>
+        <v>2.849360530346516</v>
       </c>
       <c r="F52">
-        <v>2.701576754683835</v>
+        <v>2.702080848264559</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -3877,16 +3877,16 @@
         <v>87030.22274499034</v>
       </c>
       <c r="C53">
-        <v>26055.83778789427</v>
+        <v>26060.69960814299</v>
       </c>
       <c r="D53">
-        <v>247694.6399511283</v>
+        <v>247740.857878405</v>
       </c>
       <c r="E53">
-        <v>2.84607613468835</v>
+        <v>2.846607190749325</v>
       </c>
       <c r="F53">
-        <v>2.631594341458679</v>
+        <v>2.632085376855781</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3897,16 +3897,16 @@
         <v>88343.06612814374</v>
       </c>
       <c r="C54">
-        <v>26414.46888927231</v>
+        <v>26419.39762734438</v>
       </c>
       <c r="D54">
-        <v>251103.8951919013</v>
+        <v>251150.7492601571</v>
       </c>
       <c r="E54">
-        <v>2.842372426010991</v>
+        <v>2.842902790988224</v>
       </c>
       <c r="F54">
-        <v>2.562637467636612</v>
+        <v>2.563115636207962</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -3917,16 +3917,16 @@
         <v>89655.90951129713</v>
       </c>
       <c r="C55">
-        <v>26763.65076378548</v>
+        <v>26768.64465652738</v>
       </c>
       <c r="D55">
-        <v>254423.3232367437</v>
+        <v>254470.7966849102</v>
       </c>
       <c r="E55">
-        <v>2.837775274642492</v>
+        <v>2.838304781826406</v>
       </c>
       <c r="F55">
-        <v>2.494788757017665</v>
+        <v>2.495254265538035</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -3937,16 +3937,16 @@
         <v>90968.75289445052</v>
       </c>
       <c r="C56">
-        <v>27103.54172014493</v>
+        <v>27108.59903394231</v>
       </c>
       <c r="D56">
-        <v>257654.4290159335</v>
+        <v>257702.5053637509</v>
       </c>
       <c r="E56">
-        <v>2.832339905933255</v>
+        <v>2.832868398918897</v>
       </c>
       <c r="F56">
-        <v>2.428118681344674</v>
+        <v>2.4285717497383</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -3957,16 +3957,16 @@
         <v>92281.59627760391</v>
       </c>
       <c r="C57">
-        <v>27434.30899436408</v>
+        <v>27439.42802680757</v>
       </c>
       <c r="D57">
-        <v>260798.8023253726</v>
+        <v>260847.4653892246</v>
       </c>
       <c r="E57">
-        <v>2.826119322219252</v>
+        <v>2.826646654491502</v>
       </c>
       <c r="F57">
-        <v>2.362686530019737</v>
+        <v>2.36312738927387</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -3977,16 +3977,16 @@
         <v>93594.4396607573</v>
       </c>
       <c r="C58">
-        <v>27756.12727117633</v>
+        <v>27761.30635245138</v>
       </c>
       <c r="D58">
-        <v>263858.1037707377</v>
+        <v>263907.3376768644</v>
       </c>
       <c r="E58">
-        <v>2.819164308554211</v>
+        <v>2.819690343074051</v>
       </c>
       <c r="F58">
-        <v>2.298541341709127</v>
+        <v>2.298970231961261</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -3997,16 +3997,16 @@
         <v>94907.28304391068</v>
       </c>
       <c r="C59">
-        <v>28069.17733131404</v>
+        <v>28074.41482533843</v>
       </c>
       <c r="D59">
-        <v>266834.0519081073</v>
+        <v>266883.8411034184</v>
       </c>
       <c r="E59">
-        <v>2.811523450572823</v>
+        <v>2.812048059366945</v>
       </c>
       <c r="F59">
-        <v>2.235722793754943</v>
+        <v>2.236139962545971</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4017,16 +4017,16 @@
         <v>96220.12642706408</v>
       </c>
       <c r="C60">
-        <v>28373.64481858616</v>
+        <v>28378.93912391735</v>
       </c>
       <c r="D60">
-        <v>269728.4115234304</v>
+        <v>269778.740784131</v>
       </c>
       <c r="E60">
-        <v>2.803243162727369</v>
+        <v>2.803766226483046</v>
       </c>
       <c r="F60">
-        <v>2.174262046550118</v>
+        <v>2.174667747235286</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -4037,16 +4037,16 @@
         <v>97532.96981021746</v>
       </c>
       <c r="C61">
-        <v>28669.71912037766</v>
+        <v>28675.06867091137</v>
       </c>
       <c r="D61">
-        <v>272542.982990217</v>
+        <v>272593.8374284483</v>
       </c>
       <c r="E61">
-        <v>2.794367725298832</v>
+        <v>2.794889132965698</v>
       </c>
       <c r="F61">
-        <v>2.143874511540111</v>
+        <v>2.144274542143451</v>
       </c>
     </row>
   </sheetData>
@@ -4087,16 +4087,16 @@
         <v>30287.18702759737</v>
       </c>
       <c r="C2">
-        <v>3061.683650620165</v>
+        <v>3047.621403891404</v>
       </c>
       <c r="D2">
-        <v>29105.28671762604</v>
+        <v>28971.60676579572</v>
       </c>
       <c r="E2">
-        <v>0.9609768873915432</v>
+        <v>0.9565631413507334</v>
       </c>
       <c r="F2">
-        <v>2.091869939539614</v>
+        <v>2.082262026191564</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4107,16 +4107,16 @@
         <v>32287.2500206046</v>
       </c>
       <c r="C3">
-        <v>3501.799274915058</v>
+        <v>3485.715586651419</v>
       </c>
       <c r="D3">
-        <v>33289.1583698835</v>
+        <v>33136.26198612572</v>
       </c>
       <c r="E3">
-        <v>1.031031083435087</v>
+        <v>1.026295579988364</v>
       </c>
       <c r="F3">
-        <v>2.15003904337075</v>
+        <v>2.140163960588038</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4127,16 +4127,16 @@
         <v>34287.31301361182</v>
       </c>
       <c r="C4">
-        <v>3966.391690011721</v>
+        <v>3948.17413884292</v>
       </c>
       <c r="D4">
-        <v>37705.71376595904</v>
+        <v>37532.53223887554</v>
       </c>
       <c r="E4">
-        <v>1.099698706369617</v>
+        <v>1.094647814017254</v>
       </c>
       <c r="F4">
-        <v>2.262107679736299</v>
+        <v>2.251717868132796</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4147,16 +4147,16 @@
         <v>36287.37600661905</v>
       </c>
       <c r="C5">
-        <v>4453.664316685793</v>
+        <v>4433.20873289103</v>
       </c>
       <c r="D5">
-        <v>42337.87408275953</v>
+        <v>42143.41714361678</v>
       </c>
       <c r="E5">
-        <v>1.166738374112166</v>
+        <v>1.16137957001712</v>
       </c>
       <c r="F5">
-        <v>2.365393728567169</v>
+        <v>2.354529526377292</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4167,16 +4167,16 @@
         <v>38287.43899962628</v>
       </c>
       <c r="C6">
-        <v>4961.718137296184</v>
+        <v>4938.929073301575</v>
       </c>
       <c r="D6">
-        <v>47167.58668675621</v>
+        <v>46950.94698217567</v>
       </c>
       <c r="E6">
-        <v>1.231933707742025</v>
+        <v>1.226275462890948</v>
       </c>
       <c r="F6">
-        <v>2.459474127500929</v>
+        <v>2.448177816075377</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4187,16 +4187,16 @@
         <v>40287.50199263351</v>
       </c>
       <c r="C7">
-        <v>5488.578553562715</v>
+        <v>5463.369631081532</v>
       </c>
       <c r="D7">
-        <v>52176.08045210623</v>
+        <v>51936.43684408402</v>
       </c>
       <c r="E7">
-        <v>1.295093462524594</v>
+        <v>1.289145126287068</v>
       </c>
       <c r="F7">
-        <v>2.544051629487719</v>
+        <v>2.532366855426456</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4207,16 +4207,16 @@
         <v>42287.56498564074</v>
       </c>
       <c r="C8">
-        <v>6032.221470210703</v>
+        <v>6004.515607581998</v>
       </c>
       <c r="D8">
-        <v>57344.11371963246</v>
+        <v>57080.73344668876</v>
       </c>
       <c r="E8">
-        <v>1.356051447727112</v>
+        <v>1.349823132783153</v>
       </c>
       <c r="F8">
-        <v>2.618950121579768</v>
+        <v>2.606921340365708</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4227,16 +4227,16 @@
         <v>44287.62797864796</v>
       </c>
       <c r="C9">
-        <v>6590.598182957016</v>
+        <v>6560.327708174262</v>
       </c>
       <c r="D9">
-        <v>62652.21088951318</v>
+        <v>62364.45064117653</v>
       </c>
       <c r="E9">
-        <v>1.414666211514403</v>
+        <v>1.408168680229246</v>
       </c>
       <c r="F9">
-        <v>2.684108061368568</v>
+        <v>2.671780011147581</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4247,16 +4247,16 @@
         <v>46287.6909716552</v>
       </c>
       <c r="C10">
-        <v>7161.658700294107</v>
+        <v>7128.765356917394</v>
       </c>
       <c r="D10">
-        <v>68080.88412518376</v>
+        <v>67768.19009819419</v>
       </c>
       <c r="E10">
-        <v>1.470820485879796</v>
+        <v>1.464065039228093</v>
       </c>
       <c r="F10">
-        <v>2.739570302759328</v>
+        <v>2.726987515664265</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4267,16 +4267,16 @@
         <v>48287.75396466242</v>
       </c>
       <c r="C11">
-        <v>7743.373191869883</v>
+        <v>7707.808046426167</v>
       </c>
       <c r="D11">
-        <v>73610.83724809426</v>
+        <v>73272.74426612216</v>
       </c>
       <c r="E11">
-        <v>1.524420400707881</v>
+        <v>1.517418770807689</v>
       </c>
       <c r="F11">
-        <v>2.785478629022353</v>
+        <v>2.772684985978571</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4287,16 +4287,16 @@
         <v>50287.81695766964</v>
       </c>
       <c r="C12">
-        <v>8333.751326704767</v>
+        <v>8295.474587268107</v>
       </c>
       <c r="D12">
-        <v>79223.14957262395</v>
+        <v>78859.27936163916</v>
       </c>
       <c r="E12">
-        <v>1.57539448648787</v>
+        <v>1.568158733715164</v>
       </c>
       <c r="F12">
-        <v>2.822061333841242</v>
+        <v>2.80909966722616</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4307,16 +4307,16 @@
         <v>52287.87995067688</v>
       </c>
       <c r="C13">
-        <v>8930.859337414253</v>
+        <v>8889.840093810444</v>
       </c>
       <c r="D13">
-        <v>84899.43812371926</v>
+        <v>84509.4968422981</v>
       </c>
       <c r="E13">
-        <v>1.623692492482098</v>
+        <v>1.616234908013403</v>
       </c>
       <c r="F13">
-        <v>2.849622193604552</v>
+        <v>2.836533940557208</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4327,16 +4327,16 @@
         <v>54287.9429436841</v>
       </c>
       <c r="C14">
-        <v>9532.834718111853</v>
+        <v>9489.050614615908</v>
       </c>
       <c r="D14">
-        <v>90621.99735958506</v>
+        <v>90205.77248747405</v>
       </c>
       <c r="E14">
-        <v>1.669284051775406</v>
+        <v>1.661617066261831</v>
       </c>
       <c r="F14">
-        <v>2.868529159983445</v>
+        <v>2.855354067648824</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4347,16 +4347,16 @@
         <v>56288.00593669133</v>
       </c>
       <c r="C15">
-        <v>10137.89853061769</v>
+        <v>10091.33538212918</v>
       </c>
       <c r="D15">
-        <v>96373.91615820923</v>
+        <v>95931.27284757223</v>
       </c>
       <c r="E15">
-        <v>1.71215722700505</v>
+        <v>1.704293325925753</v>
       </c>
       <c r="F15">
-        <v>2.879203074602914</v>
+        <v>2.865978957209514</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4367,16 +4367,16 @@
         <v>58288.06892969856</v>
       </c>
       <c r="C16">
-        <v>10744.36535364412</v>
+        <v>10695.01671616608</v>
       </c>
       <c r="D16">
-        <v>102139.1723973169</v>
+        <v>101670.0493895784</v>
       </c>
       <c r="E16">
-        <v>1.75231697108558</v>
+        <v>1.744268617171089</v>
       </c>
       <c r="F16">
-        <v>2.882106671038374</v>
+        <v>2.868869217489396</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4387,16 +4387,16 @@
         <v>60288.13192270578</v>
       </c>
       <c r="C17">
-        <v>11350.65096118964</v>
+        <v>11298.51766704085</v>
       </c>
       <c r="D17">
-        <v>107902.7059474954</v>
+        <v>107407.1111549285</v>
       </c>
       <c r="E17">
-        <v>1.789783536266065</v>
+        <v>1.781563099228767</v>
       </c>
       <c r="F17">
-        <v>2.877734086951566</v>
+        <v>2.864516716586641</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4407,16 +4407,16 @@
         <v>62288.19491571302</v>
       </c>
       <c r="C18">
-        <v>11955.27785856985</v>
+        <v>11900.36752617021</v>
       </c>
       <c r="D18">
-        <v>113650.4712993715</v>
+        <v>113128.4771449695</v>
       </c>
       <c r="E18">
-        <v>1.824590862733472</v>
+        <v>1.816210556399209</v>
       </c>
       <c r="F18">
-        <v>2.866601064061821</v>
+        <v>2.853434827430025</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4427,16 +4427,16 @@
         <v>64288.25790872025</v>
       </c>
       <c r="C19">
-        <v>12556.87883708869</v>
+        <v>12499.20536441801</v>
       </c>
       <c r="D19">
-        <v>119369.4713553858</v>
+        <v>118821.20995753</v>
       </c>
       <c r="E19">
-        <v>1.856784975024097</v>
+        <v>1.848256801829013</v>
       </c>
       <c r="F19">
-        <v>2.849235968507659</v>
+        <v>2.83614948938383</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4447,16 +4447,16 @@
         <v>66288.32090172748</v>
       </c>
       <c r="C20">
-        <v>13154.19873155605</v>
+        <v>13093.78178154071</v>
       </c>
       <c r="D20">
-        <v>125047.774137286</v>
+        <v>124473.4324176754</v>
       </c>
       <c r="E20">
-        <v>1.886422411010674</v>
+        <v>1.877758113713687</v>
       </c>
       <c r="F20">
-        <v>2.826171721134485</v>
+        <v>2.813191175599547</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4467,16 +4467,16 @@
         <v>68288.3838947347</v>
       </c>
       <c r="C21">
-        <v>13746.09457933069</v>
+        <v>13682.95906449973</v>
       </c>
       <c r="D21">
-        <v>130674.5142980351</v>
+        <v>130074.3290826723</v>
       </c>
       <c r="E21">
-        <v>1.913568704444192</v>
+        <v>1.904779724809121</v>
       </c>
       <c r="F21">
-        <v>2.797938687941175</v>
+        <v>2.785087816116508</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4487,16 +4487,16 @@
         <v>70288.44688774191</v>
       </c>
       <c r="C22">
-        <v>14331.53438623167</v>
+        <v>14265.70995904106</v>
       </c>
       <c r="D22">
-        <v>136239.8813901946</v>
+        <v>135614.1345642552</v>
       </c>
       <c r="E22">
-        <v>1.938296938155201</v>
+        <v>1.929394382278006</v>
       </c>
       <c r="F22">
-        <v>2.765058546406209</v>
+        <v>2.752358692359835</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4507,16 +4507,16 @@
         <v>72288.50988074916</v>
       </c>
       <c r="C23">
-        <v>14909.59470461222</v>
+        <v>14841.11525889299</v>
       </c>
       <c r="D23">
-        <v>141735.0968423659</v>
+        <v>141084.1106108137</v>
       </c>
       <c r="E23">
-        <v>1.960686381226829</v>
+        <v>1.951680991122286</v>
       </c>
       <c r="F23">
-        <v>2.728039114288039</v>
+        <v>2.715509289692012</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4527,16 +4527,16 @@
         <v>74288.57287375638</v>
       </c>
       <c r="C24">
-        <v>15479.45722329869</v>
+        <v>15408.36041136737</v>
       </c>
       <c r="D24">
-        <v>147152.3815421221</v>
+        <v>146476.5138392159</v>
       </c>
       <c r="E24">
-        <v>1.980821219869012</v>
+        <v>1.97172335088646</v>
       </c>
       <c r="F24">
-        <v>2.687370103953426</v>
+        <v>2.675027071241469</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4547,16 +4547,16 @@
         <v>76288.63586676362</v>
       </c>
       <c r="C25">
-        <v>16040.40455914189</v>
+        <v>15966.73132824028</v>
       </c>
       <c r="D25">
-        <v>152484.9158292284</v>
+        <v>151784.5559117789</v>
       </c>
       <c r="E25">
-        <v>1.998789388442334</v>
+        <v>1.989608992050496</v>
       </c>
       <c r="F25">
-        <v>2.643519747208111</v>
+        <v>2.63137811823542</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4567,16 +4567,16 @@
         <v>78288.69885977084</v>
       </c>
       <c r="C26">
-        <v>16591.81542672928</v>
+        <v>16515.60957764965</v>
       </c>
       <c r="D26">
-        <v>157726.7935774717</v>
+        <v>157002.3578289993</v>
       </c>
       <c r="E26">
-        <v>2.014681504159224</v>
+        <v>2.005428115623926</v>
       </c>
       <c r="F26">
-        <v>2.596932222622883</v>
+        <v>2.585004569142089</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4587,16 +4587,16 @@
         <v>80288.76185277806</v>
       </c>
       <c r="C27">
-        <v>17133.15934738913</v>
+        <v>17054.46711740077</v>
       </c>
       <c r="D27">
-        <v>162872.9718968604</v>
+        <v>162124.8998627702</v>
       </c>
       <c r="E27">
-        <v>2.028589906461796</v>
+        <v>2.019272636935807</v>
       </c>
       <c r="F27">
-        <v>2.548025808941346</v>
+        <v>2.536322781559872</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4607,16 +4607,16 @@
         <v>82288.8248457853</v>
       </c>
       <c r="C28">
-        <v>17663.99104188108</v>
+        <v>17582.86071341124</v>
       </c>
       <c r="D28">
-        <v>167919.2178288535</v>
+        <v>167147.9684964374</v>
       </c>
       <c r="E28">
-        <v>2.040607799947869</v>
+        <v>2.031235332497259</v>
       </c>
       <c r="F28">
-        <v>2.497191683703464</v>
+        <v>2.485722136358785</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4627,16 +4627,16 @@
         <v>84288.88783879252</v>
       </c>
       <c r="C29">
-        <v>18183.94463387692</v>
+        <v>18100.42616981486</v>
       </c>
       <c r="D29">
-        <v>172862.0532429019</v>
+        <v>172068.1015744303</v>
       </c>
       <c r="E29">
-        <v>2.050828497980786</v>
+        <v>2.041409087085367</v>
       </c>
       <c r="F29">
-        <v>2.444793285062347</v>
+        <v>2.433564402428312</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4647,16 +4647,16 @@
         <v>86288.95083179977</v>
       </c>
       <c r="C30">
-        <v>18692.72777411213</v>
+        <v>18606.87248010098</v>
       </c>
       <c r="D30">
-        <v>177698.698978865</v>
+        <v>176882.5327012306</v>
       </c>
       <c r="E30">
-        <v>2.059344762752386</v>
+        <v>2.049886236837228</v>
       </c>
       <c r="F30">
-        <v>2.391166156258612</v>
+        <v>2.38018358186626</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4667,16 +4667,16 @@
         <v>88289.01382480699</v>
       </c>
       <c r="C31">
-        <v>19190.11577842349</v>
+        <v>19101.97599207587</v>
       </c>
       <c r="D31">
-        <v>182427.0191214303</v>
+        <v>181589.1357717385</v>
       </c>
       <c r="E31">
-        <v>2.066248236540761</v>
+        <v>2.056758003119937</v>
       </c>
       <c r="F31">
-        <v>2.336618195729196</v>
+        <v>2.32588615893872</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4687,16 +4687,16 @@
         <v>90289.0768178142</v>
       </c>
       <c r="C32">
-        <v>19675.94585714313</v>
+        <v>19585.57466376106</v>
       </c>
       <c r="D32">
-        <v>187045.4661429955</v>
+        <v>186186.3703661127</v>
       </c>
       <c r="E32">
-        <v>2.071628958178595</v>
+        <v>2.062114011219769</v>
       </c>
       <c r="F32">
-        <v>2.281430240807185</v>
+        <v>2.270951681098974</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4707,16 +4707,16 @@
         <v>92289.13981082145</v>
       </c>
       <c r="C33">
-        <v>20150.11149874929</v>
+        <v>20057.56247283994</v>
       </c>
       <c r="D33">
-        <v>191553.0275129623</v>
+        <v>190673.2286042858</v>
       </c>
       <c r="E33">
-        <v>2.075574958284546</v>
+        <v>2.066041887432656</v>
       </c>
       <c r="F33">
-        <v>2.225856918931735</v>
+        <v>2.215633606287863</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4727,16 +4727,16 @@
         <v>94289.20280382867</v>
       </c>
       <c r="C34">
-        <v>20612.55705743826</v>
+        <v>20517.88402908876</v>
       </c>
       <c r="D34">
-        <v>195949.1742455645</v>
+        <v>195049.1839301117</v>
       </c>
       <c r="E34">
-        <v>2.078171926569814</v>
+        <v>2.068626927898808</v>
       </c>
       <c r="F34">
-        <v>2.170127706815625</v>
+        <v>2.160160357236578</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4747,16 +4747,16 @@
         <v>96289.2657968359</v>
       </c>
       <c r="C35">
-        <v>21063.27258245892</v>
+        <v>20966.52942745997</v>
       </c>
       <c r="D35">
-        <v>200233.8117459654</v>
+        <v>199314.1421832261</v>
       </c>
       <c r="E35">
-        <v>2.079502944476135</v>
+        <v>2.069951832468699</v>
       </c>
       <c r="F35">
-        <v>2.1144481447821</v>
+        <v>2.104736530226141</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4767,16 +4767,16 @@
         <v>98289.32878984312</v>
       </c>
       <c r="C36">
-        <v>21502.28891666155</v>
+        <v>21403.52936914332</v>
       </c>
       <c r="D36">
-        <v>204407.2332155874</v>
+        <v>203468.3952183832</v>
       </c>
       <c r="E36">
-        <v>2.079648276494387</v>
+        <v>2.070096496980137</v>
       </c>
       <c r="F36">
-        <v>2.059001160214964</v>
+        <v>2.049544212458819</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4787,16 +4787,16 @@
         <v>100289.3917828503</v>
       </c>
       <c r="C37">
-        <v>21929.67308272267</v>
+        <v>21828.95056898162</v>
       </c>
       <c r="D37">
-        <v>208470.0757921752</v>
+        <v>207512.5772469681</v>
       </c>
       <c r="E37">
-        <v>2.078685213721916</v>
+        <v>2.069137857534132</v>
       </c>
       <c r="F37">
-        <v>2.003948460565351</v>
+        <v>1.994744368666931</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4807,16 +4807,16 @@
         <v>102289.4547758576</v>
       </c>
       <c r="C38">
-        <v>22345.52396785275</v>
+        <v>22242.89145999853</v>
       </c>
       <c r="D38">
-        <v>212423.2795273285</v>
+        <v>211447.6240029438</v>
       </c>
       <c r="E38">
-        <v>2.076687963512978</v>
+        <v>2.067149780652167</v>
       </c>
       <c r="F38">
-        <v>1.949431962485592</v>
+        <v>1.940478263682698</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4827,16 +4827,16 @@
         <v>104289.5177688648</v>
       </c>
       <c r="C39">
-        <v>22749.96831138166</v>
+        <v>22645.47819941293</v>
       </c>
       <c r="D39">
-        <v>216268.049243281</v>
+        <v>215274.7347748215</v>
       </c>
       <c r="E39">
-        <v>2.073727579435092</v>
+        <v>2.064202993554265</v>
       </c>
       <c r="F39">
-        <v>1.895575229316954</v>
+        <v>1.886868893323624</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4847,16 +4847,16 @@
         <v>106289.580761872</v>
       </c>
       <c r="C40">
-        <v>23143.15699434232</v>
+        <v>23036.86097526439</v>
       </c>
       <c r="D40">
-        <v>220005.8192605646</v>
+        <v>218995.33729533</v>
       </c>
       <c r="E40">
-        <v>2.069871926143532</v>
+        <v>2.060365049194808</v>
       </c>
       <c r="F40">
-        <v>1.842484894287753</v>
+        <v>1.834022401053927</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4867,16 +4867,16 @@
         <v>108289.6437548793</v>
       </c>
       <c r="C41">
-        <v>23525.26162591902</v>
+        <v>23417.21060853996</v>
       </c>
       <c r="D41">
-        <v>223638.2209477605</v>
+        <v>222611.0554402099</v>
       </c>
       <c r="E41">
-        <v>2.065185674208887</v>
+        <v>2.055700321113852</v>
       </c>
       <c r="F41">
-        <v>1.790252051357895</v>
+        <v>1.782029462440918</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4887,16 +4887,16 @@
         <v>110289.7067478865</v>
       </c>
       <c r="C42">
-        <v>23896.47141828016</v>
+        <v>23786.71544236064</v>
       </c>
       <c r="D42">
-        <v>227167.053012717</v>
+        <v>226123.6796558833</v>
       </c>
       <c r="E42">
-        <v>2.059730320364373</v>
+        <v>2.050270023591449</v>
       </c>
       <c r="F42">
-        <v>1.738953599674941</v>
+        <v>1.73096662343605</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4907,16 +4907,16 @@
         <v>112289.7697408937</v>
       </c>
       <c r="C43">
-        <v>24256.99033875595</v>
+        <v>24145.5785072391</v>
       </c>
       <c r="D43">
-        <v>230594.2544302937</v>
+        <v>229535.1400115402</v>
       </c>
       <c r="E43">
-        <v>2.053564229068997</v>
+        <v>2.044132253019912</v>
       </c>
       <c r="F43">
-        <v>1.688653531099135</v>
+        <v>1.680897581986338</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4927,16 +4927,16 @@
         <v>114289.8327339009</v>
       </c>
       <c r="C44">
-        <v>24607.03452644456</v>
+        <v>24494.01494955133</v>
       </c>
       <c r="D44">
-        <v>233921.8798838417</v>
+        <v>232847.4817534157</v>
       </c>
       <c r="E44">
-        <v>2.046742691701002</v>
+        <v>2.037342046825377</v>
       </c>
       <c r="F44">
-        <v>1.639404153246367</v>
+        <v>1.63187440545991</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4947,16 +4947,16 @@
         <v>116289.8957269082</v>
       </c>
       <c r="C45">
-        <v>24946.82995903029</v>
+        <v>24832.24970907099</v>
       </c>
       <c r="D45">
-        <v>237152.0775852744</v>
+        <v>236062.8432267322</v>
       </c>
       <c r="E45">
-        <v>2.039318000096892</v>
+        <v>2.029951456669076</v>
       </c>
       <c r="F45">
-        <v>1.591247243020474</v>
+        <v>1.583938678880189</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -4967,16 +4967,16 @@
         <v>118289.9587199154</v>
       </c>
       <c r="C46">
-        <v>25276.61035478082</v>
+        <v>25160.51543060284</v>
       </c>
       <c r="D46">
-        <v>240287.0693308217</v>
+        <v>239183.4360230577</v>
       </c>
       <c r="E46">
-        <v>2.031339531530049</v>
+        <v>2.022009633035645</v>
       </c>
       <c r="F46">
-        <v>1.544215127705821</v>
+        <v>1.537122581053035</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4987,16 +4987,16 @@
         <v>120290.0217129226</v>
       </c>
       <c r="C47">
-        <v>25596.61529427483</v>
+        <v>25479.05059433714</v>
       </c>
       <c r="D47">
-        <v>243329.1326456071</v>
+        <v>242211.5272068921</v>
       </c>
       <c r="E47">
-        <v>2.022853842576592</v>
+        <v>2.013562918667855</v>
       </c>
       <c r="F47">
-        <v>1.498331692412895</v>
+        <v>1.491449887385137</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -5007,16 +5007,16 @@
         <v>122290.0847059299</v>
       </c>
       <c r="C48">
-        <v>25907.08854631911</v>
+        <v>25788.09784945583</v>
       </c>
       <c r="D48">
-        <v>246280.5848693116</v>
+        <v>245149.4234744253</v>
       </c>
       <c r="E48">
-        <v>2.013904769642942</v>
+        <v>2.004654948632463</v>
       </c>
       <c r="F48">
-        <v>1.453613314054601</v>
+        <v>1.446936899570592</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -5027,16 +5027,16 @@
         <v>124290.1476989371</v>
       </c>
       <c r="C49">
-        <v>26208.27658268104</v>
+        <v>26087.90253568679</v>
       </c>
       <c r="D49">
-        <v>249143.7690367735</v>
+        <v>247999.4570989876</v>
       </c>
       <c r="E49">
-        <v>2.00453353422883</v>
+        <v>1.995326755099741</v>
       </c>
       <c r="F49">
-        <v>1.410069723127158</v>
+        <v>1.403593303413663</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -5047,16 +5047,16 @@
         <v>126290.2106919443</v>
       </c>
       <c r="C50">
-        <v>26500.42726663173</v>
+        <v>26378.71137787049</v>
       </c>
       <c r="D50">
-        <v>251921.0414108848</v>
+        <v>250763.9735212062</v>
       </c>
       <c r="E50">
-        <v>1.994778851271281</v>
+        <v>1.98561687518985</v>
       </c>
       <c r="F50">
-        <v>1.367704795413331</v>
+        <v>1.361422956895715</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -5067,16 +5067,16 @@
         <v>128290.2736849515</v>
       </c>
       <c r="C51">
-        <v>26783.78870081677</v>
+        <v>26660.77133912246</v>
       </c>
       <c r="D51">
-        <v>254614.760530103</v>
+        <v>253445.3204468228</v>
       </c>
       <c r="E51">
-        <v>1.984677039160213</v>
+        <v>1.975561460483126</v>
       </c>
       <c r="F51">
-        <v>1.326517276356851</v>
+        <v>1.32042461122265</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -5087,16 +5087,16 @@
         <v>130290.3366779588</v>
       </c>
       <c r="C52">
-        <v>27058.60822060657</v>
+        <v>26934.32861880708</v>
       </c>
       <c r="D52">
-        <v>257227.2776389369</v>
+        <v>256045.838321131</v>
       </c>
       <c r="E52">
-        <v>1.974262130235573</v>
+        <v>1.965194387009718</v>
       </c>
       <c r="F52">
-        <v>1.286501441309512</v>
+        <v>1.280592568039438</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -5107,16 +5107,16 @@
         <v>132290.399670966</v>
       </c>
       <c r="C53">
-        <v>27325.13151979034</v>
+        <v>27199.62778224733</v>
       </c>
       <c r="D53">
-        <v>259760.9283765302</v>
+        <v>258567.8520557343</v>
       </c>
       <c r="E53">
-        <v>1.963565980771169</v>
+        <v>1.954547364728256</v>
       </c>
       <c r="F53">
-        <v>1.247647695154908</v>
+        <v>1.241917276299813</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -5127,16 +5127,16 @@
         <v>134290.4626639732</v>
       </c>
       <c r="C54">
-        <v>27583.60189624018</v>
+        <v>27456.91100985344</v>
       </c>
       <c r="D54">
-        <v>262218.0256057171</v>
+        <v>261013.6638905381</v>
       </c>
       <c r="E54">
-        <v>1.952618379622752</v>
+        <v>1.943650045674923</v>
       </c>
       <c r="F54">
-        <v>1.209943114994367</v>
+        <v>1.20438587245974</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -5147,16 +5147,16 @@
         <v>136290.5256569805</v>
       </c>
       <c r="C55">
-        <v>27834.25960596021</v>
+        <v>27706.4174541389</v>
       </c>
       <c r="D55">
-        <v>264600.8532724185</v>
+        <v>263385.5472813493</v>
       </c>
       <c r="E55">
-        <v>1.941447154869538</v>
+        <v>1.932530130115169</v>
       </c>
       <c r="F55">
-        <v>1.173371939663482</v>
+        <v>1.167982667745466</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -5167,16 +5167,16 @@
         <v>138290.5886499877</v>
       </c>
       <c r="C56">
-        <v>28077.34131473267</v>
+        <v>27948.38269388513</v>
       </c>
       <c r="D56">
-        <v>266911.6611928252</v>
+        <v>265685.7417110013</v>
       </c>
       <c r="E56">
-        <v>1.9300782779107</v>
+        <v>1.921213470162092</v>
       </c>
       <c r="F56">
-        <v>1.137916009850715</v>
+        <v>1.132689586250779</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -5187,16 +5187,16 @@
         <v>140290.6516429949</v>
       </c>
       <c r="C57">
-        <v>28313.07963736314</v>
+        <v>28183.03827550297</v>
       </c>
       <c r="D57">
-        <v>269152.6606733242</v>
+        <v>267916.4483293989</v>
       </c>
       <c r="E57">
-        <v>1.91853596459336</v>
+        <v>1.909724170439953</v>
       </c>
       <c r="F57">
-        <v>1.103555162533511</v>
+        <v>1.098486557561464</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -5207,16 +5207,16 @@
         <v>142290.7146360021</v>
       </c>
       <c r="C58">
-        <v>28541.70275530022</v>
+        <v>28410.61133240853</v>
       </c>
       <c r="D58">
-        <v>271326.0208754759</v>
+        <v>270079.8263351904</v>
       </c>
       <c r="E58">
-        <v>1.906842773047859</v>
+        <v>1.89808468547009</v>
       </c>
       <c r="F58">
-        <v>1.070267583342525</v>
+        <v>1.065351867501103</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -5227,16 +5227,16 @@
         <v>144290.7776290094</v>
       </c>
       <c r="C59">
-        <v>28763.43410415093</v>
+        <v>28631.32427397395</v>
       </c>
       <c r="D59">
-        <v>273433.8658454415</v>
+        <v>272177.9900188391</v>
       </c>
       <c r="E59">
-        <v>1.895019697991206</v>
+        <v>1.886315913541229</v>
       </c>
       <c r="F59">
-        <v>1.038030120326147</v>
+        <v>1.03326247045449</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -5247,16 +5247,16 @@
         <v>146290.8406220166</v>
       </c>
       <c r="C60">
-        <v>28978.49212332832</v>
+        <v>28845.39453632478</v>
       </c>
       <c r="D60">
-        <v>275478.2721340582</v>
+        <v>274213.006393629</v>
       </c>
       <c r="E60">
-        <v>1.883086261332202</v>
+        <v>1.874437286898468</v>
       </c>
       <c r="F60">
-        <v>1.006818562424545</v>
+        <v>1.002194266562669</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -5267,16 +5267,16 @@
         <v>148290.9036150238</v>
       </c>
       <c r="C61">
-        <v>29187.09006074514</v>
+        <v>29053.03438793072</v>
       </c>
       <c r="D61">
-        <v>277461.2669401977</v>
+        <v>276186.8933475512</v>
       </c>
       <c r="E61">
-        <v>1.87106059897316</v>
+        <v>1.862466858146313</v>
       </c>
       <c r="F61">
-        <v>0.9914661753517496</v>
+        <v>0.9869123926713735</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/response_curves.xlsx
+++ b/outputs/response_curves.xlsx
@@ -397,16 +397,16 @@
         <v>69063.60521282686</v>
       </c>
       <c r="C2">
-        <v>10054.00330671036</v>
+        <v>10096.61763643983</v>
       </c>
       <c r="D2">
-        <v>95576.38289719849</v>
+        <v>95981.4875476428</v>
       </c>
       <c r="E2">
-        <v>1.383889280072618</v>
+        <v>1.389754954897961</v>
       </c>
       <c r="F2">
-        <v>2.630867649918145</v>
+        <v>2.642018696728857</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -417,16 +417,16 @@
         <v>73100.70547741983</v>
       </c>
       <c r="C3">
-        <v>11171.27030165239</v>
+        <v>11218.62021607045</v>
       </c>
       <c r="D3">
-        <v>106197.4593827921</v>
+        <v>106647.5819272664</v>
       </c>
       <c r="E3">
-        <v>1.452755601867558</v>
+        <v>1.458913169589163</v>
       </c>
       <c r="F3">
-        <v>2.649337584566363</v>
+        <v>2.660566916997356</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -437,16 +437,16 @@
         <v>77137.8057420128</v>
       </c>
       <c r="C4">
-        <v>12304.224781582</v>
+        <v>12356.37677277518</v>
       </c>
       <c r="D4">
-        <v>116967.6658244964</v>
+        <v>117463.4383567975</v>
       </c>
       <c r="E4">
-        <v>1.516346812037854</v>
+        <v>1.522773913865966</v>
       </c>
       <c r="F4">
-        <v>2.677338174591661</v>
+        <v>2.688686188739736</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -457,16 +457,16 @@
         <v>81174.90600660577</v>
       </c>
       <c r="C5">
-        <v>13445.27414738951</v>
+        <v>13502.26252588322</v>
       </c>
       <c r="D5">
-        <v>127814.8246888898</v>
+        <v>128356.5733752037</v>
       </c>
       <c r="E5">
-        <v>1.574560796885784</v>
+        <v>1.581234641217305</v>
       </c>
       <c r="F5">
-        <v>2.688122515954567</v>
+        <v>2.699516240001945</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -477,16 +477,16 @@
         <v>85212.00627119873</v>
       </c>
       <c r="C6">
-        <v>14587.38833451102</v>
+        <v>14649.21761359666</v>
       </c>
       <c r="D6">
-        <v>138672.1060653334</v>
+        <v>139259.8738103672</v>
       </c>
       <c r="E6">
-        <v>1.627377550811216</v>
+        <v>1.634275261248442</v>
       </c>
       <c r="F6">
-        <v>2.683106649545761</v>
+        <v>2.694479113625492</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -497,16 +497,16 @@
         <v>89249.1065357917</v>
       </c>
       <c r="C7">
-        <v>15724.17746169362</v>
+        <v>15790.82507087334</v>
       </c>
       <c r="D7">
-        <v>149478.7658185145</v>
+        <v>150112.3380603191</v>
       </c>
       <c r="E7">
-        <v>1.674848876594286</v>
+        <v>1.681947796307847</v>
       </c>
       <c r="F7">
-        <v>2.663853673299013</v>
+        <v>2.675144532802635</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -517,16 +517,16 @@
         <v>93286.20680038465</v>
       </c>
       <c r="C8">
-        <v>16849.93908549591</v>
+        <v>16921.35828421762</v>
       </c>
       <c r="D8">
-        <v>160180.5948039581</v>
+        <v>160859.527212771</v>
       </c>
       <c r="E8">
-        <v>1.717087662774361</v>
+        <v>1.724365613417864</v>
       </c>
       <c r="F8">
-        <v>2.632006225647995</v>
+        <v>2.643162098361398</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -537,16 +537,16 @@
         <v>97323.30706497761</v>
       </c>
       <c r="C9">
-        <v>17959.67850370912</v>
+        <v>18035.80138115849</v>
       </c>
       <c r="D9">
-        <v>170730.1118784621</v>
+        <v>171453.7588736328</v>
       </c>
       <c r="E9">
-        <v>1.754257197245411</v>
+        <v>1.761692692575297</v>
       </c>
       <c r="F9">
-        <v>2.589227856377319</v>
+        <v>2.600202411114407</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -557,16 +557,16 @@
         <v>101360.4073295706</v>
       </c>
       <c r="C10">
-        <v>19049.10621304403</v>
+        <v>19129.84667716069</v>
       </c>
       <c r="D10">
-        <v>181086.5397321029</v>
+        <v>181854.0828965815</v>
       </c>
       <c r="E10">
-        <v>1.786560891999032</v>
+        <v>1.794133307942301</v>
       </c>
       <c r="F10">
-        <v>2.537154375635279</v>
+        <v>2.547908214662331</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -577,16 +577,16 @@
         <v>105397.5075941635</v>
       </c>
       <c r="C11">
-        <v>20114.61689071483</v>
+        <v>20199.8735681212</v>
       </c>
       <c r="D11">
-        <v>191215.6050808429</v>
+        <v>192026.0807287766</v>
       </c>
       <c r="E11">
-        <v>1.814232702893931</v>
+        <v>1.821922407009653</v>
       </c>
       <c r="F11">
-        <v>2.477355424439617</v>
+        <v>2.487855803014561</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -597,16 +597,16 @@
         <v>109434.6078587565</v>
       </c>
       <c r="C12">
-        <v>21153.25421193946</v>
+        <v>21242.91319874694</v>
       </c>
       <c r="D12">
-        <v>201089.2042110948</v>
+        <v>201941.5295378199</v>
       </c>
       <c r="E12">
-        <v>1.837528439546599</v>
+        <v>1.845316883654017</v>
       </c>
       <c r="F12">
-        <v>2.411305851910404</v>
+        <v>2.421526276503194</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -617,16 +617,16 @@
         <v>113471.7081233495</v>
       </c>
       <c r="C13">
-        <v>22162.66552070493</v>
+        <v>22256.60294119024</v>
       </c>
       <c r="D13">
-        <v>210684.972066367</v>
+        <v>211577.9694719563</v>
       </c>
       <c r="E13">
-        <v>1.856718080222621</v>
+        <v>1.864587860455581</v>
       </c>
       <c r="F13">
-        <v>2.34036602292918</v>
+        <v>2.350285765975427</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -637,16 +637,16 @@
         <v>117508.8083879425</v>
       </c>
       <c r="C14">
-        <v>23141.04992152893</v>
+        <v>23239.13426679505</v>
       </c>
       <c r="D14">
-        <v>219985.7887919184</v>
+        <v>220918.2081131969</v>
       </c>
       <c r="E14">
-        <v>1.872079138660478</v>
+        <v>1.880014027406862</v>
       </c>
       <c r="F14">
-        <v>2.265769899650476</v>
+        <v>2.275373463787995</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -657,16 +657,16 @@
         <v>121545.9086525354</v>
       </c>
       <c r="C15">
-        <v>24087.10282722726</v>
+        <v>24189.19705882771</v>
       </c>
       <c r="D15">
-        <v>228979.2525891384</v>
+        <v>229949.791097369</v>
       </c>
       <c r="E15">
-        <v>1.88389107562414</v>
+        <v>1.891876029778419</v>
       </c>
       <c r="F15">
-        <v>2.188619612548633</v>
+        <v>2.197896171843103</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -677,16 +677,16 @@
         <v>125583.0089171284</v>
       </c>
       <c r="C16">
-        <v>24999.9594395805</v>
+        <v>25105.922853584</v>
       </c>
       <c r="D16">
-        <v>237657.1424257452</v>
+        <v>238664.4625469882</v>
       </c>
       <c r="E16">
-        <v>1.892430707585403</v>
+        <v>1.900451857340683</v>
       </c>
       <c r="F16">
-        <v>2.109885227022632</v>
+        <v>2.118828067204082</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -697,16 +697,16 @@
         <v>129620.1091817213</v>
       </c>
       <c r="C17">
-        <v>25879.13909886678</v>
+        <v>25988.82895404493</v>
       </c>
       <c r="D17">
-        <v>246014.8890056862</v>
+        <v>247057.6337988422</v>
       </c>
       <c r="E17">
-        <v>1.897968537125553</v>
+        <v>1.906013159211885</v>
       </c>
       <c r="F17">
-        <v>2.030408485549421</v>
+        <v>2.039014460109919</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -717,16 +717,16 @@
         <v>133657.2094463143</v>
       </c>
       <c r="C18">
-        <v>26724.49194293557</v>
+        <v>26837.76486286275</v>
       </c>
       <c r="D18">
-        <v>254051.067694232</v>
+        <v>255127.8741798255</v>
       </c>
       <c r="E18">
-        <v>1.900765912640694</v>
+        <v>1.908822391524656</v>
       </c>
       <c r="F18">
-        <v>1.950909432162395</v>
+        <v>1.95917844653192</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -737,16 +737,16 @@
         <v>137694.3097109073</v>
       </c>
       <c r="C19">
-        <v>27536.14888325783</v>
+        <v>27652.86204638237</v>
       </c>
       <c r="D19">
-        <v>261766.9229752456</v>
+        <v>262876.4334485999</v>
       </c>
       <c r="E19">
-        <v>1.901072916701002</v>
+        <v>1.909130696835009</v>
       </c>
       <c r="F19">
-        <v>1.871994980359576</v>
+        <v>1.879929512397348</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -757,16 +757,16 @@
         <v>141731.4099755002</v>
       </c>
       <c r="C20">
-        <v>28314.47554117396</v>
+        <v>28434.48767564611</v>
       </c>
       <c r="D20">
-        <v>269165.9305552847</v>
+        <v>270306.8020436564</v>
       </c>
       <c r="E20">
-        <v>1.899126880920841</v>
+        <v>1.907176412697664</v>
       </c>
       <c r="F20">
-        <v>1.794168648214046</v>
+        <v>1.801773309962489</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -777,16 +777,16 @@
         <v>145768.5102400932</v>
       </c>
       <c r="C21">
-        <v>29060.03049248411</v>
+        <v>29183.20269400194</v>
       </c>
       <c r="D21">
-        <v>276253.4004241042</v>
+        <v>277424.3124613721</v>
       </c>
       <c r="E21">
-        <v>1.895151428584207</v>
+        <v>1.90318411023362</v>
       </c>
       <c r="F21">
-        <v>1.717840842017086</v>
+        <v>1.725121985043517</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -797,16 +797,16 @@
         <v>149805.6105046861</v>
       </c>
       <c r="C22">
-        <v>29773.52793813419</v>
+        <v>29899.72432956747</v>
       </c>
       <c r="D22">
-        <v>283036.1219909562</v>
+        <v>284235.782888205</v>
       </c>
       <c r="E22">
-        <v>1.889355952940777</v>
+        <v>1.897364070214938</v>
       </c>
       <c r="F22">
-        <v>1.643339213708043</v>
+        <v>1.650304578346786</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -817,16 +817,16 @@
         <v>153842.7107692791</v>
       </c>
       <c r="C23">
-        <v>30455.804745915</v>
+        <v>30584.89299723399</v>
       </c>
       <c r="D23">
-        <v>289522.0507730577</v>
+        <v>290749.2025611777</v>
       </c>
       <c r="E23">
-        <v>1.881935447739604</v>
+        <v>1.889912112880147</v>
       </c>
       <c r="F23">
-        <v>1.570918743013933</v>
+        <v>1.577577150341924</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -837,16 +837,16 @@
         <v>157879.811033872</v>
       </c>
       <c r="C24">
-        <v>31107.79168443849</v>
+        <v>31239.64341071666</v>
       </c>
       <c r="D24">
-        <v>295720.0349371074</v>
+        <v>296973.4571503274</v>
       </c>
       <c r="E24">
-        <v>1.873070616189568</v>
+        <v>1.881009707356527</v>
       </c>
       <c r="F24">
-        <v>1.500771300907838</v>
+        <v>1.507132385255477</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -857,16 +857,16 @@
         <v>161916.911298465</v>
       </c>
       <c r="C25">
-        <v>31730.48858758427</v>
+        <v>31864.9796417344</v>
       </c>
       <c r="D25">
-        <v>301639.5792050348</v>
+        <v>302918.0916637607</v>
       </c>
       <c r="E25">
-        <v>1.862928194381227</v>
+        <v>1.870824296452796</v>
       </c>
       <c r="F25">
-        <v>1.433034536951062</v>
+        <v>1.439108516082395</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -877,16 +877,16 @@
         <v>165954.011563058</v>
       </c>
       <c r="C26">
-        <v>32324.94313696198</v>
+        <v>32461.95381254086</v>
       </c>
       <c r="D26">
-        <v>307290.6431536993</v>
+        <v>308593.1078924359</v>
       </c>
       <c r="E26">
-        <v>1.851661434751984</v>
+        <v>1.859509782173472</v>
       </c>
       <c r="F26">
-        <v>1.367800000799371</v>
+        <v>1.373597480515642</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -897,16 +897,16 @@
         <v>169991.111827651</v>
       </c>
       <c r="C27">
-        <v>32892.2329243793</v>
+        <v>33031.64808236341</v>
       </c>
       <c r="D27">
-        <v>312683.4706953096</v>
+        <v>314008.7931678285</v>
       </c>
       <c r="E27">
-        <v>1.839410704086283</v>
+        <v>1.847207126253712</v>
       </c>
       <c r="F27">
-        <v>1.305120459797495</v>
+        <v>1.310652269556638</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -917,16 +917,16 @@
         <v>174028.2120922439</v>
       </c>
       <c r="C28">
-        <v>33433.45044952153</v>
+        <v>33575.15958149473</v>
       </c>
       <c r="D28">
-        <v>317828.4474608477</v>
+        <v>319175.5771408688</v>
       </c>
       <c r="E28">
-        <v>1.826304158617582</v>
+        <v>1.834045028122735</v>
       </c>
       <c r="F28">
-        <v>1.245016412589908</v>
+        <v>1.250293468734234</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -937,16 +937,16 @@
         <v>178065.3123568369</v>
       </c>
       <c r="C29">
-        <v>33949.69071477108</v>
+        <v>34093.58795353238</v>
       </c>
       <c r="D29">
-        <v>322735.9828726882</v>
+        <v>324103.9133547202</v>
       </c>
       <c r="E29">
-        <v>1.812458465947237</v>
+        <v>1.820140649882594</v>
       </c>
       <c r="F29">
-        <v>1.187481825468263</v>
+        <v>1.192515018765947</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -957,16 +957,16 @@
         <v>182102.4126214298</v>
       </c>
       <c r="C30">
-        <v>34442.04109506805</v>
+        <v>34588.02518230237</v>
       </c>
       <c r="D30">
-        <v>327416.4138444422</v>
+        <v>328804.182536451</v>
       </c>
       <c r="E30">
-        <v>1.79797954970044</v>
+        <v>1.805600364120367</v>
       </c>
       <c r="F30">
-        <v>1.132489136014615</v>
+        <v>1.137289240409339</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -977,16 +977,16 @@
         <v>186139.5128860228</v>
       </c>
       <c r="C31">
-        <v>34911.57318258653</v>
+        <v>35059.54740196878</v>
       </c>
       <c r="D31">
-        <v>331879.9272539947</v>
+        <v>333286.6147414707</v>
       </c>
       <c r="E31">
-        <v>1.782963338134509</v>
+        <v>1.790520505689457</v>
       </c>
       <c r="F31">
-        <v>1.079993579479926</v>
+        <v>1.084571179178039</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -997,16 +997,16 @@
         <v>190176.6131506157</v>
       </c>
       <c r="C32">
-        <v>35359.33633121553</v>
+        <v>35509.20841415266</v>
       </c>
       <c r="D32">
-        <v>336136.4985753964</v>
+        <v>337561.2277253101</v>
       </c>
       <c r="E32">
-        <v>1.767496502365323</v>
+        <v>1.774988113065032</v>
       </c>
       <c r="F32">
-        <v>1.029936898961007</v>
+        <v>1.034302331244439</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1017,16 +1017,16 @@
         <v>194213.7134152087</v>
       </c>
       <c r="C33">
-        <v>35786.35265248337</v>
+        <v>35938.03466264642</v>
       </c>
       <c r="D33">
-        <v>340195.8443086137</v>
+        <v>341637.7791717428</v>
       </c>
       <c r="E33">
-        <v>1.751657173565856</v>
+        <v>1.759081648582439</v>
       </c>
       <c r="F33">
-        <v>0.9822505022106592</v>
+        <v>0.9864138136301253</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1037,16 +1037,16 @@
         <v>198250.8136798017</v>
       </c>
       <c r="C34">
-        <v>36193.61324128309</v>
+        <v>36347.02144314188</v>
       </c>
       <c r="D34">
-        <v>344067.3861001388</v>
+        <v>345525.7306613188</v>
       </c>
       <c r="E34">
-        <v>1.7355156315063</v>
+        <v>1.742871689895726</v>
       </c>
       <c r="F34">
-        <v>0.9368581269652443</v>
+        <v>0.9408290408305324</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1057,16 +1057,16 @@
         <v>202287.9139443946</v>
       </c>
       <c r="C35">
-        <v>36582.07543559946</v>
+        <v>36737.13015134243</v>
       </c>
       <c r="D35">
-        <v>347760.2246931287</v>
+        <v>349234.2215110902</v>
       </c>
       <c r="E35">
-        <v>1.719134959237959</v>
+        <v>1.726421587436452</v>
       </c>
       <c r="F35">
-        <v>0.8936780738884034</v>
+        <v>0.8974659672231093</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1077,16 +1077,16 @@
         <v>206325.0142089876</v>
       </c>
       <c r="C36">
-        <v>36952.66093879075</v>
+        <v>37109.28639728604</v>
       </c>
       <c r="D36">
-        <v>351283.1220772504</v>
+        <v>352772.050848798</v>
       </c>
       <c r="E36">
-        <v>1.702571660658819</v>
+        <v>1.709788084596827</v>
       </c>
       <c r="F36">
-        <v>0.8526250622900584</v>
+        <v>0.8562389506518966</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1097,16 +1097,16 @@
         <v>210362.1144735806</v>
       </c>
       <c r="C37">
-        <v>37306.25465547524</v>
+        <v>37464.37883629769</v>
       </c>
       <c r="D37">
-        <v>354644.4904222682</v>
+        <v>356147.6664995533</v>
       </c>
       <c r="E37">
-        <v>1.685876239216107</v>
+        <v>1.693021898885134</v>
       </c>
       <c r="F37">
-        <v>0.8136117591938101</v>
+        <v>0.8170602879758632</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -1117,16 +1117,16 @@
         <v>214399.2147381735</v>
       </c>
       <c r="C38">
-        <v>37643.70411253022</v>
+        <v>37803.25858753412</v>
       </c>
       <c r="D38">
-        <v>357852.386573885</v>
+        <v>359369.1594583495</v>
       </c>
       <c r="E38">
-        <v>1.669093737171089</v>
+        <v>1.67616826347622</v>
       </c>
       <c r="F38">
-        <v>0.7765500274648378</v>
+        <v>0.7798414684871187</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1137,16 +1137,16 @@
         <v>218436.3150027665</v>
       </c>
       <c r="C39">
-        <v>37965.81935507903</v>
+        <v>38126.73912953015</v>
       </c>
       <c r="D39">
-        <v>360914.5110649642</v>
+        <v>362444.2628970931</v>
       </c>
       <c r="E39">
-        <v>1.65226423573568</v>
+        <v>1.659267429467956</v>
       </c>
       <c r="F39">
-        <v>0.7413519338358985</v>
+        <v>0.7444941862094471</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1157,16 +1157,16 @@
         <v>222473.4152673595</v>
       </c>
       <c r="C40">
-        <v>38273.37322365945</v>
+        <v>38435.59657854171</v>
       </c>
       <c r="D40">
-        <v>363838.2107503758</v>
+        <v>365380.3548106176</v>
       </c>
       <c r="E40">
-        <v>1.635423317042757</v>
+        <v>1.642355129809638</v>
       </c>
       <c r="F40">
-        <v>0.707930552957649</v>
+        <v>0.7109311473566113</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1177,16 +1177,16 @@
         <v>226510.5155319524</v>
       </c>
       <c r="C41">
-        <v>38567.10193313289</v>
+        <v>38730.57026990889</v>
       </c>
       <c r="D41">
-        <v>366630.4843102817</v>
+        <v>368184.4635432946</v>
       </c>
       <c r="E41">
-        <v>1.618602489377865</v>
+        <v>1.625463006336044</v>
       </c>
       <c r="F41">
-        <v>0.6762005991652968</v>
+        <v>0.6790667047768585</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -1197,16 +1197,16 @@
         <v>230547.6157965454</v>
       </c>
       <c r="C42">
-        <v>38847.70588644536</v>
+        <v>39012.36357526603</v>
       </c>
       <c r="D42">
-        <v>369297.9899859921</v>
+        <v>370863.2755576795</v>
       </c>
       <c r="E42">
-        <v>1.601829577417498</v>
+        <v>1.608619001659772</v>
       </c>
       <c r="F42">
-        <v>0.6460789135620364</v>
+        <v>0.6488173471007874</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -1217,16 +1217,16 @@
         <v>234584.7160611384</v>
       </c>
       <c r="C43">
-        <v>39115.85066724221</v>
+        <v>39281.64489936364</v>
       </c>
       <c r="D43">
-        <v>371847.0550160602</v>
+        <v>373423.1449106009</v>
       </c>
       <c r="E43">
-        <v>1.585129079420281</v>
+        <v>1.591847717876376</v>
       </c>
       <c r="F43">
-        <v>0.6174848303029281</v>
+        <v>0.6201020665777565</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1237,16 +1237,16 @@
         <v>238621.8163257313</v>
       </c>
       <c r="C44">
-        <v>39372.16816473315</v>
+        <v>39539.04880970131</v>
       </c>
       <c r="D44">
-        <v>374283.6863295883</v>
+        <v>375870.1039917909</v>
       </c>
       <c r="E44">
-        <v>1.568522493428142</v>
+        <v>1.575170744148173</v>
       </c>
       <c r="F44">
-        <v>0.5903404426273968</v>
+        <v>0.5928426262359854</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -1257,16 +1257,16 @@
         <v>242658.9165903243</v>
       </c>
       <c r="C45">
-        <v>39617.25779226242</v>
+        <v>39785.17726026278</v>
       </c>
       <c r="D45">
-        <v>376613.5821303222</v>
+        <v>378209.8751570794</v>
       </c>
       <c r="E45">
-        <v>1.552028614576527</v>
+        <v>1.558606955274604</v>
       </c>
       <c r="F45">
-        <v>0.5645707862273147</v>
+        <v>0.5669637440279001</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1277,16 +1277,16 @@
         <v>246696.0168549173</v>
       </c>
       <c r="C46">
-        <v>39851.68776791796</v>
+        <v>40020.60087755303</v>
       </c>
       <c r="D46">
-        <v>378842.1440705078</v>
+        <v>380447.8829538502</v>
       </c>
       <c r="E46">
-        <v>1.535663805602934</v>
+        <v>1.542172783347341</v>
       </c>
       <c r="F46">
-        <v>0.5401039549302316</v>
+        <v>0.5423932090036037</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1297,16 +1297,16 @@
         <v>250733.1171195102</v>
       </c>
       <c r="C47">
-        <v>40075.99643135738</v>
+        <v>40245.86028300569</v>
       </c>
       <c r="D47">
-        <v>380974.4897690353</v>
+        <v>382589.2666922432</v>
       </c>
       <c r="E47">
-        <v>1.519442242595526</v>
+        <v>1.525882464540512</v>
       </c>
       <c r="F47">
-        <v>0.5168711613971189</v>
+        <v>0.5190619422659422</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1317,16 +1317,16 @@
         <v>254770.2173841032</v>
       </c>
       <c r="C48">
-        <v>40290.69357597092</v>
+        <v>40461.46743079244</v>
       </c>
       <c r="D48">
-        <v>383015.4654753814</v>
+        <v>384638.8931627742</v>
       </c>
       <c r="E48">
-        <v>1.503376137949161</v>
+        <v>1.509748263011744</v>
       </c>
       <c r="F48">
-        <v>0.4948067535547717</v>
+        <v>0.4969040134725448</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1337,16 +1337,16 @@
         <v>258807.3176486962</v>
       </c>
       <c r="C49">
-        <v>40496.26177966432</v>
+        <v>40667.90694424642</v>
       </c>
       <c r="D49">
-        <v>384969.658720432</v>
+        <v>386601.3693407778</v>
       </c>
       <c r="E49">
-        <v>1.487475942403561</v>
+        <v>1.493780673796669</v>
       </c>
       <c r="F49">
-        <v>0.4738481957725984</v>
+        <v>0.4758566219328391</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1357,16 +1357,16 @@
         <v>262844.4179132891</v>
       </c>
       <c r="C50">
-        <v>40693.15772103426</v>
+        <v>40865.63743761639</v>
       </c>
       <c r="D50">
-        <v>386841.4108284423</v>
+        <v>388481.0549514009</v>
       </c>
       <c r="E50">
-        <v>1.471750527934206</v>
+        <v>1.477988606475024</v>
       </c>
       <c r="F50">
-        <v>0.4539360223232138</v>
+        <v>0.4558600498713743</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1377,16 +1377,16 @@
         <v>266881.5181778821</v>
       </c>
       <c r="C51">
-        <v>40881.81347062284</v>
+        <v>41055.09281279421</v>
       </c>
       <c r="D51">
-        <v>388634.8291920906</v>
+        <v>390282.074796684</v>
       </c>
       <c r="E51">
-        <v>1.456207353156083</v>
+        <v>1.462379551275457</v>
       </c>
       <c r="F51">
-        <v>0.4350137694079094</v>
+        <v>0.4368575941651584</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1397,16 +1397,16 @@
         <v>270918.618442475</v>
       </c>
       <c r="C52">
-        <v>41062.63774935868</v>
+        <v>41236.68352308991</v>
       </c>
       <c r="D52">
-        <v>390353.7992355988</v>
+        <v>392008.3307693881</v>
       </c>
       <c r="E52">
-        <v>1.440852612787422</v>
+        <v>1.446959729172783</v>
       </c>
       <c r="F52">
-        <v>0.417027890955437</v>
+        <v>0.4187954817856132</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1417,16 +1417,16 @@
         <v>274955.718707068</v>
       </c>
       <c r="C53">
-        <v>41236.01714829494</v>
+        <v>41410.79779813961</v>
       </c>
       <c r="D53">
-        <v>392001.9960099283</v>
+        <v>393663.513497338</v>
       </c>
       <c r="E53">
-        <v>1.425691372608107</v>
+        <v>1.431734227418411</v>
       </c>
       <c r="F53">
-        <v>0.3999276624919303</v>
+        <v>0.4016227732609945</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1437,16 +1437,16 @@
         <v>278992.8189716609</v>
       </c>
       <c r="C54">
-        <v>41402.31730540207</v>
+        <v>41577.80282568619</v>
       </c>
       <c r="D54">
-        <v>393582.8953797272</v>
+        <v>395251.1135777851</v>
       </c>
       <c r="E54">
-        <v>1.410727691237479</v>
+        <v>1.41670712183432</v>
       </c>
       <c r="F54">
-        <v>0.3836650766085852</v>
+        <v>0.3852912577009809</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -1457,16 +1457,16 @@
         <v>283029.9192362539</v>
       </c>
       <c r="C55">
-        <v>41561.88403652098</v>
+        <v>41738.04588732601</v>
       </c>
       <c r="D55">
-        <v>395099.7847745115</v>
+        <v>396774.432374158</v>
       </c>
       <c r="E55">
-        <v>1.395964729950367</v>
+        <v>1.401881587094536</v>
       </c>
       <c r="F55">
-        <v>0.3681947329034668</v>
+        <v>0.3697553422720872</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -1477,16 +1477,16 @@
         <v>287067.0195008469</v>
       </c>
       <c r="C56">
-        <v>41715.04441867767</v>
+        <v>41891.85544641528</v>
       </c>
       <c r="D56">
-        <v>396555.7734869798</v>
+        <v>398236.5923580278</v>
       </c>
       <c r="E56">
-        <v>1.38140485164932</v>
+        <v>1.387259996116875</v>
       </c>
       <c r="F56">
-        <v>0.353473724727836</v>
+        <v>0.3549719384638738</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1497,16 +1497,16 @@
         <v>291104.1197654398</v>
       </c>
       <c r="C57">
-        <v>41862.10782484413</v>
+        <v>42039.54218721674</v>
       </c>
       <c r="D57">
-        <v>397953.8025097623</v>
+        <v>399640.5469875492</v>
       </c>
       <c r="E57">
-        <v>1.367049710015845</v>
+        <v>1.372844009592045</v>
       </c>
       <c r="F57">
-        <v>0.3394615246087361</v>
+        <v>0.3409003470259138</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -1517,16 +1517,16 @@
         <v>295141.2200300328</v>
       </c>
       <c r="C58">
-        <v>42003.36690993628</v>
+        <v>42181.4000050769</v>
       </c>
       <c r="D58">
-        <v>399296.653908614</v>
+        <v>400989.0901203841</v>
       </c>
       <c r="E58">
-        <v>1.352900329774277</v>
+        <v>1.358634656587719</v>
       </c>
       <c r="F58">
-        <v>0.326119869837703</v>
+        <v>0.3275021430716193</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -1537,16 +1537,16 @@
         <v>299178.3202946258</v>
       </c>
       <c r="C59">
-        <v>42139.09854839938</v>
+        <v>42317.70694798537</v>
       </c>
       <c r="D59">
-        <v>400586.9597353839</v>
+        <v>402284.8649644476</v>
       </c>
       <c r="E59">
-        <v>1.338957178918889</v>
+        <v>1.344632407081784</v>
       </c>
       <c r="F59">
-        <v>0.3134126493971574</v>
+        <v>0.3147410625252732</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -1557,16 +1557,16 @@
         <v>303215.4205592187</v>
       </c>
       <c r="C60">
-        <v>42269.56472416664</v>
+        <v>42448.72611030566</v>
       </c>
       <c r="D60">
-        <v>401827.21048823</v>
+        <v>403530.3725739822</v>
       </c>
       <c r="E60">
-        <v>1.325220233677898</v>
+        <v>1.3308372372017</v>
       </c>
       <c r="F60">
-        <v>0.3013057931318713</v>
+        <v>0.3025828908238297</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1577,16 +1577,16 @@
         <v>307252.5208238117</v>
       </c>
       <c r="C61">
-        <v>42395.01337411214</v>
+        <v>42574.70647980305</v>
       </c>
       <c r="D61">
-        <v>403019.7631297361</v>
+        <v>404727.9799016599</v>
       </c>
       <c r="E61">
-        <v>1.311689036917098</v>
+        <v>1.317248687875677</v>
       </c>
       <c r="F61">
-        <v>0.2953983214053892</v>
+        <v>0.29665038002184</v>
       </c>
     </row>
   </sheetData>
@@ -1627,16 +1627,16 @@
         <v>33337.86217631619</v>
       </c>
       <c r="C2">
-        <v>5416.629980920686</v>
+        <v>5432.587701633281</v>
       </c>
       <c r="D2">
-        <v>51492.11565540164</v>
+        <v>51643.81455368781</v>
       </c>
       <c r="E2">
-        <v>1.544553618437554</v>
+        <v>1.549103967151694</v>
       </c>
       <c r="F2">
-        <v>3.196634415990065</v>
+        <v>3.206051895014905</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1647,16 +1647,16 @@
         <v>35262.06742565849</v>
       </c>
       <c r="C3">
-        <v>6063.672468392299</v>
+        <v>6081.536415548389</v>
       </c>
       <c r="D3">
-        <v>57643.09637887797</v>
+        <v>57812.91643973931</v>
       </c>
       <c r="E3">
-        <v>1.634705523163225</v>
+        <v>1.639521464860896</v>
       </c>
       <c r="F3">
-        <v>3.267999347296076</v>
+        <v>3.277627071740386</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1667,16 +1667,16 @@
         <v>37186.27267500078</v>
       </c>
       <c r="C4">
-        <v>6739.60543044524</v>
+        <v>6759.460717136588</v>
       </c>
       <c r="D4">
-        <v>64068.71865323023</v>
+        <v>64257.46898734633</v>
       </c>
       <c r="E4">
-        <v>1.722913162423555</v>
+        <v>1.727988969180681</v>
       </c>
       <c r="F4">
-        <v>3.405967593578304</v>
+        <v>3.416001780850815</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1687,16 +1687,16 @@
         <v>39110.47792434307</v>
       </c>
       <c r="C5">
-        <v>7442.50123465523</v>
+        <v>7464.427295051473</v>
       </c>
       <c r="D5">
-        <v>70750.65782418416</v>
+        <v>70959.0935566908</v>
       </c>
       <c r="E5">
-        <v>1.808994969610118</v>
+        <v>1.814324378596371</v>
       </c>
       <c r="F5">
-        <v>3.534254498133003</v>
+        <v>3.544666626413335</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1707,16 +1707,16 @@
         <v>41034.68317368537</v>
       </c>
       <c r="C6">
-        <v>8170.368241726207</v>
+        <v>8194.438642506722</v>
       </c>
       <c r="D6">
-        <v>77669.98076886853</v>
+        <v>77898.8012467723</v>
       </c>
       <c r="E6">
-        <v>1.892788606168076</v>
+        <v>1.898364876293893</v>
       </c>
       <c r="F6">
-        <v>3.652588647400797</v>
+        <v>3.663349395267741</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1727,16 +1727,16 @@
         <v>42958.88842302767</v>
       </c>
       <c r="C7">
-        <v>8921.168943607368</v>
+        <v>8947.45124882914</v>
       </c>
       <c r="D7">
-        <v>84807.31832221757</v>
+        <v>85057.16582978905</v>
       </c>
       <c r="E7">
-        <v>1.974150669055894</v>
+        <v>1.979966636757646</v>
       </c>
       <c r="F7">
-        <v>3.760786465882804</v>
+        <v>3.771865971090589</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1747,16 +1747,16 @@
         <v>44883.09367236996</v>
       </c>
       <c r="C8">
-        <v>9692.837384623619</v>
+        <v>9721.393071912807</v>
       </c>
       <c r="D8">
-        <v>92143.0308874828</v>
+        <v>92414.48984954845</v>
       </c>
       <c r="E8">
-        <v>2.052956321596122</v>
+        <v>2.059004455533751</v>
       </c>
       <c r="F8">
-        <v>3.858748271980796</v>
+        <v>3.870116378615617</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1767,16 +1767,16 @@
         <v>46807.29892171224</v>
       </c>
       <c r="C9">
-        <v>10483.29570288893</v>
+        <v>10514.18012836446</v>
       </c>
       <c r="D9">
-        <v>99657.36568388944</v>
+        <v>99950.96233238453</v>
       </c>
       <c r="E9">
-        <v>2.129098836712877</v>
+        <v>2.135371291121881</v>
       </c>
       <c r="F9">
-        <v>3.946453580585853</v>
+        <v>3.958080072383524</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1787,16 +1787,16 @@
         <v>48731.50417105455</v>
       </c>
       <c r="C10">
-        <v>11290.46964979627</v>
+        <v>11323.73205871474</v>
       </c>
       <c r="D10">
-        <v>107330.6042795808</v>
+        <v>107646.8067547435</v>
       </c>
       <c r="E10">
-        <v>2.202489049031506</v>
+        <v>2.208977715460779</v>
       </c>
       <c r="F10">
-        <v>4.023955762494613</v>
+        <v>4.035810580424565</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1807,16 +1807,16 @@
         <v>50655.70942039684</v>
       </c>
       <c r="C11">
-        <v>12112.30296941668</v>
+        <v>12147.98654917994</v>
       </c>
       <c r="D11">
-        <v>115143.1992865161</v>
+        <v>115482.4181407928</v>
       </c>
       <c r="E11">
-        <v>2.273054717898254</v>
+        <v>2.279751275071336</v>
       </c>
       <c r="F11">
-        <v>4.091376184284026</v>
+        <v>4.103429626868981</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1827,16 +1827,16 @@
         <v>52579.91466973913</v>
       </c>
       <c r="C12">
-        <v>12946.7705456504</v>
+        <v>12984.91251754533</v>
       </c>
       <c r="D12">
-        <v>123075.8993412475</v>
+        <v>123438.4884113994</v>
       </c>
       <c r="E12">
-        <v>2.340739807477861</v>
+        <v>2.347635769033321</v>
       </c>
       <c r="F12">
-        <v>4.148897958796089</v>
+        <v>4.161120864020315</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1847,16 +1847,16 @@
         <v>54504.11991908143</v>
       </c>
       <c r="C13">
-        <v>13791.89025165137</v>
+        <v>13832.52199749885</v>
       </c>
       <c r="D13">
-        <v>131109.861749118</v>
+        <v>131496.1193601841</v>
       </c>
       <c r="E13">
-        <v>2.405503693000969</v>
+        <v>2.41259045289434</v>
       </c>
       <c r="F13">
-        <v>4.196759437022207</v>
+        <v>4.209123345066481</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1867,16 +1867,16 @@
         <v>56428.32516842373</v>
       </c>
       <c r="C14">
-        <v>14645.73346231523</v>
+        <v>14688.8806820895</v>
       </c>
       <c r="D14">
-        <v>139226.7524191375</v>
+        <v>139636.9228828117</v>
       </c>
       <c r="E14">
-        <v>2.467320304183797</v>
+        <v>2.474589179565974</v>
       </c>
       <c r="F14">
-        <v>4.235247568001644</v>
+        <v>4.247724864416018</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1887,16 +1887,16 @@
         <v>58352.53041776601</v>
       </c>
       <c r="C15">
-        <v>15506.43421560924</v>
+        <v>15552.11711204716</v>
       </c>
       <c r="D15">
-        <v>147408.8329543439</v>
+        <v>147843.1083239262</v>
       </c>
       <c r="E15">
-        <v>2.526177218005679</v>
+        <v>2.533619489428584</v>
       </c>
       <c r="F15">
-        <v>4.264691245363138</v>
+        <v>4.277255284638229</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1907,16 +1907,16 @@
         <v>60276.73566710831</v>
       </c>
       <c r="C16">
-        <v>16372.19703155857</v>
+        <v>16420.43051780398</v>
       </c>
       <c r="D16">
-        <v>155639.0349814412</v>
+        <v>156097.5570257676</v>
       </c>
       <c r="E16">
-        <v>2.582074713551052</v>
+        <v>2.589681662388804</v>
       </c>
       <c r="F16">
-        <v>4.28545474829052</v>
+        <v>4.298079958105577</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1927,16 +1927,16 @@
         <v>62200.9409164506</v>
       </c>
       <c r="C17">
-        <v>17241.30341829979</v>
+        <v>17292.09734471519</v>
       </c>
       <c r="D17">
-        <v>163901.0219993028</v>
+        <v>164383.8843588855</v>
       </c>
       <c r="E17">
-        <v>2.635024801625712</v>
+        <v>2.642787744636996</v>
       </c>
       <c r="F17">
-        <v>4.297931371852298</v>
+        <v>4.310593338557704</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1947,16 +1947,16 @@
         <v>64125.14616579289</v>
       </c>
       <c r="C18">
-        <v>18112.11711245045</v>
+        <v>18165.4765088671</v>
       </c>
       <c r="D18">
-        <v>172179.2391955034</v>
+        <v>172686.4896854328</v>
       </c>
       <c r="E18">
-        <v>2.685050241450384</v>
+        <v>2.69296056244393</v>
       </c>
       <c r="F18">
-        <v>4.302537327588221</v>
+        <v>4.315212863718799</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1967,16 +1967,16 @@
         <v>66049.35141513518</v>
       </c>
       <c r="C19">
-        <v>18983.08811595338</v>
+        <v>19039.01344581419</v>
       </c>
       <c r="D19">
-        <v>180458.9518217757</v>
+        <v>180990.5948476797</v>
       </c>
       <c r="E19">
-        <v>2.732183556013293</v>
+        <v>2.740232734612528</v>
       </c>
       <c r="F19">
-        <v>4.299705980687394</v>
+        <v>4.312373175498149</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1987,16 +1987,16 @@
         <v>67973.5566644775</v>
       </c>
       <c r="C20">
-        <v>19852.75560349846</v>
+        <v>19911.2430265663</v>
       </c>
       <c r="D20">
-        <v>188726.2728328377</v>
+        <v>189282.2718882658</v>
       </c>
       <c r="E20">
-        <v>2.776466056710914</v>
+        <v>2.784645694245147</v>
       </c>
       <c r="F20">
-        <v>4.289882475601626</v>
+        <v>4.30252072977012</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2007,16 +2007,16 @@
         <v>69897.76191381979</v>
       </c>
       <c r="C21">
-        <v>20719.74978366834</v>
+        <v>20780.7914242174</v>
       </c>
       <c r="D21">
-        <v>196968.1805790041</v>
+        <v>197548.4607949352</v>
       </c>
       <c r="E21">
-        <v>2.81794688679525</v>
+        <v>2.826248729372793</v>
       </c>
       <c r="F21">
-        <v>4.273518787996707</v>
+        <v>4.286108833748226</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2027,16 +2027,16 @@
         <v>71821.96716316207</v>
       </c>
       <c r="C22">
-        <v>21582.79280325478</v>
+        <v>21646.37702092615</v>
       </c>
       <c r="D22">
-        <v>205172.52740289</v>
+        <v>205776.9781225672</v>
       </c>
       <c r="E22">
-        <v>2.856682091939752</v>
+        <v>2.865098050782873</v>
       </c>
       <c r="F22">
-        <v>4.251069227922779</v>
+        <v>4.263593135907636</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2047,16 +2047,16 @@
         <v>73746.17241250437</v>
       </c>
       <c r="C23">
-        <v>22440.69878796494</v>
+        <v>22506.81044874206</v>
       </c>
       <c r="D23">
-        <v>213328.040026377</v>
+        <v>213956.5173812817</v>
       </c>
       <c r="E23">
-        <v>2.892733724987268</v>
+        <v>2.901255894129676</v>
       </c>
       <c r="F23">
-        <v>4.222986407250534</v>
+        <v>4.235427581541074</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2067,16 +2067,16 @@
         <v>75670.37766184665</v>
       </c>
       <c r="C24">
-        <v>23292.37311424563</v>
+        <v>23360.99385928451</v>
       </c>
       <c r="D24">
-        <v>221424.3126283553</v>
+        <v>222076.6420937881</v>
       </c>
       <c r="E24">
-        <v>2.926168990696057</v>
+        <v>2.93478966216076</v>
       </c>
       <c r="F24">
-        <v>4.189717673950813</v>
+        <v>4.20206083653365</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2087,16 +2087,16 @@
         <v>77594.58291118896</v>
       </c>
       <c r="C25">
-        <v>24136.81100648855</v>
+        <v>24207.91951681525</v>
       </c>
       <c r="D25">
-        <v>229451.7935093337</v>
+        <v>230127.7724207091</v>
       </c>
       <c r="E25">
-        <v>2.957059435089087</v>
+        <v>2.965771111678019</v>
       </c>
       <c r="F25">
-        <v>4.151702006787385</v>
+        <v>4.163933172907208</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2107,16 +2107,16 @@
         <v>79518.78816053126</v>
       </c>
       <c r="C26">
-        <v>24973.09555174126</v>
+        <v>25046.66780710065</v>
       </c>
       <c r="D26">
-        <v>237401.7662186858</v>
+        <v>238101.1662322253</v>
       </c>
       <c r="E26">
-        <v>2.985480182864745</v>
+        <v>2.99427558870176</v>
       </c>
       <c r="F26">
-        <v>4.109367356467452</v>
+        <v>4.121473802137723</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2127,16 +2127,16 @@
         <v>81442.99340987354</v>
       </c>
       <c r="C27">
-        <v>25800.39522053751</v>
+        <v>25876.40475093816</v>
       </c>
       <c r="D27">
-        <v>245266.3259869148</v>
+        <v>245988.8954709094</v>
       </c>
       <c r="E27">
-        <v>3.011509225263576</v>
+        <v>3.020381314239458</v>
       </c>
       <c r="F27">
-        <v>4.063128413227478</v>
+        <v>4.075098636164272</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2147,16 +2147,16 @@
         <v>83367.19865921584</v>
       </c>
       <c r="C28">
-        <v>26617.96097786602</v>
+        <v>26696.37910661391</v>
       </c>
       <c r="D28">
-        <v>253038.352261654</v>
+        <v>253783.8186068151</v>
       </c>
       <c r="E28">
-        <v>3.035226759819665</v>
+        <v>3.044168722092001</v>
       </c>
       <c r="F28">
-        <v>4.013384776143096</v>
+        <v>4.025208451305591</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2167,16 +2167,16 @@
         <v>85291.40390855813</v>
       </c>
       <c r="C29">
-        <v>27425.12306288731</v>
+        <v>27505.91914013232</v>
       </c>
       <c r="D29">
-        <v>260711.4780946848</v>
+        <v>261479.5499343078</v>
       </c>
       <c r="E29">
-        <v>3.056714582564457</v>
+        <v>3.065719849266908</v>
       </c>
       <c r="F29">
-        <v>3.960519496034674</v>
+        <v>3.972187426873043</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2187,16 +2187,16 @@
         <v>87215.60915790043</v>
       </c>
       <c r="C30">
-        <v>28221.28751003088</v>
+        <v>28304.42913606426</v>
       </c>
       <c r="D30">
-        <v>268280.0570704389</v>
+        <v>269070.4264031362</v>
       </c>
       <c r="E30">
-        <v>3.076055532499101</v>
+        <v>3.085117778814052</v>
       </c>
       <c r="F30">
-        <v>3.904897961572445</v>
+        <v>3.91640202799407</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2207,16 +2207,16 @@
         <v>89139.81440724272</v>
       </c>
       <c r="C31">
-        <v>29005.93247777695</v>
+        <v>29091.38571551316</v>
       </c>
       <c r="D31">
-        <v>275739.1284062922</v>
+        <v>276551.4726159098</v>
       </c>
       <c r="E31">
-        <v>3.093332987508308</v>
+        <v>3.102446134254455</v>
       </c>
       <c r="F31">
-        <v>3.846867096918251</v>
+        <v>3.858200200890153</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2227,16 +2227,16 @@
         <v>91064.01965658503</v>
       </c>
       <c r="C32">
-        <v>29778.6044449371</v>
+        <v>29866.33402118967</v>
       </c>
       <c r="D32">
-        <v>283084.3807932634</v>
+        <v>283918.364562269</v>
       </c>
       <c r="E32">
-        <v>3.108630410351022</v>
+        <v>3.117788624233415</v>
       </c>
       <c r="F32">
-        <v>3.786754838835854</v>
+        <v>3.797910848446645</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2247,16 +2247,16 @@
         <v>92988.22490592733</v>
       </c>
       <c r="C33">
-        <v>30538.91432775597</v>
+        <v>30628.88382307404</v>
       </c>
       <c r="D33">
-        <v>290312.1154840129</v>
+        <v>291167.39259814</v>
       </c>
       <c r="E33">
-        <v>3.122030942925415</v>
+        <v>3.131228635590184</v>
       </c>
       <c r="F33">
-        <v>3.724869861514243</v>
+        <v>3.735843554225432</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2267,16 +2267,16 @@
         <v>94912.43015526961</v>
       </c>
       <c r="C34">
-        <v>31286.53356479283</v>
+        <v>31378.70559176361</v>
       </c>
       <c r="D34">
-        <v>297419.2090745486</v>
+        <v>298295.4241177932</v>
       </c>
       <c r="E34">
-        <v>3.133617046660728</v>
+        <v>3.142848872690377</v>
       </c>
       <c r="F34">
-        <v>3.661501518240957</v>
+        <v>3.672288523966401</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2287,16 +2287,16 @@
         <v>96836.63540461191</v>
       </c>
       <c r="C35">
-        <v>32021.19021041109</v>
+        <v>32115.52658045344</v>
       </c>
       <c r="D35">
-        <v>304403.0763677609</v>
+        <v>305299.8663079712</v>
       </c>
       <c r="E35">
-        <v>3.143470186627978</v>
+        <v>3.152731040606054</v>
       </c>
       <c r="F35">
-        <v>3.596919970408846</v>
+        <v>3.607516714974308</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2307,16 +2307,16 @@
         <v>98760.8406539542</v>
       </c>
       <c r="C36">
-        <v>32742.66507188532</v>
+        <v>32839.12695066301</v>
       </c>
       <c r="D36">
-        <v>311261.6336515983</v>
+        <v>312178.6293178805</v>
       </c>
       <c r="E36">
-        <v>3.151670556776857</v>
+        <v>3.160955569543154</v>
       </c>
       <c r="F36">
-        <v>3.531376476026346</v>
+        <v>3.54178012547884</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2327,16 +2327,16 @@
         <v>100685.0459032965</v>
       </c>
       <c r="C37">
-        <v>33450.78791968754</v>
+        <v>33549.33597135782</v>
       </c>
       <c r="D37">
-        <v>317993.2626729084</v>
+        <v>318930.0901268963</v>
       </c>
       <c r="E37">
-        <v>3.158296843588142</v>
+        <v>3.167601377797598</v>
       </c>
       <c r="F37">
-        <v>3.465103811823878</v>
+        <v>3.475312217984897</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2347,16 +2347,16 @@
         <v>102609.2511526388</v>
       </c>
       <c r="C38">
-        <v>34145.43379547454</v>
+        <v>34246.02831605983</v>
       </c>
       <c r="D38">
-        <v>324596.7755400533</v>
+        <v>325553.0573437804</v>
       </c>
       <c r="E38">
-        <v>3.163426025370673</v>
+        <v>3.172745670461003</v>
       </c>
       <c r="F38">
-        <v>3.39831680512497</v>
+        <v>3.408328452710315</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2367,16 +2367,16 @@
         <v>104533.4564019811</v>
       </c>
       <c r="C39">
-        <v>34826.51943769011</v>
+        <v>34929.12047791918</v>
       </c>
       <c r="D39">
-        <v>331071.3807436076</v>
+        <v>332046.7371272721</v>
       </c>
       <c r="E39">
-        <v>3.167133204420985</v>
+        <v>3.176463771085821</v>
       </c>
       <c r="F39">
-        <v>3.331212953799098</v>
+        <v>3.341026909365214</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2387,16 +2387,16 @@
         <v>106457.6616513234</v>
       </c>
       <c r="C40">
-        <v>35493.99984052617</v>
+        <v>35598.56731853797</v>
       </c>
       <c r="D40">
-        <v>337416.6504448078</v>
+        <v>338410.7003781691</v>
       </c>
       <c r="E40">
-        <v>3.169491469293543</v>
+        <v>3.178828983549841</v>
       </c>
       <c r="F40">
-        <v>3.26397311477999</v>
+        <v>3.273588977698921</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2407,16 +2407,16 @@
         <v>108381.8669006656</v>
       </c>
       <c r="C41">
-        <v>36147.86495825605</v>
+        <v>36254.35876259422</v>
       </c>
       <c r="D41">
-        <v>343632.4891459511</v>
+        <v>344644.8513174267</v>
       </c>
       <c r="E41">
-        <v>3.170571784493229</v>
+        <v>3.17991248142368</v>
       </c>
       <c r="F41">
-        <v>3.196762243763509</v>
+        <v>3.206180099376719</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2427,16 +2427,16 @@
         <v>110306.072150008</v>
       </c>
       <c r="C42">
-        <v>36788.1365636456</v>
+        <v>36896.51664699765</v>
       </c>
       <c r="D42">
-        <v>349719.1038255058</v>
+        <v>350749.3975332842</v>
       </c>
       <c r="E42">
-        <v>3.170442904991795</v>
+        <v>3.179783222235412</v>
       </c>
       <c r="F42">
-        <v>3.129730170757777</v>
+        <v>3.138950545815073</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2447,16 +2447,16 @@
         <v>112230.2773993503</v>
       </c>
       <c r="C43">
-        <v>37414.86526625022</v>
+        <v>37525.09173040251</v>
       </c>
       <c r="D43">
-        <v>355676.9755931454</v>
+        <v>356724.8215527933</v>
       </c>
       <c r="E43">
-        <v>3.169171313081014</v>
+        <v>3.178507884137676</v>
       </c>
       <c r="F43">
-        <v>3.06301239811732</v>
+        <v>3.072036218566672</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2467,16 +2467,16 @@
         <v>114154.4826486925</v>
       </c>
       <c r="C44">
-        <v>38028.12769389211</v>
+        <v>38140.16086638119</v>
       </c>
       <c r="D44">
-        <v>361506.8328960215</v>
+        <v>362571.8539691554</v>
       </c>
       <c r="E44">
-        <v>3.166821175201235</v>
+        <v>3.17615082260905</v>
       </c>
       <c r="F44">
-        <v>2.996730909527789</v>
+        <v>3.005559460688476</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2487,16 +2487,16 @@
         <v>116078.6878980348</v>
       </c>
       <c r="C45">
-        <v>38628.02383845647</v>
+        <v>38741.82434140106</v>
       </c>
       <c r="D45">
-        <v>367209.6262871047</v>
+        <v>368291.4481357276</v>
       </c>
       <c r="E45">
-        <v>3.163454316520762</v>
+        <v>3.172774044958537</v>
       </c>
       <c r="F45">
-        <v>2.930994980109862</v>
+        <v>2.939629869232318</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2507,16 +2507,16 @@
         <v>118002.8931473771</v>
       </c>
       <c r="C46">
-        <v>39214.67456532078</v>
+        <v>39330.20337691634</v>
       </c>
       <c r="D46">
-        <v>372786.5047490682</v>
+        <v>373884.7564201559</v>
       </c>
       <c r="E46">
-        <v>3.159130211184607</v>
+        <v>3.168437200545589</v>
       </c>
       <c r="F46">
-        <v>2.865901979371381</v>
+        <v>2.874345100562527</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2527,16 +2527,16 @@
         <v>119927.0983967194</v>
       </c>
       <c r="C47">
-        <v>39788.21928420808</v>
+        <v>39905.43779335958</v>
       </c>
       <c r="D47">
-        <v>378238.7935527184</v>
+        <v>379353.107997575</v>
       </c>
       <c r="E47">
-        <v>3.153905986297631</v>
+        <v>3.163197584774986</v>
       </c>
       <c r="F47">
-        <v>2.801538160150459</v>
+        <v>2.809791661623303</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2547,16 +2547,16 @@
         <v>121851.3036460617</v>
       </c>
       <c r="C48">
-        <v>40348.81377800203</v>
+        <v>40467.68383256027</v>
       </c>
       <c r="D48">
-        <v>383567.9736170567</v>
+        <v>384697.9881498634</v>
       </c>
       <c r="E48">
-        <v>3.147836437853767</v>
+        <v>3.157110155072986</v>
       </c>
       <c r="F48">
-        <v>2.737979427963786</v>
+        <v>2.746045681553601</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2567,16 +2567,16 @@
         <v>123775.508895404</v>
       </c>
       <c r="C49">
-        <v>40896.62818505332</v>
+        <v>41017.112134107</v>
       </c>
       <c r="D49">
-        <v>388775.6623284767</v>
+        <v>389921.0190283334</v>
       </c>
       <c r="E49">
-        <v>3.140974056968006</v>
+        <v>3.150227557196589</v>
       </c>
       <c r="F49">
-        <v>2.675292086306878</v>
+        <v>2.683173659183049</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2587,16 +2587,16 @@
         <v>125699.7141447463</v>
       </c>
       <c r="C50">
-        <v>41431.84512971261</v>
+        <v>41553.90586037286</v>
       </c>
       <c r="D50">
-        <v>393863.5957690479</v>
+        <v>395023.9418296574</v>
       </c>
       <c r="E50">
-        <v>3.133369064908964</v>
+        <v>3.142600160369319</v>
       </c>
       <c r="F50">
-        <v>2.613533554450351</v>
+        <v>2.621233182942953</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2607,16 +2607,16 @@
         <v>127623.9193940886</v>
       </c>
       <c r="C51">
-        <v>41954.6579952206</v>
+        <v>42078.25896431733</v>
       </c>
       <c r="D51">
-        <v>398833.6122980879</v>
+        <v>400008.6003290715</v>
       </c>
       <c r="E51">
-        <v>3.125069455566034</v>
+        <v>3.13427609987348</v>
       </c>
       <c r="F51">
-        <v>2.552753055151094</v>
+        <v>2.560273620603374</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2627,16 +2627,16 @@
         <v>129548.1246434309</v>
       </c>
       <c r="C52">
-        <v>42465.26933264521</v>
+        <v>42590.37459373603</v>
       </c>
       <c r="D52">
-        <v>403687.6374270406</v>
+        <v>404876.9257106927</v>
       </c>
       <c r="E52">
-        <v>3.116121044115096</v>
+        <v>3.125301325859239</v>
       </c>
       <c r="F52">
-        <v>2.492992270451785</v>
+        <v>2.500336777004836</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2647,16 +2647,16 @@
         <v>131472.3298927732</v>
       </c>
       <c r="C53">
-        <v>42963.88939925716</v>
+        <v>43090.4636253304</v>
       </c>
       <c r="D53">
-        <v>408427.6699248341</v>
+        <v>409630.9226319441</v>
       </c>
       <c r="E53">
-        <v>3.106567520769894</v>
+        <v>3.115719657254364</v>
       </c>
       <c r="F53">
-        <v>2.434285964393707</v>
+        <v>2.441457518605694</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2667,16 +2667,16 @@
         <v>133396.5351421155</v>
       </c>
       <c r="C54">
-        <v>43450.73481955838</v>
+        <v>43578.74332179129</v>
       </c>
       <c r="D54">
-        <v>413055.7690892138</v>
+        <v>414272.6564573872</v>
       </c>
       <c r="E54">
-        <v>3.096450508621984</v>
+        <v>3.105572839774565</v>
       </c>
       <c r="F54">
-        <v>2.37666257201785</v>
+        <v>2.383664364218157</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2687,16 +2687,16 @@
         <v>135320.7403914578</v>
       </c>
       <c r="C55">
-        <v>43926.02736210132</v>
+        <v>44055.43610501476</v>
       </c>
       <c r="D55">
-        <v>417574.0431188183</v>
+        <v>418804.2415965415</v>
       </c>
       <c r="E55">
-        <v>3.085809624680253</v>
+        <v>3.094900607142841</v>
       </c>
       <c r="F55">
-        <v>2.320144754493493</v>
+        <v>2.326980041772728</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2707,16 +2707,16 @@
         <v>137244.9456408001</v>
       </c>
       <c r="C56">
-        <v>44389.99282524855</v>
+        <v>44520.76843857906</v>
       </c>
       <c r="D56">
-        <v>421984.6385208745</v>
+        <v>423227.8308803749</v>
       </c>
       <c r="E56">
-        <v>3.074682543321488</v>
+        <v>3.083740744726981</v>
       </c>
       <c r="F56">
-        <v>2.264749920598836</v>
+        <v>2.271422011334993</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2727,16 +2727,16 @@
         <v>139169.1508901424</v>
       </c>
       <c r="C57">
-        <v>44842.8600251017</v>
+        <v>44974.96981269197</v>
       </c>
       <c r="D57">
-        <v>426289.7304901459</v>
+        <v>427545.6059119063</v>
       </c>
       <c r="E57">
-        <v>3.063105061456123</v>
+        <v>3.072129154897289</v>
       </c>
       <c r="F57">
-        <v>2.210490715091542</v>
+        <v>2.217002954914748</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2747,16 +2747,16 @@
         <v>141093.3561394847</v>
       </c>
       <c r="C58">
-        <v>45284.85987896682</v>
+        <v>45418.27182495593</v>
       </c>
       <c r="D58">
-        <v>430491.5141960777</v>
+        <v>431759.7683276836</v>
       </c>
       <c r="E58">
-        <v>3.051111164798535</v>
+        <v>3.06009992349212</v>
       </c>
       <c r="F58">
-        <v>2.157375474762368</v>
+        <v>2.163731233863445</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2767,16 +2767,16 @@
         <v>143017.561388827</v>
       </c>
       <c r="C59">
-        <v>45716.22457790631</v>
+        <v>45850.90735048227</v>
       </c>
       <c r="D59">
-        <v>434592.1969168261</v>
+        <v>435872.5319086382</v>
       </c>
       <c r="E59">
-        <v>3.03873309470915</v>
+        <v>3.047685386856905</v>
       </c>
       <c r="F59">
-        <v>2.10540865316265</v>
+        <v>2.111611314852917</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2787,16 +2787,16 @@
         <v>144941.7666381693</v>
       </c>
       <c r="C60">
-        <v>46137.1868421455</v>
+        <v>46273.10979510427</v>
       </c>
       <c r="D60">
-        <v>438593.9909609302</v>
+        <v>439886.1154809047</v>
       </c>
       <c r="E60">
-        <v>3.026001415146474</v>
+        <v>3.034916198993425</v>
       </c>
       <c r="F60">
-        <v>2.054591215150116</v>
+        <v>2.060644165583413</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2807,16 +2807,16 @@
         <v>146865.9718875116</v>
       </c>
       <c r="C61">
-        <v>46547.97925334755</v>
+        <v>46685.11242568478</v>
       </c>
       <c r="D61">
-        <v>442499.1073197149</v>
+        <v>443802.7365495226</v>
       </c>
       <c r="E61">
-        <v>3.01294507933149</v>
+        <v>3.021821398420613</v>
       </c>
       <c r="F61">
-        <v>2.029469756471949</v>
+        <v>2.035448697563113</v>
       </c>
     </row>
   </sheetData>
@@ -2857,16 +2857,16 @@
         <v>20075.2102041675</v>
       </c>
       <c r="C2">
-        <v>1555.106124179238</v>
+        <v>1559.195086302095</v>
       </c>
       <c r="D2">
-        <v>14783.30709033404</v>
+        <v>14822.17799554306</v>
       </c>
       <c r="E2">
-        <v>0.7363961293548553</v>
+        <v>0.7383323932750681</v>
       </c>
       <c r="F2">
-        <v>1.925320252643367</v>
+        <v>1.930382647720479</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2877,16 +2877,16 @@
         <v>21388.05358732089</v>
       </c>
       <c r="C3">
-        <v>1820.997549473961</v>
+        <v>1825.785640710849</v>
       </c>
       <c r="D3">
-        <v>17310.9510444681</v>
+        <v>17356.46808155701</v>
       </c>
       <c r="E3">
-        <v>0.8093747742772744</v>
+        <v>0.8115029266546322</v>
       </c>
       <c r="F3">
-        <v>2.009517714786316</v>
+        <v>2.014801496833864</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2897,16 +2897,16 @@
         <v>22700.89697047428</v>
       </c>
       <c r="C4">
-        <v>2110.144724750694</v>
+        <v>2115.69309326336</v>
       </c>
       <c r="D4">
-        <v>20059.67116070751</v>
+        <v>20112.41562251483</v>
       </c>
       <c r="E4">
-        <v>0.8836510375249905</v>
+        <v>0.8859744902888137</v>
       </c>
       <c r="F4">
-        <v>2.17733583358487</v>
+        <v>2.183060872933528</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2917,16 +2917,16 @@
         <v>24013.74035362767</v>
       </c>
       <c r="C5">
-        <v>2422.388333518647</v>
+        <v>2428.757708565533</v>
       </c>
       <c r="D5">
-        <v>23027.95292851743</v>
+        <v>23088.5021256607</v>
       </c>
       <c r="E5">
-        <v>0.958949026241082</v>
+        <v>0.9614704658940314</v>
       </c>
       <c r="F5">
-        <v>2.343472668333186</v>
+        <v>2.349634544251346</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2937,16 +2937,16 @@
         <v>25326.58373678106</v>
       </c>
       <c r="C6">
-        <v>2757.423313408181</v>
+        <v>2764.673622123387</v>
       </c>
       <c r="D6">
-        <v>26212.8963331516</v>
+        <v>26281.81995101284</v>
       </c>
       <c r="E6">
-        <v>1.034995347401844</v>
+        <v>1.037716741592926</v>
       </c>
       <c r="F6">
-        <v>2.506890868273533</v>
+        <v>2.51348243244213</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2957,16 +2957,16 @@
         <v>26639.42711993445</v>
       </c>
       <c r="C7">
-        <v>3114.803826586276</v>
+        <v>3122.99382382763</v>
       </c>
       <c r="D7">
-        <v>29610.26310591856</v>
+        <v>29688.11968586857</v>
       </c>
       <c r="E7">
-        <v>1.111520265530073</v>
+        <v>1.114442872671716</v>
       </c>
       <c r="F7">
-        <v>2.666593989433909</v>
+        <v>2.673605473505834</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2977,16 +2977,16 @@
         <v>27952.27050308784</v>
       </c>
       <c r="C8">
-        <v>3493.949587994934</v>
+        <v>3503.136502831387</v>
       </c>
       <c r="D8">
-        <v>33214.53688232141</v>
+        <v>33301.87046112248</v>
       </c>
       <c r="E8">
-        <v>1.188258995942825</v>
+        <v>1.191383378228387</v>
       </c>
       <c r="F8">
-        <v>2.82163615446854</v>
+        <v>2.829055303027419</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2997,16 +2997,16 @@
         <v>29265.11388624123</v>
       </c>
       <c r="C9">
-        <v>3894.153503861738</v>
+        <v>3904.392706145302</v>
       </c>
       <c r="D9">
-        <v>37018.99581603935</v>
+        <v>37116.33275617768</v>
       </c>
       <c r="E9">
-        <v>1.264953075526679</v>
+        <v>1.268279115552243</v>
       </c>
       <c r="F9">
-        <v>2.971131216711757</v>
+        <v>2.978943444326499</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3017,16 +3017,16 @@
         <v>30577.95726939462</v>
       </c>
       <c r="C10">
-        <v>4314.590531094665</v>
+        <v>4325.935221327039</v>
       </c>
       <c r="D10">
-        <v>41015.79679900243</v>
+        <v>41123.64284046691</v>
       </c>
       <c r="E10">
-        <v>1.341351759950787</v>
+        <v>1.344878681010763</v>
       </c>
       <c r="F10">
-        <v>3.114261146251946</v>
+        <v>3.122449716581465</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3037,16 +3037,16 @@
         <v>31890.80065254801</v>
       </c>
       <c r="C11">
-        <v>4754.327632067194</v>
+        <v>4766.828557441296</v>
       </c>
       <c r="D11">
-        <v>45196.07009457648</v>
+        <v>45314.90765546399</v>
       </c>
       <c r="E11">
-        <v>1.417213402290839</v>
+        <v>1.420939792298486</v>
       </c>
       <c r="F11">
-        <v>3.250283399166617</v>
+        <v>3.258829623441028</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3057,16 +3057,16 @@
         <v>33203.6440357014</v>
       </c>
       <c r="C12">
-        <v>5212.334669431812</v>
+        <v>5226.039868519885</v>
       </c>
       <c r="D12">
-        <v>49550.02290694084</v>
+        <v>49680.30865638453</v>
       </c>
       <c r="E12">
-        <v>1.492306773728311</v>
+        <v>1.496230612608875</v>
       </c>
       <c r="F12">
-        <v>3.378537077812306</v>
+        <v>3.387420529511871</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3077,16 +3077,16 @@
         <v>34516.48741885479</v>
       </c>
       <c r="C13">
-        <v>5687.496062407267</v>
+        <v>5702.450640497785</v>
       </c>
       <c r="D13">
-        <v>54067.05018926504</v>
+        <v>54209.21291171922</v>
       </c>
       <c r="E13">
-        <v>1.56641229257096</v>
+        <v>1.570530982886375</v>
       </c>
       <c r="F13">
-        <v>3.498447739398501</v>
+        <v>3.507646481576143</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3097,16 +3097,16 @@
         <v>35829.33080200817</v>
       </c>
       <c r="C14">
-        <v>6178.623009743652</v>
+        <v>6194.868946317008</v>
       </c>
       <c r="D14">
-        <v>58735.85083889533</v>
+        <v>58890.28960394153</v>
       </c>
       <c r="E14">
-        <v>1.639323133425737</v>
+        <v>1.643633533915761</v>
       </c>
       <c r="F14">
-        <v>3.609530760636067</v>
+        <v>3.619021582086795</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3117,16 +3117,16 @@
         <v>37142.17418516156</v>
       </c>
       <c r="C15">
-        <v>6684.466075341983</v>
+        <v>6702.042064638546</v>
       </c>
       <c r="D15">
-        <v>63544.54734004436</v>
+        <v>63711.6299867831</v>
       </c>
       <c r="E15">
-        <v>1.710846193958959</v>
+        <v>1.715344655624284</v>
       </c>
       <c r="F15">
-        <v>3.711393216403899</v>
+        <v>3.721151872773996</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3137,16 +3137,16 @@
         <v>38455.01756831495</v>
       </c>
       <c r="C16">
-        <v>7203.727930116178</v>
+        <v>7222.669255207516</v>
       </c>
       <c r="D16">
-        <v>68480.80689176779</v>
+        <v>68660.86883170188</v>
       </c>
       <c r="E16">
-        <v>1.780802902250983</v>
+        <v>1.785485306559191</v>
       </c>
       <c r="F16">
-        <v>3.803734278409221</v>
+        <v>3.813735734353612</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -3157,16 +3157,16 @@
         <v>39767.86095146834</v>
       </c>
       <c r="C17">
-        <v>7735.076047724549</v>
+        <v>7755.414487966533</v>
       </c>
       <c r="D17">
-        <v>73531.96209741093</v>
+        <v>73725.30543466666</v>
       </c>
       <c r="E17">
-        <v>1.84902985320602</v>
+        <v>1.853891651970899</v>
       </c>
       <c r="F17">
-        <v>3.886344184100927</v>
+        <v>3.89656285272945</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3177,16 +3177,16 @@
         <v>41080.70433462173</v>
       </c>
       <c r="C18">
-        <v>8277.15516164062</v>
+        <v>8298.918932880873</v>
       </c>
       <c r="D18">
-        <v>78685.12938527492</v>
+        <v>78892.0223481962</v>
       </c>
       <c r="E18">
-        <v>1.915379267705524</v>
+        <v>1.920415524173671</v>
       </c>
       <c r="F18">
-        <v>3.959101865219292</v>
+        <v>3.969511841307553</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3197,16 +3197,16 @@
         <v>42393.54771777512</v>
       </c>
       <c r="C19">
-        <v>8828.59930587847</v>
+        <v>8851.813032323453</v>
       </c>
       <c r="D19">
-        <v>83927.32347137769</v>
+        <v>84148.00014508594</v>
       </c>
       <c r="E19">
-        <v>1.979719273086172</v>
+        <v>1.984924703761079</v>
       </c>
       <c r="F19">
-        <v>4.021971358222238</v>
+        <v>4.032546641984087</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3217,16 +3217,16 @@
         <v>43706.39110092851</v>
       </c>
       <c r="C20">
-        <v>9388.043280605782</v>
+        <v>9412.72799683529</v>
       </c>
       <c r="D20">
-        <v>89245.56635502394</v>
+        <v>89480.22670056864</v>
       </c>
       <c r="E20">
-        <v>2.041934007979167</v>
+        <v>2.04730302472097</v>
       </c>
       <c r="F20">
-        <v>4.074997144673013</v>
+        <v>4.085711853281152</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3237,16 +3237,16 @@
         <v>45019.2344840819</v>
       </c>
       <c r="C21">
-        <v>9954.133405861507</v>
+        <v>9980.306587118774</v>
       </c>
       <c r="D21">
-        <v>94626.98954688355</v>
+        <v>94875.79968918902</v>
       </c>
       <c r="E21">
-        <v>2.101923558481257</v>
+        <v>2.107450310438655</v>
       </c>
       <c r="F21">
-        <v>4.118298588141747</v>
+        <v>4.129127152620853</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3257,16 +3257,16 @@
         <v>46332.07786723529</v>
       </c>
       <c r="C22">
-        <v>10525.53745061396</v>
+        <v>10553.21306920301</v>
       </c>
       <c r="D22">
-        <v>100058.9284576076</v>
+        <v>100322.0212216032</v>
       </c>
       <c r="E22">
-        <v>2.1596037359759</v>
+        <v>2.16528215093388</v>
       </c>
       <c r="F22">
-        <v>4.152063645273781</v>
+        <v>4.162980990857625</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3277,16 +3277,16 @@
         <v>47644.92125038867</v>
       </c>
       <c r="C23">
-        <v>11100.95364944489</v>
+        <v>11130.14225483613</v>
       </c>
       <c r="D23">
-        <v>105529.0081131424</v>
+        <v>105806.4837852706</v>
       </c>
       <c r="E23">
-        <v>2.214905709646472</v>
+        <v>2.220729534407771</v>
       </c>
       <c r="F23">
-        <v>4.176542032753138</v>
+        <v>4.187523741275095</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3297,16 +3297,16 @@
         <v>48957.76463354206</v>
       </c>
       <c r="C24">
-        <v>11679.11874428953</v>
+        <v>11709.82756437018</v>
       </c>
       <c r="D24">
-        <v>111025.2196019315</v>
+        <v>111317.1468926647</v>
       </c>
       <c r="E24">
-        <v>2.267775508807967</v>
+        <v>2.273738348265983</v>
       </c>
       <c r="F24">
-        <v>4.192038029567525</v>
+        <v>4.203060482925505</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3317,16 +3317,16 @@
         <v>50270.60801669546</v>
       </c>
       <c r="C25">
-        <v>12258.81501307109</v>
+        <v>12291.04807387651</v>
       </c>
       <c r="D25">
-        <v>116535.9868912326</v>
+        <v>116842.404073275</v>
       </c>
       <c r="E25">
-        <v>2.318173411639056</v>
+        <v>2.324268766243494</v>
       </c>
       <c r="F25">
-        <v>4.198903086100577</v>
+        <v>4.209943590288459</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3337,16 +3337,16 @@
         <v>51583.45139984885</v>
       </c>
       <c r="C26">
-        <v>12838.87627003607</v>
+        <v>12872.63453125823</v>
       </c>
       <c r="D26">
-        <v>122050.2238681105</v>
+        <v>122371.1400645831</v>
       </c>
       <c r="E26">
-        <v>2.366073237752916</v>
+        <v>2.372294539115344</v>
       </c>
       <c r="F26">
-        <v>4.19752839912328</v>
+        <v>4.208565288739218</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -3357,16 +3357,16 @@
         <v>52896.29478300223</v>
       </c>
       <c r="C27">
-        <v>13418.19284356514</v>
+        <v>13453.47434714965</v>
       </c>
       <c r="D27">
-        <v>127557.3816600074</v>
+        <v>127892.7782570557</v>
       </c>
       <c r="E27">
-        <v>2.411461562351186</v>
+        <v>2.4178022067843</v>
       </c>
       <c r="F27">
-        <v>4.188337595784674</v>
+        <v>4.199350319302781</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -3377,16 +3377,16 @@
         <v>54209.13816615562</v>
       </c>
       <c r="C28">
-        <v>13995.71555579093</v>
+        <v>14032.51558499801</v>
       </c>
       <c r="D28">
-        <v>133047.4864661875</v>
+        <v>133397.3186250626</v>
       </c>
       <c r="E28">
-        <v>2.454336869521622</v>
+        <v>2.460790249352212</v>
       </c>
       <c r="F28">
-        <v>4.171779651273541</v>
+        <v>4.182748837693524</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -3397,16 +3397,16 @@
         <v>55521.98154930901</v>
       </c>
       <c r="C29">
-        <v>14570.45874423254</v>
+        <v>14608.76999064298</v>
       </c>
       <c r="D29">
-        <v>138511.1682823043</v>
+        <v>138875.3665269726</v>
       </c>
       <c r="E29">
-        <v>2.494708661636881</v>
+        <v>2.501268194177067</v>
       </c>
       <c r="F29">
-        <v>4.148322144956671</v>
+        <v>4.159229652721187</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -3417,16 +3417,16 @@
         <v>56834.8249324624</v>
       </c>
       <c r="C30">
-        <v>15141.50237872579</v>
+        <v>15181.31511481312</v>
       </c>
       <c r="D30">
-        <v>143939.6810245776</v>
+        <v>144318.1528822433</v>
       </c>
       <c r="E30">
-        <v>2.532596540864216</v>
+        <v>2.539255694967629</v>
       </c>
       <c r="F30">
-        <v>4.118444939415117</v>
+        <v>4.129273888707048</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -3437,16 +3437,16 @@
         <v>58147.66831561578</v>
       </c>
       <c r="C31">
-        <v>15707.9933371767</v>
+        <v>15749.29559223386</v>
       </c>
       <c r="D31">
-        <v>149324.9146574897</v>
+        <v>149717.5463310068</v>
       </c>
       <c r="E31">
-        <v>2.568029277579611</v>
+        <v>2.574781597748083</v>
       </c>
       <c r="F31">
-        <v>4.082634346701258</v>
+        <v>4.093369136401837</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -3457,16 +3457,16 @@
         <v>59460.51169876917</v>
       </c>
       <c r="C32">
-        <v>16269.14591118351</v>
+        <v>16311.92364857887</v>
       </c>
       <c r="D32">
-        <v>154659.4000003806</v>
+        <v>155066.0580533022</v>
       </c>
       <c r="E32">
-        <v>2.60104387906877</v>
+        <v>2.607883007110281</v>
       </c>
       <c r="F32">
-        <v>4.041377826986029</v>
+        <v>4.052004137693572</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -3477,16 +3477,16 @@
         <v>60773.35508192256</v>
       </c>
       <c r="C33">
-        <v>16824.24161753056</v>
+        <v>16868.47891146842</v>
       </c>
       <c r="D33">
-        <v>159936.3069354525</v>
+        <v>160356.8399723691</v>
       </c>
       <c r="E33">
-        <v>2.631684670360196</v>
+        <v>2.638604364629991</v>
       </c>
       <c r="F33">
-        <v>3.995159247069048</v>
+        <v>4.005664031650656</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -3497,16 +3497,16 @@
         <v>62086.19846507596</v>
       </c>
       <c r="C34">
-        <v>17372.6283941877</v>
+        <v>17418.30760435466</v>
       </c>
       <c r="D34">
-        <v>165149.4367646979</v>
+        <v>165583.6770914784</v>
       </c>
       <c r="E34">
-        <v>2.660002397434527</v>
+        <v>2.666996549718224</v>
       </c>
       <c r="F34">
-        <v>3.944454710352238</v>
+        <v>3.954826173530951</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -3517,16 +3517,16 @@
         <v>63399.04184822935</v>
       </c>
       <c r="C35">
-        <v>17913.7192600226</v>
+        <v>17960.82120270988</v>
       </c>
       <c r="D35">
-        <v>170293.2094687209</v>
+        <v>170740.974719253</v>
       </c>
       <c r="E35">
-        <v>2.6860533614433</v>
+        <v>2.693116011563535</v>
       </c>
       <c r="F35">
-        <v>3.889728956058944</v>
+        <v>3.899956524533025</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -3537,16 +3537,16 @@
         <v>64711.88523138273</v>
       </c>
       <c r="C36">
-        <v>18446.99051624682</v>
+        <v>18495.49463074347</v>
       </c>
       <c r="D36">
-        <v>175362.6466091422</v>
+        <v>175823.7413271166</v>
       </c>
       <c r="E36">
-        <v>2.709898590994814</v>
+        <v>2.717023939241519</v>
       </c>
       <c r="F36">
-        <v>3.831432313826786</v>
+        <v>3.841506598381356</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -3557,16 +3557,16 @@
         <v>66024.72861453613</v>
       </c>
       <c r="C37">
-        <v>18971.97956497185</v>
+        <v>19021.86407422213</v>
       </c>
       <c r="D37">
-        <v>180353.350591136</v>
+        <v>180827.5677573032</v>
       </c>
       <c r="E37">
-        <v>2.731603058061326</v>
+        <v>2.738785475560316</v>
       </c>
       <c r="F37">
-        <v>3.769998190317769</v>
+        <v>3.779910941327976</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -3577,16 +3577,16 @@
         <v>67337.57199768951</v>
       </c>
       <c r="C38">
-        <v>19488.28241644458</v>
+        <v>19539.52448115089</v>
       </c>
       <c r="D38">
-        <v>185261.48096646</v>
+        <v>185748.6034635796</v>
       </c>
       <c r="E38">
-        <v>2.75123494165808</v>
+        <v>2.758468978803587</v>
       </c>
       <c r="F38">
-        <v>3.705841057100386</v>
+        <v>3.715585114743934</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -3597,16 +3597,16 @@
         <v>68650.41538084291</v>
       </c>
       <c r="C39">
-        <v>19995.55095184662</v>
+        <v>20048.12681737535</v>
       </c>
       <c r="D39">
-        <v>190083.7284128008</v>
+        <v>190583.5304221728</v>
       </c>
       <c r="E39">
-        <v>2.768864942160921</v>
+        <v>2.776145335245206</v>
       </c>
       <c r="F39">
-        <v>3.639354903627287</v>
+        <v>3.648924144029093</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -3617,16 +3617,16 @@
         <v>69963.25876399629</v>
       </c>
       <c r="C40">
-        <v>20493.4900032346</v>
+        <v>20547.37513884398</v>
       </c>
       <c r="D40">
-        <v>194817.2869748079</v>
+        <v>195329.5352998141</v>
       </c>
       <c r="E40">
-        <v>2.784565647977829</v>
+        <v>2.791887324155524</v>
       </c>
       <c r="F40">
-        <v>3.570912115469755</v>
+        <v>3.580301393897233</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -3637,16 +3637,16 @@
         <v>71276.10214714968</v>
       </c>
       <c r="C41">
-        <v>20981.85430650241</v>
+        <v>21037.02353655856</v>
       </c>
       <c r="D41">
-        <v>199459.8250980343</v>
+        <v>199984.2804115184</v>
       </c>
       <c r="E41">
-        <v>2.798410955277114</v>
+        <v>2.805769036003826</v>
       </c>
       <c r="F41">
-        <v>3.500862735875512</v>
+        <v>3.510067827992204</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -3657,16 +3657,16 @@
         <v>72588.94553030307</v>
       </c>
       <c r="C42">
-        <v>21460.44537736014</v>
+        <v>21516.87300433896</v>
       </c>
       <c r="D42">
-        <v>204009.4559310528</v>
+        <v>204545.8739446124</v>
       </c>
       <c r="E42">
-        <v>2.810475540602622</v>
+        <v>2.817865343686835</v>
       </c>
       <c r="F42">
-        <v>3.429534067957993</v>
+        <v>3.4385516100311</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -3677,16 +3677,16 @@
         <v>73901.78891345646</v>
       </c>
       <c r="C43">
-        <v>21929.10835441905</v>
+        <v>21986.76827360724</v>
       </c>
       <c r="D43">
-        <v>208464.7073148699</v>
+        <v>209012.8398692399</v>
       </c>
       <c r="E43">
-        <v>2.820834385470626</v>
+        <v>2.828251425875588</v>
       </c>
       <c r="F43">
-        <v>3.357230575180493</v>
+        <v>3.366058004026781</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -3697,16 +3697,16 @@
         <v>75214.63229660985</v>
       </c>
       <c r="C44">
-        <v>22387.72884768378</v>
+        <v>22446.59465359351</v>
       </c>
       <c r="D44">
-        <v>212824.4918237447</v>
+        <v>213384.0879004066</v>
       </c>
       <c r="E44">
-        <v>2.829562351438064</v>
+        <v>2.837002340966366</v>
       </c>
       <c r="F44">
-        <v>3.284234039054021</v>
+        <v>3.292869532400403</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -3717,16 +3717,16 @@
         <v>76527.47567976324</v>
       </c>
       <c r="C45">
-        <v>22836.2298251942</v>
+        <v>22896.27490979146</v>
       </c>
       <c r="D45">
-        <v>217088.0771686683</v>
+        <v>217658.8838236385</v>
       </c>
       <c r="E45">
-        <v>2.83673380364844</v>
+        <v>2.84419264963676</v>
       </c>
       <c r="F45">
-        <v>3.210803934914804</v>
+        <v>3.219246352747023</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -3737,16 +3737,16 @@
         <v>77840.31906291662</v>
       </c>
       <c r="C46">
-        <v>23274.56856530923</v>
+        <v>23335.76620822868</v>
       </c>
       <c r="D46">
-        <v>221255.0572248562</v>
+        <v>221836.8204462958</v>
       </c>
       <c r="E46">
-        <v>2.842422280489634</v>
+        <v>2.849896083634882</v>
       </c>
       <c r="F46">
-        <v>3.137177989106773</v>
+        <v>3.145426816483019</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -3757,16 +3757,16 @@
         <v>79153.16244607003</v>
       </c>
       <c r="C47">
-        <v>23702.73369724518</v>
+        <v>23765.05714822339</v>
       </c>
       <c r="D47">
-        <v>225325.3238982148</v>
+        <v>225917.7893900644</v>
       </c>
       <c r="E47">
-        <v>2.846700206725629</v>
+        <v>2.854185258156812</v>
       </c>
       <c r="F47">
-        <v>3.063572883704364</v>
+        <v>3.071628175421961</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -3777,16 +3777,16 @@
         <v>80466.0058292234</v>
       </c>
       <c r="C48">
-        <v>24120.7423480075</v>
+        <v>24184.16490181439</v>
       </c>
       <c r="D48">
-        <v>229299.0400032151</v>
+        <v>229901.9538975162</v>
       </c>
       <c r="E48">
-        <v>2.849638647280028</v>
+        <v>2.857131424982712</v>
       </c>
       <c r="F48">
-        <v>2.990185077927695</v>
+        <v>2.998047405349534</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -3797,16 +3797,16 @@
         <v>81778.84921237681</v>
       </c>
       <c r="C49">
-        <v>24528.63740980794</v>
+        <v>24593.1324739933</v>
       </c>
       <c r="D49">
-        <v>233176.6132861376</v>
+        <v>233789.7227870511</v>
       </c>
       <c r="E49">
-        <v>2.851307098741217</v>
+        <v>2.858804263433781</v>
       </c>
       <c r="F49">
-        <v>2.917191718517608</v>
+        <v>2.924862118792328</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3817,16 +3817,16 @@
         <v>83091.69259553018</v>
       </c>
       <c r="C50">
-        <v>24926.48493844633</v>
+        <v>24992.02609424563</v>
       </c>
       <c r="D50">
-        <v>236958.6716933065</v>
+        <v>237581.7256561013</v>
       </c>
       <c r="E50">
-        <v>2.851773315616071</v>
+        <v>2.859271706169116</v>
       </c>
       <c r="F50">
-        <v>2.844751614448841</v>
+        <v>2.852231542293987</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -3837,16 +3837,16 @@
         <v>84404.53597868356</v>
       </c>
       <c r="C51">
-        <v>25314.37168994836</v>
+        <v>25380.93274671145</v>
       </c>
       <c r="D51">
-        <v>240646.0399536257</v>
+        <v>241278.7894020951</v>
       </c>
       <c r="E51">
-        <v>2.851103168370016</v>
+        <v>2.858599796852509</v>
       </c>
       <c r="F51">
-        <v>2.773006254394975</v>
+        <v>2.780297536555319</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -3857,16 +3857,16 @@
         <v>85717.37936183697</v>
       </c>
       <c r="C52">
-        <v>25692.40279997608</v>
+        <v>25759.95784349424</v>
       </c>
       <c r="D52">
-        <v>244239.7175183573</v>
+        <v>244881.9161042299</v>
       </c>
       <c r="E52">
-        <v>2.849360530346516</v>
+        <v>2.856852576774601</v>
       </c>
       <c r="F52">
-        <v>2.702080848264559</v>
+        <v>2.709185640709068</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -3877,16 +3877,16 @@
         <v>87030.22274499034</v>
       </c>
       <c r="C53">
-        <v>26060.69960814299</v>
+        <v>26129.22304325523</v>
       </c>
       <c r="D53">
-        <v>247740.857878405</v>
+        <v>248392.2622863733</v>
       </c>
       <c r="E53">
-        <v>2.846607190749325</v>
+        <v>2.854091997606329</v>
       </c>
       <c r="F53">
-        <v>2.632085376855781</v>
+        <v>2.639006124734507</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3897,16 +3897,16 @@
         <v>88343.06612814374</v>
       </c>
       <c r="C54">
-        <v>26419.39762734438</v>
+        <v>26488.86421520437</v>
       </c>
       <c r="D54">
-        <v>251150.7492601571</v>
+        <v>251811.1195621478</v>
       </c>
       <c r="E54">
-        <v>2.842902790988224</v>
+        <v>2.850377857577297</v>
       </c>
       <c r="F54">
-        <v>2.563115636207962</v>
+        <v>2.569855036554963</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -3917,16 +3917,16 @@
         <v>89655.90951129713</v>
       </c>
       <c r="C55">
-        <v>26768.64465652738</v>
+        <v>26839.0295469081</v>
       </c>
       <c r="D55">
-        <v>254470.7966849102</v>
+        <v>255139.8966471825</v>
       </c>
       <c r="E55">
-        <v>2.838304781826406</v>
+        <v>2.84576775851048</v>
       </c>
       <c r="F55">
-        <v>2.495254265538035</v>
+        <v>2.501815232677199</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -3937,16 +3937,16 @@
         <v>90968.75289445052</v>
       </c>
       <c r="C56">
-        <v>27108.59903394231</v>
+        <v>27179.87779294791</v>
       </c>
       <c r="D56">
-        <v>257702.5053637509</v>
+        <v>258380.1027103331</v>
       </c>
       <c r="E56">
-        <v>2.832868398918897</v>
+        <v>2.840317081296333</v>
       </c>
       <c r="F56">
-        <v>2.4285717497383</v>
+        <v>2.434957383324916</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -3957,16 +3957,16 @@
         <v>92281.59627760391</v>
       </c>
       <c r="C57">
-        <v>27439.42802680757</v>
+        <v>27511.57666035094</v>
       </c>
       <c r="D57">
-        <v>260847.4653892246</v>
+        <v>261533.3320250997</v>
       </c>
       <c r="E57">
-        <v>2.826646654491502</v>
+        <v>2.834078977549849</v>
       </c>
       <c r="F57">
-        <v>2.36312738927387</v>
+        <v>2.36934094488657</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -3977,16 +3977,16 @@
         <v>93594.4396607573</v>
       </c>
       <c r="C58">
-        <v>27761.30635245138</v>
+        <v>27834.30132584338</v>
       </c>
       <c r="D58">
-        <v>263907.3376768644</v>
+        <v>264601.2498741905</v>
       </c>
       <c r="E58">
-        <v>2.819690343074051</v>
+        <v>2.82710437535889</v>
       </c>
       <c r="F58">
-        <v>2.298970231961261</v>
+        <v>2.305015094143921</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -3997,16 +3997,16 @@
         <v>94907.28304391068</v>
       </c>
       <c r="C59">
-        <v>28074.41482533843</v>
+        <v>28148.23307931949</v>
       </c>
       <c r="D59">
-        <v>266883.8411034184</v>
+        <v>267585.5796539307</v>
       </c>
       <c r="E59">
-        <v>2.812048059366945</v>
+        <v>2.819441997197698</v>
       </c>
       <c r="F59">
-        <v>2.236139962545971</v>
+        <v>2.242019620188689</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4017,16 +4017,16 @@
         <v>96220.12642706408</v>
       </c>
       <c r="C60">
-        <v>28378.93912391735</v>
+        <v>28453.5580874468</v>
       </c>
       <c r="D60">
-        <v>269778.740784131</v>
+        <v>270488.0911207201</v>
       </c>
       <c r="E60">
-        <v>2.803766226483046</v>
+        <v>2.811138388243057</v>
       </c>
       <c r="F60">
-        <v>2.174667747235286</v>
+        <v>2.180385771175903</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -4037,16 +4037,16 @@
         <v>97532.96981021746</v>
       </c>
       <c r="C61">
-        <v>28675.06867091137</v>
+        <v>28750.46627101249</v>
       </c>
       <c r="D61">
-        <v>272593.8374284483</v>
+        <v>273310.5897187509</v>
       </c>
       <c r="E61">
-        <v>2.794889132965698</v>
+        <v>2.802237953489643</v>
       </c>
       <c r="F61">
-        <v>2.144274542143451</v>
+        <v>2.149912650853512</v>
       </c>
     </row>
   </sheetData>
@@ -4087,16 +4087,16 @@
         <v>30287.18702759737</v>
       </c>
       <c r="C2">
-        <v>3047.621403891404</v>
+        <v>3076.666818398698</v>
       </c>
       <c r="D2">
-        <v>28971.60676579572</v>
+        <v>29247.72122226344</v>
       </c>
       <c r="E2">
-        <v>0.9565631413507334</v>
+        <v>0.9656796847991602</v>
       </c>
       <c r="F2">
-        <v>2.082262026191564</v>
+        <v>2.102107064550433</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4107,16 +4107,16 @@
         <v>32287.2500206046</v>
       </c>
       <c r="C3">
-        <v>3485.715586651419</v>
+        <v>3518.936266208123</v>
       </c>
       <c r="D3">
-        <v>33136.26198612572</v>
+        <v>33452.06776940983</v>
       </c>
       <c r="E3">
-        <v>1.026295579988364</v>
+        <v>1.036076709786739</v>
       </c>
       <c r="F3">
-        <v>2.140163960588038</v>
+        <v>2.160560834448249</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4127,16 +4127,16 @@
         <v>34287.31301361182</v>
       </c>
       <c r="C4">
-        <v>3948.17413884292</v>
+        <v>3985.80228854132</v>
       </c>
       <c r="D4">
-        <v>37532.53223887554</v>
+        <v>37890.23676050495</v>
       </c>
       <c r="E4">
-        <v>1.094647814017254</v>
+        <v>1.105080376098961</v>
       </c>
       <c r="F4">
-        <v>2.251717868132796</v>
+        <v>2.273177908658133</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4147,16 +4147,16 @@
         <v>36287.37600661905</v>
       </c>
       <c r="C5">
-        <v>4433.20873289103</v>
+        <v>4475.459514133006</v>
       </c>
       <c r="D5">
-        <v>42143.41714361678</v>
+        <v>42545.06579266721</v>
       </c>
       <c r="E5">
-        <v>1.16137957001712</v>
+        <v>1.172448120385082</v>
       </c>
       <c r="F5">
-        <v>2.354529526377292</v>
+        <v>2.376969415392368</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4167,16 +4167,16 @@
         <v>38287.43899962628</v>
       </c>
       <c r="C6">
-        <v>4938.929073301575</v>
+        <v>4985.999631991379</v>
       </c>
       <c r="D6">
-        <v>46950.94698217567</v>
+        <v>47398.41388697757</v>
       </c>
       <c r="E6">
-        <v>1.226275462890948</v>
+        <v>1.237962504816272</v>
       </c>
       <c r="F6">
-        <v>2.448177816075377</v>
+        <v>2.471510221919711</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4187,16 +4187,16 @@
         <v>40287.50199263351</v>
       </c>
       <c r="C7">
-        <v>5463.369631081532</v>
+        <v>5515.438380611479</v>
       </c>
       <c r="D7">
-        <v>51936.43684408402</v>
+        <v>52431.41805606861</v>
       </c>
       <c r="E7">
-        <v>1.289145126287068</v>
+        <v>1.301431348750677</v>
       </c>
       <c r="F7">
-        <v>2.532366855426456</v>
+        <v>2.556501626532369</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4207,16 +4207,16 @@
         <v>42287.56498564074</v>
       </c>
       <c r="C8">
-        <v>6004.515607581998</v>
+        <v>6061.741759267063</v>
       </c>
       <c r="D8">
-        <v>57080.73344668876</v>
+        <v>57624.74247655793</v>
       </c>
       <c r="E8">
-        <v>1.349823132783153</v>
+        <v>1.362687648156736</v>
       </c>
       <c r="F8">
-        <v>2.606921340365708</v>
+        <v>2.63176665442675</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4227,16 +4227,16 @@
         <v>44287.62797864796</v>
       </c>
       <c r="C9">
-        <v>6560.327708174262</v>
+        <v>6622.851037792668</v>
       </c>
       <c r="D9">
-        <v>62364.45064117653</v>
+        <v>62958.81623956738</v>
       </c>
       <c r="E9">
-        <v>1.408168680229246</v>
+        <v>1.421589258966888</v>
       </c>
       <c r="F9">
-        <v>2.671780011147581</v>
+        <v>2.697243462020118</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4247,16 +4247,16 @@
         <v>46287.6909716552</v>
       </c>
       <c r="C10">
-        <v>7128.765356917394</v>
+        <v>7196.706192499046</v>
       </c>
       <c r="D10">
-        <v>67768.19009819419</v>
+        <v>68414.0561395922</v>
       </c>
       <c r="E10">
-        <v>1.464065039228093</v>
+        <v>1.47801833929211</v>
       </c>
       <c r="F10">
-        <v>2.726987515664265</v>
+        <v>2.752977122722266</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4267,16 +4267,16 @@
         <v>48287.75396466242</v>
       </c>
       <c r="C11">
-        <v>7707.808046426167</v>
+        <v>7781.267459516405</v>
       </c>
       <c r="D11">
-        <v>73272.74426612216</v>
+        <v>73971.07156707202</v>
       </c>
       <c r="E11">
-        <v>1.517418770807689</v>
+        <v>1.531880559638474</v>
       </c>
       <c r="F11">
-        <v>2.772684985978571</v>
+        <v>2.79911011365784</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4287,16 +4287,16 @@
         <v>50287.81695766964</v>
       </c>
       <c r="C12">
-        <v>8295.474587268107</v>
+        <v>8374.534767648214</v>
       </c>
       <c r="D12">
-        <v>78859.27936163916</v>
+        <v>79610.84924295076</v>
       </c>
       <c r="E12">
-        <v>1.568158733715164</v>
+        <v>1.583104100740029</v>
       </c>
       <c r="F12">
-        <v>2.80909966722616</v>
+        <v>2.835871845726647</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4307,16 +4307,16 @@
         <v>52287.87995067688</v>
       </c>
       <c r="C13">
-        <v>8889.840093810444</v>
+        <v>8974.564886102096</v>
       </c>
       <c r="D13">
-        <v>84509.4968422981</v>
+        <v>85314.91623016998</v>
       </c>
       <c r="E13">
-        <v>1.616234908013403</v>
+        <v>1.631638465943685</v>
       </c>
       <c r="F13">
-        <v>2.836533940557208</v>
+        <v>2.86356758192825</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4327,16 +4327,16 @@
         <v>54287.9429436841</v>
       </c>
       <c r="C14">
-        <v>9489.050614615908</v>
+        <v>9579.486194320887</v>
       </c>
       <c r="D14">
-        <v>90205.77248747405</v>
+        <v>91065.48034013055</v>
       </c>
       <c r="E14">
-        <v>1.661617066261831</v>
+        <v>1.677453139725663</v>
       </c>
       <c r="F14">
-        <v>2.855354067648824</v>
+        <v>2.882567074603706</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4347,16 +4347,16 @@
         <v>56288.00593669133</v>
       </c>
       <c r="C15">
-        <v>10091.33538212918</v>
+        <v>10187.51104841496</v>
       </c>
       <c r="D15">
-        <v>95931.27284757223</v>
+        <v>96845.54769172192</v>
       </c>
       <c r="E15">
-        <v>1.704293325925753</v>
+        <v>1.720536126304541</v>
       </c>
       <c r="F15">
-        <v>2.865978957209514</v>
+        <v>2.893293224879058</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4367,16 +4367,16 @@
         <v>58288.06892969856</v>
       </c>
       <c r="C16">
-        <v>10695.01671616608</v>
+        <v>10796.94577903683</v>
       </c>
       <c r="D16">
-        <v>101670.0493895784</v>
+        <v>102639.0177541288</v>
       </c>
       <c r="E16">
-        <v>1.744268617171089</v>
+        <v>1.760892402833282</v>
       </c>
       <c r="F16">
-        <v>2.868869217489396</v>
+        <v>2.896211030840228</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4387,16 +4387,16 @@
         <v>60288.13192270578</v>
       </c>
       <c r="C17">
-        <v>11298.51766704085</v>
+        <v>11406.19840735137</v>
       </c>
       <c r="D17">
-        <v>107407.1111549285</v>
+        <v>108430.7566971676</v>
       </c>
       <c r="E17">
-        <v>1.781563099228767</v>
+        <v>1.79854232067075</v>
       </c>
       <c r="F17">
-        <v>2.864516716586641</v>
+        <v>2.891817048343758</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4407,16 +4407,16 @@
         <v>62288.19491571302</v>
       </c>
       <c r="C18">
-        <v>11900.36752617021</v>
+        <v>12013.7842081588</v>
       </c>
       <c r="D18">
-        <v>113128.4771449695</v>
+        <v>114206.6502760084</v>
       </c>
       <c r="E18">
-        <v>1.816210556399209</v>
+        <v>1.833519986099296</v>
       </c>
       <c r="F18">
-        <v>2.853434827430025</v>
+        <v>2.880629543029025</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4427,16 +4427,16 @@
         <v>64288.25790872025</v>
       </c>
       <c r="C19">
-        <v>12499.20536441801</v>
+        <v>12618.32928196163</v>
       </c>
       <c r="D19">
-        <v>118821.20995753</v>
+        <v>119953.637788319</v>
       </c>
       <c r="E19">
-        <v>1.848256801829013</v>
+        <v>1.865871648888593</v>
       </c>
       <c r="F19">
-        <v>2.83614948938383</v>
+        <v>2.863179466735554</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4447,16 +4447,16 @@
         <v>66288.32090172748</v>
       </c>
       <c r="C20">
-        <v>13093.78178154071</v>
+        <v>13218.57232108322</v>
       </c>
       <c r="D20">
-        <v>124473.4324176754</v>
+        <v>125659.7288635203</v>
       </c>
       <c r="E20">
-        <v>1.877758113713687</v>
+        <v>1.895654123594577</v>
       </c>
       <c r="F20">
-        <v>2.813191175599547</v>
+        <v>2.84000234829942</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4467,16 +4467,16 @@
         <v>68288.3838947347</v>
       </c>
       <c r="C21">
-        <v>13682.95906449973</v>
+        <v>13813.36476948897</v>
       </c>
       <c r="D21">
-        <v>130074.3290826723</v>
+        <v>131314.0049820936</v>
       </c>
       <c r="E21">
-        <v>1.904779724809121</v>
+        <v>1.922933264675171</v>
       </c>
       <c r="F21">
-        <v>2.785087816116508</v>
+        <v>2.811631149207368</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4487,16 +4487,16 @@
         <v>70288.44688774191</v>
       </c>
       <c r="C22">
-        <v>14265.70995904106</v>
+        <v>14401.66958265839</v>
       </c>
       <c r="D22">
-        <v>135614.1345642552</v>
+        <v>136906.6076865523</v>
       </c>
       <c r="E22">
-        <v>1.929394382278006</v>
+        <v>1.947782512611306</v>
       </c>
       <c r="F22">
-        <v>2.752358692359835</v>
+        <v>2.778590099906156</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4507,16 +4507,16 @@
         <v>72288.50988074916</v>
       </c>
       <c r="C23">
-        <v>14841.11525889299</v>
+        <v>14982.5587938067</v>
       </c>
       <c r="D23">
-        <v>141084.1106108137</v>
+        <v>142428.7154452107</v>
       </c>
       <c r="E23">
-        <v>1.951680991122286</v>
+        <v>1.970281524410566</v>
       </c>
       <c r="F23">
-        <v>2.715509289692012</v>
+        <v>2.741389503296226</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4527,16 +4527,16 @@
         <v>74288.57287375638</v>
       </c>
       <c r="C24">
-        <v>15408.36041136737</v>
+        <v>15555.21008713566</v>
       </c>
       <c r="D24">
-        <v>146476.5138392159</v>
+        <v>147872.5110764748</v>
       </c>
       <c r="E24">
-        <v>1.97172335088646</v>
+        <v>1.990514898270621</v>
       </c>
       <c r="F24">
-        <v>2.675027071241469</v>
+        <v>2.700521468282782</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4547,16 +4547,16 @@
         <v>76288.63586676362</v>
       </c>
       <c r="C25">
-        <v>15966.73132824028</v>
+        <v>16118.90256878978</v>
       </c>
       <c r="D25">
-        <v>151784.5559117789</v>
+        <v>153231.1415462786</v>
       </c>
       <c r="E25">
-        <v>1.989608992050496</v>
+        <v>2.008570998882367</v>
       </c>
       <c r="F25">
-        <v>2.63137811823542</v>
+        <v>2.656456518089141</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4567,16 +4567,16 @@
         <v>78288.69885977084</v>
       </c>
       <c r="C26">
-        <v>16515.60957764965</v>
+        <v>16673.01191293019</v>
       </c>
       <c r="D26">
-        <v>157002.3578289993</v>
+        <v>158498.6718252007</v>
       </c>
       <c r="E26">
-        <v>2.005428115623926</v>
+        <v>2.024540886917796</v>
       </c>
       <c r="F26">
-        <v>2.585004569142089</v>
+        <v>2.609641004992729</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4587,16 +4587,16 @@
         <v>80288.76185277806</v>
       </c>
       <c r="C27">
-        <v>17054.46711740077</v>
+        <v>17217.00504484591</v>
       </c>
       <c r="D27">
-        <v>162124.8998627702</v>
+        <v>163670.0343445188</v>
       </c>
       <c r="E27">
-        <v>2.019272636935807</v>
+        <v>2.038517353706778</v>
       </c>
       <c r="F27">
-        <v>2.536322781559872</v>
+        <v>2.560495254696036</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4607,16 +4607,16 @@
         <v>82288.8248457853</v>
       </c>
       <c r="C28">
-        <v>17582.86071341124</v>
+        <v>17750.43450620353</v>
       </c>
       <c r="D28">
-        <v>167147.9684964374</v>
+        <v>168740.975430577</v>
       </c>
       <c r="E28">
-        <v>2.031235332497259</v>
+        <v>2.05059405996876</v>
       </c>
       <c r="F28">
-        <v>2.485722136358785</v>
+        <v>2.509412359070927</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4627,16 +4627,16 @@
         <v>84288.88783879252</v>
       </c>
       <c r="C29">
-        <v>18100.42616981486</v>
+        <v>18272.93263016117</v>
       </c>
       <c r="D29">
-        <v>172068.1015744303</v>
+        <v>173707.9999316643</v>
       </c>
       <c r="E29">
-        <v>2.041409087085367</v>
+        <v>2.060864775720983</v>
       </c>
       <c r="F29">
-        <v>2.433564402428312</v>
+        <v>2.456757534852319</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4647,16 +4647,16 @@
         <v>86288.95083179977</v>
       </c>
       <c r="C30">
-        <v>18606.87248010098</v>
+        <v>18784.205636765</v>
       </c>
       <c r="D30">
-        <v>176882.5327012306</v>
+        <v>178568.3150870766</v>
       </c>
       <c r="E30">
-        <v>2.049886236837228</v>
+        <v>2.069422717111881</v>
       </c>
       <c r="F30">
-        <v>2.38018358186626</v>
+        <v>2.402867967351446</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4667,16 +4667,16 @@
         <v>88289.01382480699</v>
       </c>
       <c r="C31">
-        <v>19101.97599207587</v>
+        <v>19284.02774229976</v>
       </c>
       <c r="D31">
-        <v>181589.1357717385</v>
+        <v>183319.7745288286</v>
       </c>
       <c r="E31">
-        <v>2.056758003119937</v>
+        <v>2.076359974895544</v>
       </c>
       <c r="F31">
-        <v>2.32588615893872</v>
+        <v>2.348053061788558</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4687,16 +4687,16 @@
         <v>90289.0768178142</v>
       </c>
       <c r="C32">
-        <v>19585.57466376106</v>
+        <v>19772.23536044279</v>
       </c>
       <c r="D32">
-        <v>186186.3703661127</v>
+        <v>187960.8231560778</v>
       </c>
       <c r="E32">
-        <v>2.062114011219769</v>
+        <v>2.081767028533763</v>
       </c>
       <c r="F32">
-        <v>2.270951681098974</v>
+        <v>2.292595029849353</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4707,16 +4707,16 @@
         <v>92289.13981082145</v>
       </c>
       <c r="C33">
-        <v>20057.56247283994</v>
+        <v>20248.72145842973</v>
       </c>
       <c r="D33">
-        <v>190673.2286042858</v>
+        <v>192490.4434831366</v>
       </c>
       <c r="E33">
-        <v>2.066041887432656</v>
+        <v>2.085732339446574</v>
       </c>
       <c r="F33">
-        <v>2.215633606287863</v>
+        <v>2.236749745060478</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4727,16 +4727,16 @@
         <v>94289.20280382867</v>
       </c>
       <c r="C34">
-        <v>20517.88402908876</v>
+        <v>20713.43011813923</v>
       </c>
       <c r="D34">
-        <v>195049.1839301117</v>
+        <v>196908.1039355054</v>
       </c>
       <c r="E34">
-        <v>2.068626927898808</v>
+        <v>2.088342016690694</v>
       </c>
       <c r="F34">
-        <v>2.160160357236578</v>
+        <v>2.180747807140307</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4747,16 +4747,16 @@
         <v>96289.2657968359</v>
       </c>
       <c r="C35">
-        <v>20966.52942745997</v>
+        <v>21166.35134012352</v>
       </c>
       <c r="D35">
-        <v>199314.1421832261</v>
+        <v>201213.7094554225</v>
       </c>
       <c r="E35">
-        <v>2.069951832468699</v>
+        <v>2.089679548289114</v>
       </c>
       <c r="F35">
-        <v>2.104736530226141</v>
+        <v>2.124795762278714</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4767,16 +4767,16 @@
         <v>98289.32878984312</v>
       </c>
       <c r="C36">
-        <v>21403.52936914332</v>
+        <v>21607.51611817062</v>
       </c>
       <c r="D36">
-        <v>203468.3952183832</v>
+        <v>205407.5546791699</v>
       </c>
       <c r="E36">
-        <v>2.070096496980137</v>
+        <v>2.089825591528467</v>
       </c>
       <c r="F36">
-        <v>2.049544212458819</v>
+        <v>2.069077433063554</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4787,16 +4787,16 @@
         <v>100289.3917828503</v>
       </c>
       <c r="C37">
-        <v>21828.95056898162</v>
+        <v>22036.99180295043</v>
       </c>
       <c r="D37">
-        <v>207512.5772469681</v>
+        <v>209490.2798624961</v>
       </c>
       <c r="E37">
-        <v>2.069137857534132</v>
+        <v>2.088857815750751</v>
       </c>
       <c r="F37">
-        <v>1.994744368666931</v>
+        <v>2.013755318304586</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4807,16 +4807,16 @@
         <v>102289.4547758576</v>
       </c>
       <c r="C38">
-        <v>22242.89145999853</v>
+        <v>22454.87776560444</v>
       </c>
       <c r="D38">
-        <v>211447.6240029438</v>
+        <v>213462.8296573949</v>
       </c>
       <c r="E38">
-        <v>2.067149780652167</v>
+        <v>2.08685079146376</v>
       </c>
       <c r="F38">
-        <v>1.940478263682698</v>
+        <v>1.958972029161274</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4827,16 +4827,16 @@
         <v>104289.5177688648</v>
       </c>
       <c r="C39">
-        <v>22645.47819941293</v>
+        <v>22861.30136569533</v>
       </c>
       <c r="D39">
-        <v>215274.7347748215</v>
+        <v>217326.4147822196</v>
       </c>
       <c r="E39">
-        <v>2.064202993554265</v>
+        <v>2.083875919954647</v>
       </c>
       <c r="F39">
-        <v>1.886868893323624</v>
+        <v>1.904851733665122</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4847,16 +4847,16 @@
         <v>106289.580761872</v>
       </c>
       <c r="C40">
-        <v>23036.86097526439</v>
+        <v>23256.41422263268</v>
       </c>
       <c r="D40">
-        <v>218995.33729533</v>
+        <v>221082.4765767334</v>
       </c>
       <c r="E40">
-        <v>2.060365049194808</v>
+        <v>2.080001397992527</v>
       </c>
       <c r="F40">
-        <v>1.834022401053927</v>
+        <v>1.851501586882675</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4867,16 +4867,16 @@
         <v>108289.6437548793</v>
       </c>
       <c r="C41">
-        <v>23417.21060853996</v>
+        <v>23640.38878541626</v>
       </c>
       <c r="D41">
-        <v>222611.0554402099</v>
+        <v>224732.654393056</v>
       </c>
       <c r="E41">
-        <v>2.055700321113852</v>
+        <v>2.075292212630722</v>
       </c>
       <c r="F41">
-        <v>1.782029462440918</v>
+        <v>1.799013128566489</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4887,16 +4887,16 @@
         <v>110289.7067478865</v>
       </c>
       <c r="C42">
-        <v>23786.71544236064</v>
+        <v>24013.41519217479</v>
       </c>
       <c r="D42">
-        <v>226123.6796558833</v>
+        <v>228278.7557414934</v>
       </c>
       <c r="E42">
-        <v>2.050270023591449</v>
+        <v>2.069810161553158</v>
       </c>
       <c r="F42">
-        <v>1.73096662343605</v>
+        <v>1.747463634190659</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4907,16 +4907,16 @@
         <v>112289.7697408937</v>
       </c>
       <c r="C43">
-        <v>24145.5785072391</v>
+        <v>24375.69840840717</v>
       </c>
       <c r="D43">
-        <v>229535.1400115402</v>
+        <v>231722.7290857973</v>
       </c>
       <c r="E43">
-        <v>2.044132253019912</v>
+        <v>2.063613894840934</v>
       </c>
       <c r="F43">
-        <v>1.680897581986338</v>
+        <v>1.696917408776743</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4927,16 +4927,16 @@
         <v>114289.8327339009</v>
       </c>
       <c r="C44">
-        <v>24494.01494955133</v>
+        <v>24727.45563094606</v>
       </c>
       <c r="D44">
-        <v>232847.4817534157</v>
+        <v>235066.6391644616</v>
       </c>
       <c r="E44">
-        <v>2.037342046825377</v>
+        <v>2.056758974455437</v>
       </c>
       <c r="F44">
-        <v>1.63187440545991</v>
+        <v>1.64742701592193</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4947,16 +4947,16 @@
         <v>116289.8957269082</v>
       </c>
       <c r="C45">
-        <v>24832.24970907099</v>
+        <v>25068.91394335799</v>
       </c>
       <c r="D45">
-        <v>236062.8432267322</v>
+        <v>238312.6447022489</v>
       </c>
       <c r="E45">
-        <v>2.029951456669076</v>
+        <v>2.04929794813726</v>
       </c>
       <c r="F45">
-        <v>1.583938678880189</v>
+        <v>1.599034436976478</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -4967,16 +4967,16 @@
         <v>118289.9587199154</v>
       </c>
       <c r="C46">
-        <v>25160.51543060284</v>
+        <v>25400.30820767348</v>
       </c>
       <c r="D46">
-        <v>239183.4360230577</v>
+        <v>241462.9783683431</v>
       </c>
       <c r="E46">
-        <v>2.022009633035645</v>
+        <v>2.041280434800678</v>
       </c>
       <c r="F46">
-        <v>1.537122581053035</v>
+        <v>1.551772157426991</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4987,16 +4987,16 @@
         <v>120290.0217129226</v>
       </c>
       <c r="C47">
-        <v>25479.05059433714</v>
+        <v>25721.87917692287</v>
       </c>
       <c r="D47">
-        <v>242211.5272068921</v>
+        <v>244519.9288335463</v>
       </c>
       <c r="E47">
-        <v>2.013562918667855</v>
+        <v>2.032753218858866</v>
       </c>
       <c r="F47">
-        <v>1.491449887385137</v>
+        <v>1.505664179272127</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -5007,16 +5007,16 @@
         <v>122290.0847059299</v>
       </c>
       <c r="C48">
-        <v>25788.09784945583</v>
+        <v>26033.87181286077</v>
       </c>
       <c r="D48">
-        <v>245149.4234744253</v>
+        <v>247485.8247780607</v>
       </c>
       <c r="E48">
-        <v>2.004654948632463</v>
+        <v>2.023760351243424</v>
       </c>
       <c r="F48">
-        <v>1.446936899570592</v>
+        <v>1.460726959569595</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -5027,16 +5027,16 @@
         <v>124290.1476989371</v>
       </c>
       <c r="C49">
-        <v>26087.90253568679</v>
+        <v>26336.53379343008</v>
       </c>
       <c r="D49">
-        <v>247999.4570989876</v>
+        <v>250363.0207029925</v>
       </c>
       <c r="E49">
-        <v>1.995326755099741</v>
+        <v>2.014343255182515</v>
       </c>
       <c r="F49">
-        <v>1.403593303413663</v>
+        <v>1.416970276434407</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -5047,16 +5047,16 @@
         <v>126290.2106919443</v>
       </c>
       <c r="C50">
-        <v>26378.71137787049</v>
+        <v>26630.11419488714</v>
       </c>
       <c r="D50">
-        <v>250763.9735212062</v>
+        <v>253153.8844022361</v>
       </c>
       <c r="E50">
-        <v>1.98561687518985</v>
+        <v>2.004540835075066</v>
       </c>
       <c r="F50">
-        <v>1.361422956895715</v>
+        <v>1.374398024616497</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -5067,16 +5067,16 @@
         <v>128290.2736849515</v>
       </c>
       <c r="C51">
-        <v>26660.77133912246</v>
+        <v>26914.86233403418</v>
       </c>
       <c r="D51">
-        <v>253445.3204468228</v>
+        <v>255860.7859563879</v>
       </c>
       <c r="E51">
-        <v>1.975561460483126</v>
+        <v>1.994389587044746</v>
       </c>
       <c r="F51">
-        <v>1.32042461122265</v>
+        <v>1.333008943420086</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -5087,16 +5087,16 @@
         <v>130290.3366779588</v>
       </c>
       <c r="C52">
-        <v>26934.32861880708</v>
+        <v>27191.02675664337</v>
       </c>
       <c r="D52">
-        <v>256045.838321131</v>
+        <v>258486.0881164004</v>
       </c>
       <c r="E52">
-        <v>1.965194387009718</v>
+        <v>1.98392370997786</v>
       </c>
       <c r="F52">
-        <v>1.280592568039438</v>
+        <v>1.29279728018189</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -5107,16 +5107,16 @@
         <v>132290.399670966</v>
       </c>
       <c r="C53">
-        <v>27199.62778224733</v>
+        <v>27458.85435887222</v>
       </c>
       <c r="D53">
-        <v>258567.8520557343</v>
+        <v>261032.1379514923</v>
       </c>
       <c r="E53">
-        <v>1.954547364728256</v>
+        <v>1.973175216045413</v>
       </c>
       <c r="F53">
-        <v>1.241917276299813</v>
+        <v>1.253753392829192</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -5127,16 +5127,16 @@
         <v>134290.4626639732</v>
       </c>
       <c r="C54">
-        <v>27456.91100985344</v>
+        <v>27718.58962923601</v>
       </c>
       <c r="D54">
-        <v>261013.6638905381</v>
+        <v>263501.2596431103</v>
       </c>
       <c r="E54">
-        <v>1.943650045674923</v>
+        <v>1.962174039882887</v>
       </c>
       <c r="F54">
-        <v>1.20438587245974</v>
+        <v>1.215864295221707</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -5147,16 +5147,16 @@
         <v>136290.5256569805</v>
       </c>
       <c r="C55">
-        <v>27706.4174541389</v>
+        <v>27970.4739994959</v>
       </c>
       <c r="D55">
-        <v>263385.5472813493</v>
+        <v>265895.7483142758</v>
       </c>
       <c r="E55">
-        <v>1.932530130115169</v>
+        <v>1.950948145753646</v>
       </c>
       <c r="F55">
-        <v>1.167982667745466</v>
+        <v>1.179114149063553</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -5167,16 +5167,16 @@
         <v>138290.5886499877</v>
       </c>
       <c r="C56">
-        <v>27948.38269388513</v>
+        <v>28214.7452936214</v>
       </c>
       <c r="D56">
-        <v>265685.7417110013</v>
+        <v>268217.8647912567</v>
       </c>
       <c r="E56">
-        <v>1.921213470162092</v>
+        <v>1.939523632154853</v>
       </c>
       <c r="F56">
-        <v>1.132689586250779</v>
+        <v>1.143484706175708</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -5187,16 +5187,16 @@
         <v>140290.6516429949</v>
       </c>
       <c r="C57">
-        <v>28183.03827550297</v>
+        <v>28451.63726478087</v>
       </c>
       <c r="D57">
-        <v>267916.4483293989</v>
+        <v>270469.8312020593</v>
       </c>
       <c r="E57">
-        <v>1.909724170439953</v>
+        <v>1.927924833440352</v>
       </c>
       <c r="F57">
-        <v>1.098486557561464</v>
+        <v>1.108955704862484</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -5207,16 +5207,16 @@
         <v>142290.7146360021</v>
       </c>
       <c r="C58">
-        <v>28410.61133240853</v>
+        <v>28681.37921108985</v>
       </c>
       <c r="D58">
-        <v>270079.8263351904</v>
+        <v>272653.8273236161</v>
       </c>
       <c r="E58">
-        <v>1.89808468547009</v>
+        <v>1.916174418134729</v>
       </c>
       <c r="F58">
-        <v>1.065351867501103</v>
+        <v>1.0755052240001</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -5227,16 +5227,16 @@
         <v>144290.7776290094</v>
       </c>
       <c r="C59">
-        <v>28631.32427397395</v>
+        <v>28904.19566159726</v>
       </c>
       <c r="D59">
-        <v>272177.9900188391</v>
+        <v>274771.9875966765</v>
       </c>
       <c r="E59">
-        <v>1.886315913541229</v>
+        <v>1.904293483698255</v>
       </c>
       <c r="F59">
-        <v>1.03326247045449</v>
+        <v>1.043109998336686</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -5247,16 +5247,16 @@
         <v>146290.8406220166</v>
       </c>
       <c r="C60">
-        <v>28845.39453632478</v>
+        <v>29120.30612470785</v>
       </c>
       <c r="D60">
-        <v>274213.006393629</v>
+        <v>276826.3987342342</v>
       </c>
       <c r="E60">
-        <v>1.874437286898468</v>
+        <v>1.892301647575413</v>
       </c>
       <c r="F60">
-        <v>1.002194266562669</v>
+        <v>1.01174569832909</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -5267,16 +5267,16 @@
         <v>148290.9036150238</v>
       </c>
       <c r="C61">
-        <v>29053.03438793072</v>
+        <v>29329.92489192004</v>
       </c>
       <c r="D61">
-        <v>276186.8933475512</v>
+        <v>278819.097855801</v>
       </c>
       <c r="E61">
-        <v>1.862466858146313</v>
+        <v>1.880217134421406</v>
       </c>
       <c r="F61">
-        <v>0.9869123926713735</v>
+        <v>0.9963181802442308</v>
       </c>
     </row>
   </sheetData>
